--- a/einnahmen/Einnahmen_Ausgaben_2025-2026.xlsx
+++ b/einnahmen/Einnahmen_Ausgaben_2025-2026.xlsx
@@ -712,20 +712,12 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Kontoführung</t>
-        </is>
-      </c>
+        <v>45688</v>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="8" t="n"/>
       <c r="D7" s="9" t="n">
-        <v>-15.9</v>
+        <v>385.5</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>45717</v>
@@ -745,20 +737,12 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>45747</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Kontoführung</t>
-        </is>
-      </c>
+        <v>45698</v>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="n"/>
       <c r="D8" s="9" t="n">
-        <v>-15.9</v>
+        <v>139.25</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>45748</v>
@@ -778,20 +762,12 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Einnahme</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>BP</t>
-        </is>
-      </c>
+        <v>45699</v>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="8" t="n"/>
       <c r="D9" s="9" t="n">
-        <v>385.5</v>
+        <v>-17.49</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>45778</v>
@@ -811,20 +787,12 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Domain</t>
-        </is>
-      </c>
+        <v>45699</v>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="8" t="n"/>
       <c r="D10" s="9" t="n">
-        <v>-7.95</v>
+        <v>-17.49</v>
       </c>
       <c r="F10" s="10" t="n">
         <v>45809</v>
@@ -844,20 +812,20 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>45757</v>
+        <v>45716</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>500</v>
+        <v>-15.9</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>45839</v>
@@ -877,20 +845,12 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>45763</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>MEB</t>
-        </is>
-      </c>
+        <v>45719</v>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="8" t="n"/>
       <c r="D12" s="9" t="n">
-        <v>-300</v>
+        <v>552.55</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>45870</v>
@@ -910,20 +870,12 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>45777</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>MEB</t>
-        </is>
-      </c>
+        <v>45720</v>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="n"/>
       <c r="D13" s="9" t="n">
-        <v>-300</v>
+        <v>-17.49</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>45901</v>
@@ -943,7 +895,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -952,11 +904,11 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>-300</v>
+        <v>-15.9</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>45931</v>
@@ -976,20 +928,20 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>45777</v>
+        <v>45748</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>-16.3</v>
+        <v>385.5</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>45962</v>
@@ -1009,7 +961,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -1042,20 +994,20 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>45797</v>
+        <v>45757</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>-13.95</v>
+        <v>500</v>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
@@ -1077,7 +1029,7 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>45804</v>
+        <v>45763</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -1090,25 +1042,25 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>-150</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>45805</v>
+        <v>45777</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MEB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1750</v>
+        <v>-300</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1122,7 +1074,7 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>45807</v>
+        <v>45777</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -1135,17 +1087,17 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>-750</v>
+        <v>-300</v>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>(sollte 0 sein – sonst steht ein Datum aus einem anderen Jahr oder eine Zeile ohne Art in der Liste)</t>
+          <t>(sollte 0 sein – sonst fehlt bei einer Zeile die Art (Einnahme/Ausgabe) oder das Datum liegt in einem anderen Jahr)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>45807</v>
+        <v>45777</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
@@ -1158,12 +1110,12 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>-17.1</v>
+        <v>-16.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>45807</v>
+        <v>45778</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
@@ -1172,34 +1124,34 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>-300</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>45809</v>
+        <v>45797</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>359.8</v>
+        <v>-13.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>45811</v>
+        <v>45804</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
@@ -1208,34 +1160,34 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>MEB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>-7.95</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>45813</v>
+        <v>45805</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Powercall</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>-82.11</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>45838</v>
+        <v>45807</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
@@ -1244,16 +1196,16 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>MEB</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>-15.9</v>
+        <v>-750</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>45842</v>
+        <v>45807</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
@@ -1262,16 +1214,16 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Powercall</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>-82.11</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>45846</v>
+        <v>45807</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
@@ -1280,34 +1232,34 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>MEB</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>-7.95</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>45854</v>
+        <v>45809</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Jabra Headset</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>-152.81</v>
+        <v>359.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>45869</v>
+        <v>45811</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
@@ -1316,34 +1268,34 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>-15.9</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>45870</v>
+        <v>45813</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>Powercall</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>500</v>
+        <v>-82.11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>45873</v>
+        <v>45838</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
@@ -1352,16 +1304,16 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>-7.95</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>45874</v>
+        <v>45842</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
@@ -1379,25 +1331,25 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>45874</v>
+        <v>45846</v>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>100</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>45898</v>
+        <v>45854</v>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
@@ -1406,16 +1358,16 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Jabra Headset</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>-15.9</v>
+        <v>-152.81</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>45901</v>
+        <v>45869</v>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
@@ -1424,34 +1376,34 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>-7.95</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>45904</v>
+        <v>45870</v>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Powercall</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>-82.11</v>
+        <v>500</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>45930</v>
+        <v>45873</v>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
@@ -1460,16 +1412,16 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>-15.9</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>45937</v>
+        <v>45874</v>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
@@ -1478,16 +1430,16 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Powercall</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>-7.95</v>
+        <v>-82.11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>45946</v>
+        <v>45874</v>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
@@ -1500,12 +1452,12 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>45958</v>
+        <v>45898</v>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
@@ -1514,16 +1466,16 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>-10.95</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>45961</v>
+        <v>45901</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
@@ -1532,34 +1484,34 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>-16.1</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>45962</v>
+        <v>45904</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Powercall</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>134.46</v>
+        <v>-82.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>45989</v>
+        <v>45930</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
@@ -1568,16 +1520,16 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>-7.5</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>45989</v>
+        <v>45937</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
@@ -1586,16 +1538,16 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>-15.9</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>45992</v>
+        <v>45946</v>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
@@ -1604,66 +1556,138 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>564.64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>-10.95</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>-16.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Einnahme</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>134.46</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>-7.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>-15.9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Einnahme</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>564.64</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
         <v>46022</v>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="D53" s="9" t="n">
         <v>-15.9</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="n"/>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="9" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="n"/>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="9" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="7" t="n"/>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="9" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="7" t="n"/>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="9" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="B53" s="7" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="9" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -3772,7 +3796,7 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>(sollte 0 sein – sonst steht ein Datum aus einem anderen Jahr oder eine Zeile ohne Art in der Liste)</t>
+          <t>(sollte 0 sein – sonst fehlt bei einer Zeile die Art (Einnahme/Ausgabe) oder das Datum liegt in einem anderen Jahr)</t>
         </is>
       </c>
     </row>

--- a/einnahmen/Einnahmen_Ausgaben_2025-2026.xlsx
+++ b/einnahmen/Einnahmen_Ausgaben_2025-2026.xlsx
@@ -870,12 +870,12 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>45720</v>
+        <v>45719</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="9" t="n">
-        <v>-17.49</v>
+        <v>42.26</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>45901</v>
@@ -895,20 +895,12 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>45747</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Kontoführung</t>
-        </is>
-      </c>
+        <v>45720</v>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="n"/>
       <c r="D14" s="9" t="n">
-        <v>-15.9</v>
+        <v>-17.49</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>45931</v>
@@ -928,20 +920,20 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>45748</v>
+        <v>45747</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>385.5</v>
+        <v>-15.9</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>45962</v>
@@ -965,16 +957,16 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>-7.95</v>
+        <v>385.5</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>45992</v>
@@ -994,20 +986,20 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>45757</v>
+        <v>45748</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>500</v>
+        <v>-7.95</v>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
@@ -1029,25 +1021,25 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>45763</v>
+        <v>45757</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>-300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>45777</v>
+        <v>45763</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -1106,16 +1098,16 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>MEB</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>-16.3</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>45778</v>
+        <v>45777</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
@@ -1124,16 +1116,16 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>-7.95</v>
+        <v>-16.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>45797</v>
+        <v>45778</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
@@ -1146,12 +1138,12 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>-13.95</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>45804</v>
+        <v>45797</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
@@ -1160,47 +1152,47 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>-150</v>
+        <v>-13.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>45805</v>
+        <v>45804</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MEB</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1750</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>45807</v>
+        <v>45805</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>-750</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="27">
@@ -1214,11 +1206,11 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>MEB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>-17.1</v>
+        <v>-750</v>
       </c>
     </row>
     <row r="28">
@@ -1232,52 +1224,52 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>-300</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>45809</v>
+        <v>45807</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>MEB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>359.8</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>45811</v>
+        <v>45809</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>-7.95</v>
+        <v>359.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>45813</v>
+        <v>45811</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1286,16 +1278,16 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Powercall</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>-82.11</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>45838</v>
+        <v>45813</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
@@ -1304,16 +1296,16 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Powercall</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>-15.9</v>
+        <v>-82.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>45842</v>
+        <v>45838</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
@@ -1322,16 +1314,16 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Powercall</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>-82.11</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>45846</v>
+        <v>45842</v>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
@@ -1340,16 +1332,16 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Powercall</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>-7.95</v>
+        <v>-82.11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>45854</v>
+        <v>45846</v>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
@@ -1358,16 +1350,16 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Jabra Headset</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>-152.81</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>45869</v>
+        <v>45854</v>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
@@ -1376,52 +1368,52 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Jabra Headset</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>-15.9</v>
+        <v>-152.81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>45870</v>
+        <v>45869</v>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>500</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>45873</v>
+        <v>45870</v>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>-7.95</v>
+        <v>500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>45874</v>
+        <v>45873</v>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
@@ -1430,11 +1422,11 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Powercall</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>-82.11</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="40">
@@ -1443,39 +1435,39 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Powercall</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>100</v>
+        <v>-82.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>45898</v>
+        <v>45874</v>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>-15.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>45901</v>
+        <v>45898</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
@@ -1484,16 +1476,16 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>-7.95</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>45904</v>
+        <v>45901</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
@@ -1502,16 +1494,16 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Powercall</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>-82.11</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>45930</v>
+        <v>45904</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
@@ -1520,16 +1512,16 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Powercall</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>-15.9</v>
+        <v>-82.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>45937</v>
+        <v>45930</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
@@ -1538,52 +1530,52 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>-7.95</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>45946</v>
+        <v>45937</v>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>60</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>45958</v>
+        <v>45946</v>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>-10.95</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>45961</v>
+        <v>45958</v>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
@@ -1592,47 +1584,47 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>-16.1</v>
+        <v>-10.95</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>134.46</v>
+        <v>-16.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>45989</v>
+        <v>45962</v>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>-7.5</v>
+        <v>134.46</v>
       </c>
     </row>
     <row r="51">
@@ -1646,54 +1638,66 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Kontoführung</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>-15.9</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>45992</v>
+        <v>45989</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Kontoführung</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>564.64</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Einnahme</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>564.64</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
         <v>46022</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
       </c>
-      <c r="D53" s="9" t="n">
+      <c r="D54" s="9" t="n">
         <v>-15.9</v>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="7" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="9" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -3336,20 +3340,12 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>46063</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Einnahme</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
       <c r="D6" s="9" t="n">
-        <v>405.73</v>
+        <v>-15.9</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>46054</v>
@@ -3369,7 +3365,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>46091</v>
+        <v>46063</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
@@ -3382,7 +3378,7 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>544.42</v>
+        <v>405.73</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>46082</v>
@@ -3402,20 +3398,12 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>46122</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Einnahme</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
+        <v>46080</v>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="n"/>
       <c r="D8" s="9" t="n">
-        <v>446.89</v>
+        <v>-15.9</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>46113</v>
@@ -3435,20 +3423,20 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>46132</v>
+        <v>46091</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>-21.42</v>
+        <v>544.42</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>46143</v>
@@ -3468,20 +3456,12 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Einnahme</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
+        <v>46092</v>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="8" t="n"/>
       <c r="D10" s="9" t="n">
-        <v>575.52</v>
+        <v>-32.25</v>
       </c>
       <c r="F10" s="10" t="n">
         <v>46174</v>
@@ -3501,20 +3481,12 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>46183</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Einnahme</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
+        <v>46112</v>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="8" t="n"/>
       <c r="D11" s="9" t="n">
-        <v>560.23</v>
+        <v>-15.9</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>46204</v>
@@ -3534,20 +3506,20 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>46191</v>
+        <v>46122</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>V2T</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>-39.9</v>
+        <v>446.89</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>46235</v>
@@ -3567,7 +3539,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>46202</v>
+        <v>46132</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -3576,11 +3548,11 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>-7.95</v>
+        <v>-21.42</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>46266</v>
@@ -3600,20 +3572,12 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Einnahme</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
+        <v>46142</v>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="n"/>
       <c r="D14" s="9" t="n">
-        <v>178.48</v>
+        <v>-15.9</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>46296</v>
@@ -3633,20 +3597,20 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>46223</v>
+        <v>46150</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>-21.42</v>
+        <v>575.52</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>46327</v>
@@ -3666,20 +3630,12 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>46232</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Whoop</t>
-        </is>
-      </c>
+        <v>46154</v>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="8" t="n"/>
       <c r="D16" s="9" t="n">
-        <v>-11.89</v>
+        <v>-15.9</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>46357</v>
@@ -3699,20 +3655,12 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Einnahme</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
+        <v>46161</v>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="8" t="n"/>
       <c r="D17" s="9" t="n">
-        <v>420.07</v>
+        <v>-21.42</v>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
@@ -3734,38 +3682,30 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>46252</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Claude</t>
-        </is>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="8" t="n"/>
       <c r="D18" s="9" t="n">
-        <v>-21.42</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>46262</v>
+        <v>46183</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Einnahme</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>-11.89</v>
+        <v>560.23</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -3779,20 +3719,20 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>46275</v>
+        <v>46191</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Einnahme</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>V2T</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>344.78</v>
+        <v>-39.9</v>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
@@ -3802,7 +3742,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>46283</v>
+        <v>46202</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
@@ -3811,34 +3751,26 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>-21.42</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Whoop</t>
-        </is>
-      </c>
+        <v>46203</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="8" t="n"/>
       <c r="D22" s="9" t="n">
-        <v>-11.89</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>46304</v>
+        <v>46213</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
@@ -3851,80 +3783,200 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>215.33</v>
+        <v>178.48</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="9" t="n"/>
+      <c r="A24" s="6" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>-21.42</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="9" t="n"/>
+      <c r="A25" s="6" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Whoop</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>-11.89</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n"/>
+      <c r="A26" s="6" t="n">
+        <v>46234</v>
+      </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>-15.9</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="9" t="n"/>
+      <c r="A27" s="6" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Einnahme</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>420.07</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="9" t="n"/>
+      <c r="A28" s="6" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>-21.42</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="9" t="n"/>
+      <c r="A29" s="6" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Whoop</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>-11.89</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n"/>
+      <c r="A30" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>-15.9</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="9" t="n"/>
+      <c r="A31" s="6" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Einnahme</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>344.78</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="9" t="n"/>
+      <c r="A32" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>-21.42</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="9" t="n"/>
+      <c r="A33" s="6" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Whoop</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>-11.89</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n"/>
+      <c r="A34" s="6" t="n">
+        <v>46295</v>
+      </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>-15.9</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="9" t="n"/>
+      <c r="A35" s="6" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Einnahme</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>215.33</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>

--- a/einnahmen/Einnahmen_Ausgaben_2025-2026.xlsx
+++ b/einnahmen/Einnahmen_Ausgaben_2025-2026.xlsx
@@ -2,13 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Übersicht" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2025" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +14,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="165" formatCode="#,##0.00 €;-#,##0.00 €;-"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="MMMM YYYY"/>
+    <numFmt numFmtId="166" formatCode="MMMM YYYY"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -34,54 +29,61 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color theme="1"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="FF595959"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color theme="1"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00375623"/>
+      <color rgb="FF375623"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00C00000"/>
+      <color rgb="FFC00000"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="FF375623"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="FFC00000"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -89,61 +91,65 @@
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00548235"/>
+        <fgColor rgb="FF548235"/>
+        <bgColor rgb="FF548235"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FFC00000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
     <border>
-      <top style="medium"/>
-      <bottom style="double"/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,42 +169,79 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
     <dxf>
       <font>
-        <color rgb="00375623"/>
+        <color rgb="FF375623"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E2EFDA"/>
-          <bgColor rgb="00E2EFDA"/>
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
       <font>
-        <color rgb="00C00000"/>
+        <color rgb="FFC00000"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FCE4E4"/>
-          <bgColor rgb="00FCE4E4"/>
+          <fgColor rgb="FFFCE4E4"/>
+          <bgColor rgb="FFFCE4E4"/>
         </patternFill>
       </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill/>
+      </fill>
+      <border/>
     </dxf>
     <dxf>
       <font>
@@ -213,7 +256,6 @@
       </font>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -286,20 +328,20 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -323,77 +365,19 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="0000FF"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -405,166 +389,135 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -574,18 +527,567 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I304"/>
+  <dimension ref="A2:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" style="23" min="1" max="1"/>
+    <col width="16" customWidth="1" style="23" min="2" max="2"/>
+    <col width="16" customWidth="1" style="23" min="3" max="3"/>
+    <col width="16" customWidth="1" style="23" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" s="23">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Monat 2025</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Einnahmen (€)</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>Ausgaben (€)</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>Differenz (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10">
+        <f>'2025'!F5</f>
+        <v/>
+      </c>
+      <c r="B3" s="11">
+        <f>'2025'!G5</f>
+        <v/>
+      </c>
+      <c r="C3" s="12">
+        <f>'2025'!H5</f>
+        <v/>
+      </c>
+      <c r="D3" s="13">
+        <f>'2025'!I5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10">
+        <f>'2025'!F6</f>
+        <v/>
+      </c>
+      <c r="B4" s="11">
+        <f>'2025'!G6</f>
+        <v/>
+      </c>
+      <c r="C4" s="12">
+        <f>'2025'!H6</f>
+        <v/>
+      </c>
+      <c r="D4" s="13">
+        <f>'2025'!I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10">
+        <f>'2025'!F7</f>
+        <v/>
+      </c>
+      <c r="B5" s="11">
+        <f>'2025'!G7</f>
+        <v/>
+      </c>
+      <c r="C5" s="12">
+        <f>'2025'!H7</f>
+        <v/>
+      </c>
+      <c r="D5" s="13">
+        <f>'2025'!I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10">
+        <f>'2025'!F8</f>
+        <v/>
+      </c>
+      <c r="B6" s="11">
+        <f>'2025'!G8</f>
+        <v/>
+      </c>
+      <c r="C6" s="12">
+        <f>'2025'!H8</f>
+        <v/>
+      </c>
+      <c r="D6" s="13">
+        <f>'2025'!I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10">
+        <f>'2025'!F9</f>
+        <v/>
+      </c>
+      <c r="B7" s="11">
+        <f>'2025'!G9</f>
+        <v/>
+      </c>
+      <c r="C7" s="12">
+        <f>'2025'!H9</f>
+        <v/>
+      </c>
+      <c r="D7" s="13">
+        <f>'2025'!I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10">
+        <f>'2025'!F10</f>
+        <v/>
+      </c>
+      <c r="B8" s="11">
+        <f>'2025'!G10</f>
+        <v/>
+      </c>
+      <c r="C8" s="12">
+        <f>'2025'!H10</f>
+        <v/>
+      </c>
+      <c r="D8" s="13">
+        <f>'2025'!I10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10">
+        <f>'2025'!F11</f>
+        <v/>
+      </c>
+      <c r="B9" s="11">
+        <f>'2025'!G11</f>
+        <v/>
+      </c>
+      <c r="C9" s="12">
+        <f>'2025'!H11</f>
+        <v/>
+      </c>
+      <c r="D9" s="13">
+        <f>'2025'!I11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10">
+        <f>'2025'!F12</f>
+        <v/>
+      </c>
+      <c r="B10" s="11">
+        <f>'2025'!G12</f>
+        <v/>
+      </c>
+      <c r="C10" s="12">
+        <f>'2025'!H12</f>
+        <v/>
+      </c>
+      <c r="D10" s="13">
+        <f>'2025'!I12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10">
+        <f>'2025'!F13</f>
+        <v/>
+      </c>
+      <c r="B11" s="11">
+        <f>'2025'!G13</f>
+        <v/>
+      </c>
+      <c r="C11" s="12">
+        <f>'2025'!H13</f>
+        <v/>
+      </c>
+      <c r="D11" s="13">
+        <f>'2025'!I13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10">
+        <f>'2025'!F14</f>
+        <v/>
+      </c>
+      <c r="B12" s="11">
+        <f>'2025'!G14</f>
+        <v/>
+      </c>
+      <c r="C12" s="12">
+        <f>'2025'!H14</f>
+        <v/>
+      </c>
+      <c r="D12" s="13">
+        <f>'2025'!I14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10">
+        <f>'2025'!F15</f>
+        <v/>
+      </c>
+      <c r="B13" s="11">
+        <f>'2025'!G15</f>
+        <v/>
+      </c>
+      <c r="C13" s="12">
+        <f>'2025'!H15</f>
+        <v/>
+      </c>
+      <c r="D13" s="13">
+        <f>'2025'!I15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10">
+        <f>'2025'!F16</f>
+        <v/>
+      </c>
+      <c r="B14" s="11">
+        <f>'2025'!G16</f>
+        <v/>
+      </c>
+      <c r="C14" s="12">
+        <f>'2025'!H16</f>
+        <v/>
+      </c>
+      <c r="D14" s="13">
+        <f>'2025'!I16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Gesamt 2025</t>
+        </is>
+      </c>
+      <c r="B15" s="17">
+        <f>'2025'!G17</f>
+        <v/>
+      </c>
+      <c r="C15" s="18">
+        <f>'2025'!H17</f>
+        <v/>
+      </c>
+      <c r="D15" s="19">
+        <f>'2025'!I17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="23">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>Monat 2026</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Einnahmen (€)</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Ausgaben (€)</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>Differenz (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10">
+        <f>'2026'!F5</f>
+        <v/>
+      </c>
+      <c r="B21" s="11">
+        <f>'2026'!G5</f>
+        <v/>
+      </c>
+      <c r="C21" s="12">
+        <f>'2026'!H5</f>
+        <v/>
+      </c>
+      <c r="D21" s="13">
+        <f>'2026'!I5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10">
+        <f>'2026'!F6</f>
+        <v/>
+      </c>
+      <c r="B22" s="11">
+        <f>'2026'!G6</f>
+        <v/>
+      </c>
+      <c r="C22" s="12">
+        <f>'2026'!H6</f>
+        <v/>
+      </c>
+      <c r="D22" s="13">
+        <f>'2026'!I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10">
+        <f>'2026'!F7</f>
+        <v/>
+      </c>
+      <c r="B23" s="11">
+        <f>'2026'!G7</f>
+        <v/>
+      </c>
+      <c r="C23" s="12">
+        <f>'2026'!H7</f>
+        <v/>
+      </c>
+      <c r="D23" s="13">
+        <f>'2026'!I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10">
+        <f>'2026'!F8</f>
+        <v/>
+      </c>
+      <c r="B24" s="11">
+        <f>'2026'!G8</f>
+        <v/>
+      </c>
+      <c r="C24" s="12">
+        <f>'2026'!H8</f>
+        <v/>
+      </c>
+      <c r="D24" s="13">
+        <f>'2026'!I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10">
+        <f>'2026'!F9</f>
+        <v/>
+      </c>
+      <c r="B25" s="11">
+        <f>'2026'!G9</f>
+        <v/>
+      </c>
+      <c r="C25" s="12">
+        <f>'2026'!H9</f>
+        <v/>
+      </c>
+      <c r="D25" s="13">
+        <f>'2026'!I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10">
+        <f>'2026'!F10</f>
+        <v/>
+      </c>
+      <c r="B26" s="11">
+        <f>'2026'!G10</f>
+        <v/>
+      </c>
+      <c r="C26" s="12">
+        <f>'2026'!H10</f>
+        <v/>
+      </c>
+      <c r="D26" s="13">
+        <f>'2026'!I10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10">
+        <f>'2026'!F11</f>
+        <v/>
+      </c>
+      <c r="B27" s="11">
+        <f>'2026'!G11</f>
+        <v/>
+      </c>
+      <c r="C27" s="12">
+        <f>'2026'!H11</f>
+        <v/>
+      </c>
+      <c r="D27" s="13">
+        <f>'2026'!I11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10">
+        <f>'2026'!F12</f>
+        <v/>
+      </c>
+      <c r="B28" s="11">
+        <f>'2026'!G12</f>
+        <v/>
+      </c>
+      <c r="C28" s="12">
+        <f>'2026'!H12</f>
+        <v/>
+      </c>
+      <c r="D28" s="13">
+        <f>'2026'!I12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10">
+        <f>'2026'!F13</f>
+        <v/>
+      </c>
+      <c r="B29" s="11">
+        <f>'2026'!G13</f>
+        <v/>
+      </c>
+      <c r="C29" s="12">
+        <f>'2026'!H13</f>
+        <v/>
+      </c>
+      <c r="D29" s="13">
+        <f>'2026'!I13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10">
+        <f>'2026'!F14</f>
+        <v/>
+      </c>
+      <c r="B30" s="11">
+        <f>'2026'!G14</f>
+        <v/>
+      </c>
+      <c r="C30" s="12">
+        <f>'2026'!H14</f>
+        <v/>
+      </c>
+      <c r="D30" s="13">
+        <f>'2026'!I14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10">
+        <f>'2026'!F15</f>
+        <v/>
+      </c>
+      <c r="B31" s="11">
+        <f>'2026'!G15</f>
+        <v/>
+      </c>
+      <c r="C31" s="12">
+        <f>'2026'!H15</f>
+        <v/>
+      </c>
+      <c r="D31" s="13">
+        <f>'2026'!I15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10">
+        <f>'2026'!F16</f>
+        <v/>
+      </c>
+      <c r="B32" s="11">
+        <f>'2026'!G16</f>
+        <v/>
+      </c>
+      <c r="C32" s="12">
+        <f>'2026'!H16</f>
+        <v/>
+      </c>
+      <c r="D32" s="13">
+        <f>'2026'!I16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Gesamt 2026</t>
+        </is>
+      </c>
+      <c r="B33" s="17">
+        <f>'2026'!G17</f>
+        <v/>
+      </c>
+      <c r="C33" s="18">
+        <f>'2026'!H17</f>
+        <v/>
+      </c>
+      <c r="D33" s="19">
+        <f>'2026'!I17</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D3:D15">
+    <cfRule type="expression" priority="1" dxfId="4">
+      <formula>D3&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>D3&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21:D33">
+    <cfRule type="expression" priority="3" dxfId="4">
+      <formula>D21&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="5">
+      <formula>D21&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I304"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="13" customWidth="1" style="23" min="1" max="1"/>
+    <col width="12" customWidth="1" style="23" min="2" max="2"/>
+    <col width="30" customWidth="1" style="23" min="3" max="3"/>
+    <col width="14" customWidth="1" style="23" min="4" max="4"/>
+    <col width="3" customWidth="1" style="23" min="5" max="5"/>
+    <col width="20" customWidth="1" style="23" min="6" max="6"/>
+    <col width="16" customWidth="1" style="23" min="7" max="9"/>
+    <col width="8.710000000000001" customWidth="1" style="23" min="10" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -596,13 +1098,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Links jede Einnahme/Ausgabe als eigene Zeile eintragen (Ausgaben mit Minus). Rechts rechnet sich die Monatsübersicht automatisch: Differenz = Einnahmen − Ausgaben.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="23">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Datum</t>
@@ -648,12 +1146,12 @@
       <c r="A5" s="6" t="n">
         <v>45660</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Werbebudget</t>
         </is>
@@ -681,12 +1179,12 @@
       <c r="A6" s="6" t="n">
         <v>45688</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -714,8 +1212,16 @@
       <c r="A7" s="6" t="n">
         <v>45688</v>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="8" t="n"/>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Einnahme</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>BP</t>
+        </is>
+      </c>
       <c r="D7" s="9" t="n">
         <v>385.5</v>
       </c>
@@ -739,8 +1245,16 @@
       <c r="A8" s="6" t="n">
         <v>45698</v>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="8" t="n"/>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Einnahme</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>BP</t>
+        </is>
+      </c>
       <c r="D8" s="9" t="n">
         <v>139.25</v>
       </c>
@@ -764,8 +1278,16 @@
       <c r="A9" s="6" t="n">
         <v>45699</v>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="8" t="n"/>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
       <c r="D9" s="9" t="n">
         <v>-17.49</v>
       </c>
@@ -789,8 +1311,16 @@
       <c r="A10" s="6" t="n">
         <v>45699</v>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="8" t="n"/>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n">
         <v>-17.49</v>
       </c>
@@ -814,12 +1344,12 @@
       <c r="A11" s="6" t="n">
         <v>45716</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -847,8 +1377,16 @@
       <c r="A12" s="6" t="n">
         <v>45719</v>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="8" t="n"/>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Einnahme</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>BP</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="n">
         <v>552.55</v>
       </c>
@@ -872,8 +1410,16 @@
       <c r="A13" s="6" t="n">
         <v>45719</v>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="n"/>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Einnahme</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="n">
         <v>42.26</v>
       </c>
@@ -897,8 +1443,16 @@
       <c r="A14" s="6" t="n">
         <v>45720</v>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="8" t="n"/>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
       <c r="D14" s="9" t="n">
         <v>-17.49</v>
       </c>
@@ -922,12 +1476,12 @@
       <c r="A15" s="6" t="n">
         <v>45747</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -955,12 +1509,12 @@
       <c r="A16" s="6" t="n">
         <v>45748</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
@@ -988,12 +1542,12 @@
       <c r="A17" s="6" t="n">
         <v>45748</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -1001,20 +1555,20 @@
       <c r="D17" s="9" t="n">
         <v>-7.95</v>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Gesamt 2025</t>
         </is>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="17">
         <f>SUM(G5:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="18">
         <f>SUM(H5:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="19">
         <f>SUM(I5:I16)</f>
         <v/>
       </c>
@@ -1023,12 +1577,12 @@
       <c r="A18" s="6" t="n">
         <v>45757</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
@@ -1041,12 +1595,12 @@
       <c r="A19" s="6" t="n">
         <v>45763</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>MEB</t>
         </is>
@@ -1054,26 +1608,19 @@
       <c r="D19" s="9" t="n">
         <v>-300</v>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Kontrolle: Einträge außerhalb 2025</t>
-        </is>
-      </c>
-      <c r="I19" s="18">
-        <f>SUM($D$5:$D$304)-SUM(I5:I16)</f>
-        <v/>
-      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="I19" s="20" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
         <v>45777</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>MEB</t>
         </is>
@@ -1081,22 +1628,18 @@
       <c r="D20" s="9" t="n">
         <v>-300</v>
       </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>(sollte 0 sein – sonst fehlt bei einer Zeile die Art (Einnahme/Ausgabe) oder das Datum liegt in einem anderen Jahr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+      <c r="F20" s="21" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="23">
       <c r="A21" s="6" t="n">
         <v>45777</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>MEB</t>
         </is>
@@ -1105,16 +1648,16 @@
         <v>-300</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1" s="23">
       <c r="A22" s="6" t="n">
         <v>45777</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -1123,16 +1666,16 @@
         <v>-16.3</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1" s="23">
       <c r="A23" s="6" t="n">
         <v>45778</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -1141,16 +1684,16 @@
         <v>-7.95</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1" s="23">
       <c r="A24" s="6" t="n">
         <v>45797</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -1159,16 +1702,16 @@
         <v>-13.95</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1" s="23">
       <c r="A25" s="6" t="n">
         <v>45804</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>MEB</t>
         </is>
@@ -1177,16 +1720,16 @@
         <v>-150</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1" s="23">
       <c r="A26" s="6" t="n">
         <v>45805</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
@@ -1195,16 +1738,16 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1" s="23">
       <c r="A27" s="6" t="n">
         <v>45807</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>MEB</t>
         </is>
@@ -1213,16 +1756,16 @@
         <v>-750</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1" s="23">
       <c r="A28" s="6" t="n">
         <v>45807</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -1231,16 +1774,16 @@
         <v>-17.1</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1" s="23">
       <c r="A29" s="6" t="n">
         <v>45807</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>MEB</t>
         </is>
@@ -1249,16 +1792,16 @@
         <v>-300</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1" s="23">
       <c r="A30" s="6" t="n">
         <v>45809</v>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
@@ -1267,16 +1810,16 @@
         <v>359.8</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1" s="23">
       <c r="A31" s="6" t="n">
         <v>45811</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -1285,16 +1828,16 @@
         <v>-7.95</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1" s="23">
       <c r="A32" s="6" t="n">
         <v>45813</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>Powercall</t>
         </is>
@@ -1303,16 +1846,16 @@
         <v>-82.11</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1" s="23">
       <c r="A33" s="6" t="n">
         <v>45838</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -1321,16 +1864,16 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1" s="23">
       <c r="A34" s="6" t="n">
         <v>45842</v>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>Powercall</t>
         </is>
@@ -1339,16 +1882,16 @@
         <v>-82.11</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1" s="23">
       <c r="A35" s="6" t="n">
         <v>45846</v>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -1357,16 +1900,16 @@
         <v>-7.95</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1" s="23">
       <c r="A36" s="6" t="n">
         <v>45854</v>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>Jabra Headset</t>
         </is>
@@ -1375,16 +1918,16 @@
         <v>-152.81</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1" s="23">
       <c r="A37" s="6" t="n">
         <v>45869</v>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -1393,16 +1936,16 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1" s="23">
       <c r="A38" s="6" t="n">
         <v>45870</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
@@ -1411,16 +1954,16 @@
         <v>500</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1" s="23">
       <c r="A39" s="6" t="n">
         <v>45873</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -1429,16 +1972,16 @@
         <v>-7.95</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1" s="23">
       <c r="A40" s="6" t="n">
         <v>45874</v>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>Powercall</t>
         </is>
@@ -1447,16 +1990,16 @@
         <v>-82.11</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1" s="23">
       <c r="A41" s="6" t="n">
         <v>45874</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
@@ -1465,16 +2008,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1" s="23">
       <c r="A42" s="6" t="n">
         <v>45898</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -1483,16 +2026,16 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1" s="23">
       <c r="A43" s="6" t="n">
         <v>45901</v>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -1501,16 +2044,16 @@
         <v>-7.95</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1" s="23">
       <c r="A44" s="6" t="n">
         <v>45904</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>Powercall</t>
         </is>
@@ -1519,16 +2062,16 @@
         <v>-82.11</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1" s="23">
       <c r="A45" s="6" t="n">
         <v>45930</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -1537,16 +2080,16 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1" s="23">
       <c r="A46" s="6" t="n">
         <v>45937</v>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -1555,16 +2098,16 @@
         <v>-7.95</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1" s="23">
       <c r="A47" s="6" t="n">
         <v>45946</v>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
@@ -1573,16 +2116,16 @@
         <v>60</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1" s="23">
       <c r="A48" s="6" t="n">
         <v>45958</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -1591,16 +2134,16 @@
         <v>-10.95</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1" s="23">
       <c r="A49" s="6" t="n">
         <v>45961</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -1609,16 +2152,16 @@
         <v>-16.1</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1" s="23">
       <c r="A50" s="6" t="n">
         <v>45962</v>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -1627,16 +2170,16 @@
         <v>134.46</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1" s="23">
       <c r="A51" s="6" t="n">
         <v>45989</v>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -1645,16 +2188,16 @@
         <v>-7.5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1" s="23">
       <c r="A52" s="6" t="n">
         <v>45989</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -1663,16 +2206,16 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1" s="23">
       <c r="A53" s="6" t="n">
         <v>45992</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="15" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -1681,16 +2224,16 @@
         <v>564.64</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1" s="23">
       <c r="A54" s="6" t="n">
         <v>46022</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
         <is>
           <t>Kontoführung</t>
         </is>
@@ -1699,1508 +2242,2104 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1" s="23">
       <c r="A55" s="6" t="n"/>
-      <c r="B55" s="7" t="n"/>
-      <c r="C55" s="8" t="n"/>
+      <c r="B55" s="14" t="n"/>
+      <c r="C55" s="15" t="n"/>
       <c r="D55" s="9" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1" s="23">
       <c r="A56" s="6" t="n"/>
-      <c r="B56" s="7" t="n"/>
-      <c r="C56" s="8" t="n"/>
+      <c r="B56" s="14" t="n"/>
+      <c r="C56" s="15" t="n"/>
       <c r="D56" s="9" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1" s="23">
       <c r="A57" s="6" t="n"/>
-      <c r="B57" s="7" t="n"/>
-      <c r="C57" s="8" t="n"/>
+      <c r="B57" s="14" t="n"/>
+      <c r="C57" s="15" t="n"/>
       <c r="D57" s="9" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1" s="23">
       <c r="A58" s="6" t="n"/>
-      <c r="B58" s="7" t="n"/>
-      <c r="C58" s="8" t="n"/>
+      <c r="B58" s="14" t="n"/>
+      <c r="C58" s="15" t="n"/>
       <c r="D58" s="9" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1" s="23">
       <c r="A59" s="6" t="n"/>
-      <c r="B59" s="7" t="n"/>
-      <c r="C59" s="8" t="n"/>
+      <c r="B59" s="14" t="n"/>
+      <c r="C59" s="15" t="n"/>
       <c r="D59" s="9" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1" s="23">
       <c r="A60" s="6" t="n"/>
-      <c r="B60" s="7" t="n"/>
-      <c r="C60" s="8" t="n"/>
+      <c r="B60" s="14" t="n"/>
+      <c r="C60" s="15" t="n"/>
       <c r="D60" s="9" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1" s="23">
       <c r="A61" s="6" t="n"/>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="8" t="n"/>
+      <c r="B61" s="14" t="n"/>
+      <c r="C61" s="15" t="n"/>
       <c r="D61" s="9" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1" s="23">
       <c r="A62" s="6" t="n"/>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="8" t="n"/>
+      <c r="B62" s="14" t="n"/>
+      <c r="C62" s="15" t="n"/>
       <c r="D62" s="9" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1" s="23">
       <c r="A63" s="6" t="n"/>
-      <c r="B63" s="7" t="n"/>
-      <c r="C63" s="8" t="n"/>
+      <c r="B63" s="14" t="n"/>
+      <c r="C63" s="15" t="n"/>
       <c r="D63" s="9" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1" s="23">
       <c r="A64" s="6" t="n"/>
-      <c r="B64" s="7" t="n"/>
-      <c r="C64" s="8" t="n"/>
+      <c r="B64" s="14" t="n"/>
+      <c r="C64" s="15" t="n"/>
       <c r="D64" s="9" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1" s="23">
       <c r="A65" s="6" t="n"/>
-      <c r="B65" s="7" t="n"/>
-      <c r="C65" s="8" t="n"/>
+      <c r="B65" s="14" t="n"/>
+      <c r="C65" s="15" t="n"/>
       <c r="D65" s="9" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1" s="23">
       <c r="A66" s="6" t="n"/>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="8" t="n"/>
+      <c r="B66" s="14" t="n"/>
+      <c r="C66" s="15" t="n"/>
       <c r="D66" s="9" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1" s="23">
       <c r="A67" s="6" t="n"/>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="8" t="n"/>
+      <c r="B67" s="14" t="n"/>
+      <c r="C67" s="15" t="n"/>
       <c r="D67" s="9" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1" s="23">
       <c r="A68" s="6" t="n"/>
-      <c r="B68" s="7" t="n"/>
-      <c r="C68" s="8" t="n"/>
+      <c r="B68" s="14" t="n"/>
+      <c r="C68" s="15" t="n"/>
       <c r="D68" s="9" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1" s="23">
       <c r="A69" s="6" t="n"/>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="8" t="n"/>
+      <c r="B69" s="14" t="n"/>
+      <c r="C69" s="15" t="n"/>
       <c r="D69" s="9" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1" s="23">
       <c r="A70" s="6" t="n"/>
-      <c r="B70" s="7" t="n"/>
-      <c r="C70" s="8" t="n"/>
+      <c r="B70" s="14" t="n"/>
+      <c r="C70" s="15" t="n"/>
       <c r="D70" s="9" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1" s="23">
       <c r="A71" s="6" t="n"/>
-      <c r="B71" s="7" t="n"/>
-      <c r="C71" s="8" t="n"/>
+      <c r="B71" s="14" t="n"/>
+      <c r="C71" s="15" t="n"/>
       <c r="D71" s="9" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1" s="23">
       <c r="A72" s="6" t="n"/>
-      <c r="B72" s="7" t="n"/>
-      <c r="C72" s="8" t="n"/>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="15" t="n"/>
       <c r="D72" s="9" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1" s="23">
       <c r="A73" s="6" t="n"/>
-      <c r="B73" s="7" t="n"/>
-      <c r="C73" s="8" t="n"/>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="D73" s="9" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1" s="23">
       <c r="A74" s="6" t="n"/>
-      <c r="B74" s="7" t="n"/>
-      <c r="C74" s="8" t="n"/>
+      <c r="B74" s="14" t="n"/>
+      <c r="C74" s="15" t="n"/>
       <c r="D74" s="9" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1" s="23">
       <c r="A75" s="6" t="n"/>
-      <c r="B75" s="7" t="n"/>
-      <c r="C75" s="8" t="n"/>
+      <c r="B75" s="14" t="n"/>
+      <c r="C75" s="15" t="n"/>
       <c r="D75" s="9" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1" s="23">
       <c r="A76" s="6" t="n"/>
-      <c r="B76" s="7" t="n"/>
-      <c r="C76" s="8" t="n"/>
+      <c r="B76" s="14" t="n"/>
+      <c r="C76" s="15" t="n"/>
       <c r="D76" s="9" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1" s="23">
       <c r="A77" s="6" t="n"/>
-      <c r="B77" s="7" t="n"/>
-      <c r="C77" s="8" t="n"/>
+      <c r="B77" s="14" t="n"/>
+      <c r="C77" s="15" t="n"/>
       <c r="D77" s="9" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1" s="23">
       <c r="A78" s="6" t="n"/>
-      <c r="B78" s="7" t="n"/>
-      <c r="C78" s="8" t="n"/>
+      <c r="B78" s="14" t="n"/>
+      <c r="C78" s="15" t="n"/>
       <c r="D78" s="9" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1" s="23">
       <c r="A79" s="6" t="n"/>
-      <c r="B79" s="7" t="n"/>
-      <c r="C79" s="8" t="n"/>
+      <c r="B79" s="14" t="n"/>
+      <c r="C79" s="15" t="n"/>
       <c r="D79" s="9" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1" s="23">
       <c r="A80" s="6" t="n"/>
-      <c r="B80" s="7" t="n"/>
-      <c r="C80" s="8" t="n"/>
+      <c r="B80" s="14" t="n"/>
+      <c r="C80" s="15" t="n"/>
       <c r="D80" s="9" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1" s="23">
       <c r="A81" s="6" t="n"/>
-      <c r="B81" s="7" t="n"/>
-      <c r="C81" s="8" t="n"/>
+      <c r="B81" s="14" t="n"/>
+      <c r="C81" s="15" t="n"/>
       <c r="D81" s="9" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1" s="23">
       <c r="A82" s="6" t="n"/>
-      <c r="B82" s="7" t="n"/>
-      <c r="C82" s="8" t="n"/>
+      <c r="B82" s="14" t="n"/>
+      <c r="C82" s="15" t="n"/>
       <c r="D82" s="9" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1" s="23">
       <c r="A83" s="6" t="n"/>
-      <c r="B83" s="7" t="n"/>
-      <c r="C83" s="8" t="n"/>
+      <c r="B83" s="14" t="n"/>
+      <c r="C83" s="15" t="n"/>
       <c r="D83" s="9" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1" s="23">
       <c r="A84" s="6" t="n"/>
-      <c r="B84" s="7" t="n"/>
-      <c r="C84" s="8" t="n"/>
+      <c r="B84" s="14" t="n"/>
+      <c r="C84" s="15" t="n"/>
       <c r="D84" s="9" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1" s="23">
       <c r="A85" s="6" t="n"/>
-      <c r="B85" s="7" t="n"/>
-      <c r="C85" s="8" t="n"/>
+      <c r="B85" s="14" t="n"/>
+      <c r="C85" s="15" t="n"/>
       <c r="D85" s="9" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1" s="23">
       <c r="A86" s="6" t="n"/>
-      <c r="B86" s="7" t="n"/>
-      <c r="C86" s="8" t="n"/>
+      <c r="B86" s="14" t="n"/>
+      <c r="C86" s="15" t="n"/>
       <c r="D86" s="9" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1" s="23">
       <c r="A87" s="6" t="n"/>
-      <c r="B87" s="7" t="n"/>
-      <c r="C87" s="8" t="n"/>
+      <c r="B87" s="14" t="n"/>
+      <c r="C87" s="15" t="n"/>
       <c r="D87" s="9" t="n"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1" s="23">
       <c r="A88" s="6" t="n"/>
-      <c r="B88" s="7" t="n"/>
-      <c r="C88" s="8" t="n"/>
+      <c r="B88" s="14" t="n"/>
+      <c r="C88" s="15" t="n"/>
       <c r="D88" s="9" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1" s="23">
       <c r="A89" s="6" t="n"/>
-      <c r="B89" s="7" t="n"/>
-      <c r="C89" s="8" t="n"/>
+      <c r="B89" s="14" t="n"/>
+      <c r="C89" s="15" t="n"/>
       <c r="D89" s="9" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1" s="23">
       <c r="A90" s="6" t="n"/>
-      <c r="B90" s="7" t="n"/>
-      <c r="C90" s="8" t="n"/>
+      <c r="B90" s="14" t="n"/>
+      <c r="C90" s="15" t="n"/>
       <c r="D90" s="9" t="n"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1" s="23">
       <c r="A91" s="6" t="n"/>
-      <c r="B91" s="7" t="n"/>
-      <c r="C91" s="8" t="n"/>
+      <c r="B91" s="14" t="n"/>
+      <c r="C91" s="15" t="n"/>
       <c r="D91" s="9" t="n"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1" s="23">
       <c r="A92" s="6" t="n"/>
-      <c r="B92" s="7" t="n"/>
-      <c r="C92" s="8" t="n"/>
+      <c r="B92" s="14" t="n"/>
+      <c r="C92" s="15" t="n"/>
       <c r="D92" s="9" t="n"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1" s="23">
       <c r="A93" s="6" t="n"/>
-      <c r="B93" s="7" t="n"/>
-      <c r="C93" s="8" t="n"/>
+      <c r="B93" s="14" t="n"/>
+      <c r="C93" s="15" t="n"/>
       <c r="D93" s="9" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1" s="23">
       <c r="A94" s="6" t="n"/>
-      <c r="B94" s="7" t="n"/>
-      <c r="C94" s="8" t="n"/>
+      <c r="B94" s="14" t="n"/>
+      <c r="C94" s="15" t="n"/>
       <c r="D94" s="9" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1" s="23">
       <c r="A95" s="6" t="n"/>
-      <c r="B95" s="7" t="n"/>
-      <c r="C95" s="8" t="n"/>
+      <c r="B95" s="14" t="n"/>
+      <c r="C95" s="15" t="n"/>
       <c r="D95" s="9" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1" s="23">
       <c r="A96" s="6" t="n"/>
-      <c r="B96" s="7" t="n"/>
-      <c r="C96" s="8" t="n"/>
+      <c r="B96" s="14" t="n"/>
+      <c r="C96" s="15" t="n"/>
       <c r="D96" s="9" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1" s="23">
       <c r="A97" s="6" t="n"/>
-      <c r="B97" s="7" t="n"/>
-      <c r="C97" s="8" t="n"/>
+      <c r="B97" s="14" t="n"/>
+      <c r="C97" s="15" t="n"/>
       <c r="D97" s="9" t="n"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1" s="23">
       <c r="A98" s="6" t="n"/>
-      <c r="B98" s="7" t="n"/>
-      <c r="C98" s="8" t="n"/>
+      <c r="B98" s="14" t="n"/>
+      <c r="C98" s="15" t="n"/>
       <c r="D98" s="9" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1" s="23">
       <c r="A99" s="6" t="n"/>
-      <c r="B99" s="7" t="n"/>
-      <c r="C99" s="8" t="n"/>
+      <c r="B99" s="14" t="n"/>
+      <c r="C99" s="15" t="n"/>
       <c r="D99" s="9" t="n"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1" s="23">
       <c r="A100" s="6" t="n"/>
-      <c r="B100" s="7" t="n"/>
-      <c r="C100" s="8" t="n"/>
+      <c r="B100" s="14" t="n"/>
+      <c r="C100" s="15" t="n"/>
       <c r="D100" s="9" t="n"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1" s="23">
       <c r="A101" s="6" t="n"/>
-      <c r="B101" s="7" t="n"/>
-      <c r="C101" s="8" t="n"/>
+      <c r="B101" s="14" t="n"/>
+      <c r="C101" s="15" t="n"/>
       <c r="D101" s="9" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1" s="23">
       <c r="A102" s="6" t="n"/>
-      <c r="B102" s="7" t="n"/>
-      <c r="C102" s="8" t="n"/>
+      <c r="B102" s="14" t="n"/>
+      <c r="C102" s="15" t="n"/>
       <c r="D102" s="9" t="n"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1" s="23">
       <c r="A103" s="6" t="n"/>
-      <c r="B103" s="7" t="n"/>
-      <c r="C103" s="8" t="n"/>
+      <c r="B103" s="14" t="n"/>
+      <c r="C103" s="15" t="n"/>
       <c r="D103" s="9" t="n"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1" s="23">
       <c r="A104" s="6" t="n"/>
-      <c r="B104" s="7" t="n"/>
-      <c r="C104" s="8" t="n"/>
+      <c r="B104" s="14" t="n"/>
+      <c r="C104" s="15" t="n"/>
       <c r="D104" s="9" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1" s="23">
       <c r="A105" s="6" t="n"/>
-      <c r="B105" s="7" t="n"/>
-      <c r="C105" s="8" t="n"/>
+      <c r="B105" s="14" t="n"/>
+      <c r="C105" s="15" t="n"/>
       <c r="D105" s="9" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1" s="23">
       <c r="A106" s="6" t="n"/>
-      <c r="B106" s="7" t="n"/>
-      <c r="C106" s="8" t="n"/>
+      <c r="B106" s="14" t="n"/>
+      <c r="C106" s="15" t="n"/>
       <c r="D106" s="9" t="n"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1" s="23">
       <c r="A107" s="6" t="n"/>
-      <c r="B107" s="7" t="n"/>
-      <c r="C107" s="8" t="n"/>
+      <c r="B107" s="14" t="n"/>
+      <c r="C107" s="15" t="n"/>
       <c r="D107" s="9" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1" s="23">
       <c r="A108" s="6" t="n"/>
-      <c r="B108" s="7" t="n"/>
-      <c r="C108" s="8" t="n"/>
+      <c r="B108" s="14" t="n"/>
+      <c r="C108" s="15" t="n"/>
       <c r="D108" s="9" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1" s="23">
       <c r="A109" s="6" t="n"/>
-      <c r="B109" s="7" t="n"/>
-      <c r="C109" s="8" t="n"/>
+      <c r="B109" s="14" t="n"/>
+      <c r="C109" s="15" t="n"/>
       <c r="D109" s="9" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1" s="23">
       <c r="A110" s="6" t="n"/>
-      <c r="B110" s="7" t="n"/>
-      <c r="C110" s="8" t="n"/>
+      <c r="B110" s="14" t="n"/>
+      <c r="C110" s="15" t="n"/>
       <c r="D110" s="9" t="n"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1" s="23">
       <c r="A111" s="6" t="n"/>
-      <c r="B111" s="7" t="n"/>
-      <c r="C111" s="8" t="n"/>
+      <c r="B111" s="14" t="n"/>
+      <c r="C111" s="15" t="n"/>
       <c r="D111" s="9" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1" s="23">
       <c r="A112" s="6" t="n"/>
-      <c r="B112" s="7" t="n"/>
-      <c r="C112" s="8" t="n"/>
+      <c r="B112" s="14" t="n"/>
+      <c r="C112" s="15" t="n"/>
       <c r="D112" s="9" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1" s="23">
       <c r="A113" s="6" t="n"/>
-      <c r="B113" s="7" t="n"/>
-      <c r="C113" s="8" t="n"/>
+      <c r="B113" s="14" t="n"/>
+      <c r="C113" s="15" t="n"/>
       <c r="D113" s="9" t="n"/>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1" s="23">
       <c r="A114" s="6" t="n"/>
-      <c r="B114" s="7" t="n"/>
-      <c r="C114" s="8" t="n"/>
+      <c r="B114" s="14" t="n"/>
+      <c r="C114" s="15" t="n"/>
       <c r="D114" s="9" t="n"/>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1" s="23">
       <c r="A115" s="6" t="n"/>
-      <c r="B115" s="7" t="n"/>
-      <c r="C115" s="8" t="n"/>
+      <c r="B115" s="14" t="n"/>
+      <c r="C115" s="15" t="n"/>
       <c r="D115" s="9" t="n"/>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1" s="23">
       <c r="A116" s="6" t="n"/>
-      <c r="B116" s="7" t="n"/>
-      <c r="C116" s="8" t="n"/>
+      <c r="B116" s="14" t="n"/>
+      <c r="C116" s="15" t="n"/>
       <c r="D116" s="9" t="n"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1" s="23">
       <c r="A117" s="6" t="n"/>
-      <c r="B117" s="7" t="n"/>
-      <c r="C117" s="8" t="n"/>
+      <c r="B117" s="14" t="n"/>
+      <c r="C117" s="15" t="n"/>
       <c r="D117" s="9" t="n"/>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1" s="23">
       <c r="A118" s="6" t="n"/>
-      <c r="B118" s="7" t="n"/>
-      <c r="C118" s="8" t="n"/>
+      <c r="B118" s="14" t="n"/>
+      <c r="C118" s="15" t="n"/>
       <c r="D118" s="9" t="n"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1" s="23">
       <c r="A119" s="6" t="n"/>
-      <c r="B119" s="7" t="n"/>
-      <c r="C119" s="8" t="n"/>
+      <c r="B119" s="14" t="n"/>
+      <c r="C119" s="15" t="n"/>
       <c r="D119" s="9" t="n"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1" s="23">
       <c r="A120" s="6" t="n"/>
-      <c r="B120" s="7" t="n"/>
-      <c r="C120" s="8" t="n"/>
+      <c r="B120" s="14" t="n"/>
+      <c r="C120" s="15" t="n"/>
       <c r="D120" s="9" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1" s="23">
       <c r="A121" s="6" t="n"/>
-      <c r="B121" s="7" t="n"/>
-      <c r="C121" s="8" t="n"/>
+      <c r="B121" s="14" t="n"/>
+      <c r="C121" s="15" t="n"/>
       <c r="D121" s="9" t="n"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1" s="23">
       <c r="A122" s="6" t="n"/>
-      <c r="B122" s="7" t="n"/>
-      <c r="C122" s="8" t="n"/>
+      <c r="B122" s="14" t="n"/>
+      <c r="C122" s="15" t="n"/>
       <c r="D122" s="9" t="n"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1" s="23">
       <c r="A123" s="6" t="n"/>
-      <c r="B123" s="7" t="n"/>
-      <c r="C123" s="8" t="n"/>
+      <c r="B123" s="14" t="n"/>
+      <c r="C123" s="15" t="n"/>
       <c r="D123" s="9" t="n"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1" s="23">
       <c r="A124" s="6" t="n"/>
-      <c r="B124" s="7" t="n"/>
-      <c r="C124" s="8" t="n"/>
+      <c r="B124" s="14" t="n"/>
+      <c r="C124" s="15" t="n"/>
       <c r="D124" s="9" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1" s="23">
       <c r="A125" s="6" t="n"/>
-      <c r="B125" s="7" t="n"/>
-      <c r="C125" s="8" t="n"/>
+      <c r="B125" s="14" t="n"/>
+      <c r="C125" s="15" t="n"/>
       <c r="D125" s="9" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1" s="23">
       <c r="A126" s="6" t="n"/>
-      <c r="B126" s="7" t="n"/>
-      <c r="C126" s="8" t="n"/>
+      <c r="B126" s="14" t="n"/>
+      <c r="C126" s="15" t="n"/>
       <c r="D126" s="9" t="n"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1" s="23">
       <c r="A127" s="6" t="n"/>
-      <c r="B127" s="7" t="n"/>
-      <c r="C127" s="8" t="n"/>
+      <c r="B127" s="14" t="n"/>
+      <c r="C127" s="15" t="n"/>
       <c r="D127" s="9" t="n"/>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1" s="23">
       <c r="A128" s="6" t="n"/>
-      <c r="B128" s="7" t="n"/>
-      <c r="C128" s="8" t="n"/>
+      <c r="B128" s="14" t="n"/>
+      <c r="C128" s="15" t="n"/>
       <c r="D128" s="9" t="n"/>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1" s="23">
       <c r="A129" s="6" t="n"/>
-      <c r="B129" s="7" t="n"/>
-      <c r="C129" s="8" t="n"/>
+      <c r="B129" s="14" t="n"/>
+      <c r="C129" s="15" t="n"/>
       <c r="D129" s="9" t="n"/>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1" s="23">
       <c r="A130" s="6" t="n"/>
-      <c r="B130" s="7" t="n"/>
-      <c r="C130" s="8" t="n"/>
+      <c r="B130" s="14" t="n"/>
+      <c r="C130" s="15" t="n"/>
       <c r="D130" s="9" t="n"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1" s="23">
       <c r="A131" s="6" t="n"/>
-      <c r="B131" s="7" t="n"/>
-      <c r="C131" s="8" t="n"/>
+      <c r="B131" s="14" t="n"/>
+      <c r="C131" s="15" t="n"/>
       <c r="D131" s="9" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1" s="23">
       <c r="A132" s="6" t="n"/>
-      <c r="B132" s="7" t="n"/>
-      <c r="C132" s="8" t="n"/>
+      <c r="B132" s="14" t="n"/>
+      <c r="C132" s="15" t="n"/>
       <c r="D132" s="9" t="n"/>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1" s="23">
       <c r="A133" s="6" t="n"/>
-      <c r="B133" s="7" t="n"/>
-      <c r="C133" s="8" t="n"/>
+      <c r="B133" s="14" t="n"/>
+      <c r="C133" s="15" t="n"/>
       <c r="D133" s="9" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1" s="23">
       <c r="A134" s="6" t="n"/>
-      <c r="B134" s="7" t="n"/>
-      <c r="C134" s="8" t="n"/>
+      <c r="B134" s="14" t="n"/>
+      <c r="C134" s="15" t="n"/>
       <c r="D134" s="9" t="n"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1" s="23">
       <c r="A135" s="6" t="n"/>
-      <c r="B135" s="7" t="n"/>
-      <c r="C135" s="8" t="n"/>
+      <c r="B135" s="14" t="n"/>
+      <c r="C135" s="15" t="n"/>
       <c r="D135" s="9" t="n"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1" s="23">
       <c r="A136" s="6" t="n"/>
-      <c r="B136" s="7" t="n"/>
-      <c r="C136" s="8" t="n"/>
+      <c r="B136" s="14" t="n"/>
+      <c r="C136" s="15" t="n"/>
       <c r="D136" s="9" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1" s="23">
       <c r="A137" s="6" t="n"/>
-      <c r="B137" s="7" t="n"/>
-      <c r="C137" s="8" t="n"/>
+      <c r="B137" s="14" t="n"/>
+      <c r="C137" s="15" t="n"/>
       <c r="D137" s="9" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1" s="23">
       <c r="A138" s="6" t="n"/>
-      <c r="B138" s="7" t="n"/>
-      <c r="C138" s="8" t="n"/>
+      <c r="B138" s="14" t="n"/>
+      <c r="C138" s="15" t="n"/>
       <c r="D138" s="9" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1" s="23">
       <c r="A139" s="6" t="n"/>
-      <c r="B139" s="7" t="n"/>
-      <c r="C139" s="8" t="n"/>
+      <c r="B139" s="14" t="n"/>
+      <c r="C139" s="15" t="n"/>
       <c r="D139" s="9" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1" s="23">
       <c r="A140" s="6" t="n"/>
-      <c r="B140" s="7" t="n"/>
-      <c r="C140" s="8" t="n"/>
+      <c r="B140" s="14" t="n"/>
+      <c r="C140" s="15" t="n"/>
       <c r="D140" s="9" t="n"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1" s="23">
       <c r="A141" s="6" t="n"/>
-      <c r="B141" s="7" t="n"/>
-      <c r="C141" s="8" t="n"/>
+      <c r="B141" s="14" t="n"/>
+      <c r="C141" s="15" t="n"/>
       <c r="D141" s="9" t="n"/>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1" s="23">
       <c r="A142" s="6" t="n"/>
-      <c r="B142" s="7" t="n"/>
-      <c r="C142" s="8" t="n"/>
+      <c r="B142" s="14" t="n"/>
+      <c r="C142" s="15" t="n"/>
       <c r="D142" s="9" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1" s="23">
       <c r="A143" s="6" t="n"/>
-      <c r="B143" s="7" t="n"/>
-      <c r="C143" s="8" t="n"/>
+      <c r="B143" s="14" t="n"/>
+      <c r="C143" s="15" t="n"/>
       <c r="D143" s="9" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1" s="23">
       <c r="A144" s="6" t="n"/>
-      <c r="B144" s="7" t="n"/>
-      <c r="C144" s="8" t="n"/>
+      <c r="B144" s="14" t="n"/>
+      <c r="C144" s="15" t="n"/>
       <c r="D144" s="9" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1" s="23">
       <c r="A145" s="6" t="n"/>
-      <c r="B145" s="7" t="n"/>
-      <c r="C145" s="8" t="n"/>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="15" t="n"/>
       <c r="D145" s="9" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1" s="23">
       <c r="A146" s="6" t="n"/>
-      <c r="B146" s="7" t="n"/>
-      <c r="C146" s="8" t="n"/>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="15" t="n"/>
       <c r="D146" s="9" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1" s="23">
       <c r="A147" s="6" t="n"/>
-      <c r="B147" s="7" t="n"/>
-      <c r="C147" s="8" t="n"/>
+      <c r="B147" s="14" t="n"/>
+      <c r="C147" s="15" t="n"/>
       <c r="D147" s="9" t="n"/>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1" s="23">
       <c r="A148" s="6" t="n"/>
-      <c r="B148" s="7" t="n"/>
-      <c r="C148" s="8" t="n"/>
+      <c r="B148" s="14" t="n"/>
+      <c r="C148" s="15" t="n"/>
       <c r="D148" s="9" t="n"/>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1" s="23">
       <c r="A149" s="6" t="n"/>
-      <c r="B149" s="7" t="n"/>
-      <c r="C149" s="8" t="n"/>
+      <c r="B149" s="14" t="n"/>
+      <c r="C149" s="15" t="n"/>
       <c r="D149" s="9" t="n"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1" s="23">
       <c r="A150" s="6" t="n"/>
-      <c r="B150" s="7" t="n"/>
-      <c r="C150" s="8" t="n"/>
+      <c r="B150" s="14" t="n"/>
+      <c r="C150" s="15" t="n"/>
       <c r="D150" s="9" t="n"/>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1" s="23">
       <c r="A151" s="6" t="n"/>
-      <c r="B151" s="7" t="n"/>
-      <c r="C151" s="8" t="n"/>
+      <c r="B151" s="14" t="n"/>
+      <c r="C151" s="15" t="n"/>
       <c r="D151" s="9" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1" s="23">
       <c r="A152" s="6" t="n"/>
-      <c r="B152" s="7" t="n"/>
-      <c r="C152" s="8" t="n"/>
+      <c r="B152" s="14" t="n"/>
+      <c r="C152" s="15" t="n"/>
       <c r="D152" s="9" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1" s="23">
       <c r="A153" s="6" t="n"/>
-      <c r="B153" s="7" t="n"/>
-      <c r="C153" s="8" t="n"/>
+      <c r="B153" s="14" t="n"/>
+      <c r="C153" s="15" t="n"/>
       <c r="D153" s="9" t="n"/>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1" s="23">
       <c r="A154" s="6" t="n"/>
-      <c r="B154" s="7" t="n"/>
-      <c r="C154" s="8" t="n"/>
+      <c r="B154" s="14" t="n"/>
+      <c r="C154" s="15" t="n"/>
       <c r="D154" s="9" t="n"/>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1" s="23">
       <c r="A155" s="6" t="n"/>
-      <c r="B155" s="7" t="n"/>
-      <c r="C155" s="8" t="n"/>
+      <c r="B155" s="14" t="n"/>
+      <c r="C155" s="15" t="n"/>
       <c r="D155" s="9" t="n"/>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1" s="23">
       <c r="A156" s="6" t="n"/>
-      <c r="B156" s="7" t="n"/>
-      <c r="C156" s="8" t="n"/>
+      <c r="B156" s="14" t="n"/>
+      <c r="C156" s="15" t="n"/>
       <c r="D156" s="9" t="n"/>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1" s="23">
       <c r="A157" s="6" t="n"/>
-      <c r="B157" s="7" t="n"/>
-      <c r="C157" s="8" t="n"/>
+      <c r="B157" s="14" t="n"/>
+      <c r="C157" s="15" t="n"/>
       <c r="D157" s="9" t="n"/>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1" s="23">
       <c r="A158" s="6" t="n"/>
-      <c r="B158" s="7" t="n"/>
-      <c r="C158" s="8" t="n"/>
+      <c r="B158" s="14" t="n"/>
+      <c r="C158" s="15" t="n"/>
       <c r="D158" s="9" t="n"/>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1" s="23">
       <c r="A159" s="6" t="n"/>
-      <c r="B159" s="7" t="n"/>
-      <c r="C159" s="8" t="n"/>
+      <c r="B159" s="14" t="n"/>
+      <c r="C159" s="15" t="n"/>
       <c r="D159" s="9" t="n"/>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1" s="23">
       <c r="A160" s="6" t="n"/>
-      <c r="B160" s="7" t="n"/>
-      <c r="C160" s="8" t="n"/>
+      <c r="B160" s="14" t="n"/>
+      <c r="C160" s="15" t="n"/>
       <c r="D160" s="9" t="n"/>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1" s="23">
       <c r="A161" s="6" t="n"/>
-      <c r="B161" s="7" t="n"/>
-      <c r="C161" s="8" t="n"/>
+      <c r="B161" s="14" t="n"/>
+      <c r="C161" s="15" t="n"/>
       <c r="D161" s="9" t="n"/>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1" s="23">
       <c r="A162" s="6" t="n"/>
-      <c r="B162" s="7" t="n"/>
-      <c r="C162" s="8" t="n"/>
+      <c r="B162" s="14" t="n"/>
+      <c r="C162" s="15" t="n"/>
       <c r="D162" s="9" t="n"/>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1" s="23">
       <c r="A163" s="6" t="n"/>
-      <c r="B163" s="7" t="n"/>
-      <c r="C163" s="8" t="n"/>
+      <c r="B163" s="14" t="n"/>
+      <c r="C163" s="15" t="n"/>
       <c r="D163" s="9" t="n"/>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1" s="23">
       <c r="A164" s="6" t="n"/>
-      <c r="B164" s="7" t="n"/>
-      <c r="C164" s="8" t="n"/>
+      <c r="B164" s="14" t="n"/>
+      <c r="C164" s="15" t="n"/>
       <c r="D164" s="9" t="n"/>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1" s="23">
       <c r="A165" s="6" t="n"/>
-      <c r="B165" s="7" t="n"/>
-      <c r="C165" s="8" t="n"/>
+      <c r="B165" s="14" t="n"/>
+      <c r="C165" s="15" t="n"/>
       <c r="D165" s="9" t="n"/>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1" s="23">
       <c r="A166" s="6" t="n"/>
-      <c r="B166" s="7" t="n"/>
-      <c r="C166" s="8" t="n"/>
+      <c r="B166" s="14" t="n"/>
+      <c r="C166" s="15" t="n"/>
       <c r="D166" s="9" t="n"/>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1" s="23">
       <c r="A167" s="6" t="n"/>
-      <c r="B167" s="7" t="n"/>
-      <c r="C167" s="8" t="n"/>
+      <c r="B167" s="14" t="n"/>
+      <c r="C167" s="15" t="n"/>
       <c r="D167" s="9" t="n"/>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1" s="23">
       <c r="A168" s="6" t="n"/>
-      <c r="B168" s="7" t="n"/>
-      <c r="C168" s="8" t="n"/>
+      <c r="B168" s="14" t="n"/>
+      <c r="C168" s="15" t="n"/>
       <c r="D168" s="9" t="n"/>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1" s="23">
       <c r="A169" s="6" t="n"/>
-      <c r="B169" s="7" t="n"/>
-      <c r="C169" s="8" t="n"/>
+      <c r="B169" s="14" t="n"/>
+      <c r="C169" s="15" t="n"/>
       <c r="D169" s="9" t="n"/>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1" s="23">
       <c r="A170" s="6" t="n"/>
-      <c r="B170" s="7" t="n"/>
-      <c r="C170" s="8" t="n"/>
+      <c r="B170" s="14" t="n"/>
+      <c r="C170" s="15" t="n"/>
       <c r="D170" s="9" t="n"/>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1" s="23">
       <c r="A171" s="6" t="n"/>
-      <c r="B171" s="7" t="n"/>
-      <c r="C171" s="8" t="n"/>
+      <c r="B171" s="14" t="n"/>
+      <c r="C171" s="15" t="n"/>
       <c r="D171" s="9" t="n"/>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1" s="23">
       <c r="A172" s="6" t="n"/>
-      <c r="B172" s="7" t="n"/>
-      <c r="C172" s="8" t="n"/>
+      <c r="B172" s="14" t="n"/>
+      <c r="C172" s="15" t="n"/>
       <c r="D172" s="9" t="n"/>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1" s="23">
       <c r="A173" s="6" t="n"/>
-      <c r="B173" s="7" t="n"/>
-      <c r="C173" s="8" t="n"/>
+      <c r="B173" s="14" t="n"/>
+      <c r="C173" s="15" t="n"/>
       <c r="D173" s="9" t="n"/>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1" s="23">
       <c r="A174" s="6" t="n"/>
-      <c r="B174" s="7" t="n"/>
-      <c r="C174" s="8" t="n"/>
+      <c r="B174" s="14" t="n"/>
+      <c r="C174" s="15" t="n"/>
       <c r="D174" s="9" t="n"/>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1" s="23">
       <c r="A175" s="6" t="n"/>
-      <c r="B175" s="7" t="n"/>
-      <c r="C175" s="8" t="n"/>
+      <c r="B175" s="14" t="n"/>
+      <c r="C175" s="15" t="n"/>
       <c r="D175" s="9" t="n"/>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1" s="23">
       <c r="A176" s="6" t="n"/>
-      <c r="B176" s="7" t="n"/>
-      <c r="C176" s="8" t="n"/>
+      <c r="B176" s="14" t="n"/>
+      <c r="C176" s="15" t="n"/>
       <c r="D176" s="9" t="n"/>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1" s="23">
       <c r="A177" s="6" t="n"/>
-      <c r="B177" s="7" t="n"/>
-      <c r="C177" s="8" t="n"/>
+      <c r="B177" s="14" t="n"/>
+      <c r="C177" s="15" t="n"/>
       <c r="D177" s="9" t="n"/>
     </row>
-    <row r="178">
+    <row r="178" ht="15.75" customHeight="1" s="23">
       <c r="A178" s="6" t="n"/>
-      <c r="B178" s="7" t="n"/>
-      <c r="C178" s="8" t="n"/>
+      <c r="B178" s="14" t="n"/>
+      <c r="C178" s="15" t="n"/>
       <c r="D178" s="9" t="n"/>
     </row>
-    <row r="179">
+    <row r="179" ht="15.75" customHeight="1" s="23">
       <c r="A179" s="6" t="n"/>
-      <c r="B179" s="7" t="n"/>
-      <c r="C179" s="8" t="n"/>
+      <c r="B179" s="14" t="n"/>
+      <c r="C179" s="15" t="n"/>
       <c r="D179" s="9" t="n"/>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1" s="23">
       <c r="A180" s="6" t="n"/>
-      <c r="B180" s="7" t="n"/>
-      <c r="C180" s="8" t="n"/>
+      <c r="B180" s="14" t="n"/>
+      <c r="C180" s="15" t="n"/>
       <c r="D180" s="9" t="n"/>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1" s="23">
       <c r="A181" s="6" t="n"/>
-      <c r="B181" s="7" t="n"/>
-      <c r="C181" s="8" t="n"/>
+      <c r="B181" s="14" t="n"/>
+      <c r="C181" s="15" t="n"/>
       <c r="D181" s="9" t="n"/>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1" s="23">
       <c r="A182" s="6" t="n"/>
-      <c r="B182" s="7" t="n"/>
-      <c r="C182" s="8" t="n"/>
+      <c r="B182" s="14" t="n"/>
+      <c r="C182" s="15" t="n"/>
       <c r="D182" s="9" t="n"/>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1" s="23">
       <c r="A183" s="6" t="n"/>
-      <c r="B183" s="7" t="n"/>
-      <c r="C183" s="8" t="n"/>
+      <c r="B183" s="14" t="n"/>
+      <c r="C183" s="15" t="n"/>
       <c r="D183" s="9" t="n"/>
     </row>
-    <row r="184">
+    <row r="184" ht="15.75" customHeight="1" s="23">
       <c r="A184" s="6" t="n"/>
-      <c r="B184" s="7" t="n"/>
-      <c r="C184" s="8" t="n"/>
+      <c r="B184" s="14" t="n"/>
+      <c r="C184" s="15" t="n"/>
       <c r="D184" s="9" t="n"/>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1" s="23">
       <c r="A185" s="6" t="n"/>
-      <c r="B185" s="7" t="n"/>
-      <c r="C185" s="8" t="n"/>
+      <c r="B185" s="14" t="n"/>
+      <c r="C185" s="15" t="n"/>
       <c r="D185" s="9" t="n"/>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1" s="23">
       <c r="A186" s="6" t="n"/>
-      <c r="B186" s="7" t="n"/>
-      <c r="C186" s="8" t="n"/>
+      <c r="B186" s="14" t="n"/>
+      <c r="C186" s="15" t="n"/>
       <c r="D186" s="9" t="n"/>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1" s="23">
       <c r="A187" s="6" t="n"/>
-      <c r="B187" s="7" t="n"/>
-      <c r="C187" s="8" t="n"/>
+      <c r="B187" s="14" t="n"/>
+      <c r="C187" s="15" t="n"/>
       <c r="D187" s="9" t="n"/>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1" s="23">
       <c r="A188" s="6" t="n"/>
-      <c r="B188" s="7" t="n"/>
-      <c r="C188" s="8" t="n"/>
+      <c r="B188" s="14" t="n"/>
+      <c r="C188" s="15" t="n"/>
       <c r="D188" s="9" t="n"/>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1" s="23">
       <c r="A189" s="6" t="n"/>
-      <c r="B189" s="7" t="n"/>
-      <c r="C189" s="8" t="n"/>
+      <c r="B189" s="14" t="n"/>
+      <c r="C189" s="15" t="n"/>
       <c r="D189" s="9" t="n"/>
     </row>
-    <row r="190">
+    <row r="190" ht="15.75" customHeight="1" s="23">
       <c r="A190" s="6" t="n"/>
-      <c r="B190" s="7" t="n"/>
-      <c r="C190" s="8" t="n"/>
+      <c r="B190" s="14" t="n"/>
+      <c r="C190" s="15" t="n"/>
       <c r="D190" s="9" t="n"/>
     </row>
-    <row r="191">
+    <row r="191" ht="15.75" customHeight="1" s="23">
       <c r="A191" s="6" t="n"/>
-      <c r="B191" s="7" t="n"/>
-      <c r="C191" s="8" t="n"/>
+      <c r="B191" s="14" t="n"/>
+      <c r="C191" s="15" t="n"/>
       <c r="D191" s="9" t="n"/>
     </row>
-    <row r="192">
+    <row r="192" ht="15.75" customHeight="1" s="23">
       <c r="A192" s="6" t="n"/>
-      <c r="B192" s="7" t="n"/>
-      <c r="C192" s="8" t="n"/>
+      <c r="B192" s="14" t="n"/>
+      <c r="C192" s="15" t="n"/>
       <c r="D192" s="9" t="n"/>
     </row>
-    <row r="193">
+    <row r="193" ht="15.75" customHeight="1" s="23">
       <c r="A193" s="6" t="n"/>
-      <c r="B193" s="7" t="n"/>
-      <c r="C193" s="8" t="n"/>
+      <c r="B193" s="14" t="n"/>
+      <c r="C193" s="15" t="n"/>
       <c r="D193" s="9" t="n"/>
     </row>
-    <row r="194">
+    <row r="194" ht="15.75" customHeight="1" s="23">
       <c r="A194" s="6" t="n"/>
-      <c r="B194" s="7" t="n"/>
-      <c r="C194" s="8" t="n"/>
+      <c r="B194" s="14" t="n"/>
+      <c r="C194" s="15" t="n"/>
       <c r="D194" s="9" t="n"/>
     </row>
-    <row r="195">
+    <row r="195" ht="15.75" customHeight="1" s="23">
       <c r="A195" s="6" t="n"/>
-      <c r="B195" s="7" t="n"/>
-      <c r="C195" s="8" t="n"/>
+      <c r="B195" s="14" t="n"/>
+      <c r="C195" s="15" t="n"/>
       <c r="D195" s="9" t="n"/>
     </row>
-    <row r="196">
+    <row r="196" ht="15.75" customHeight="1" s="23">
       <c r="A196" s="6" t="n"/>
-      <c r="B196" s="7" t="n"/>
-      <c r="C196" s="8" t="n"/>
+      <c r="B196" s="14" t="n"/>
+      <c r="C196" s="15" t="n"/>
       <c r="D196" s="9" t="n"/>
     </row>
-    <row r="197">
+    <row r="197" ht="15.75" customHeight="1" s="23">
       <c r="A197" s="6" t="n"/>
-      <c r="B197" s="7" t="n"/>
-      <c r="C197" s="8" t="n"/>
+      <c r="B197" s="14" t="n"/>
+      <c r="C197" s="15" t="n"/>
       <c r="D197" s="9" t="n"/>
     </row>
-    <row r="198">
+    <row r="198" ht="15.75" customHeight="1" s="23">
       <c r="A198" s="6" t="n"/>
-      <c r="B198" s="7" t="n"/>
-      <c r="C198" s="8" t="n"/>
+      <c r="B198" s="14" t="n"/>
+      <c r="C198" s="15" t="n"/>
       <c r="D198" s="9" t="n"/>
     </row>
-    <row r="199">
+    <row r="199" ht="15.75" customHeight="1" s="23">
       <c r="A199" s="6" t="n"/>
-      <c r="B199" s="7" t="n"/>
-      <c r="C199" s="8" t="n"/>
+      <c r="B199" s="14" t="n"/>
+      <c r="C199" s="15" t="n"/>
       <c r="D199" s="9" t="n"/>
     </row>
-    <row r="200">
+    <row r="200" ht="15.75" customHeight="1" s="23">
       <c r="A200" s="6" t="n"/>
-      <c r="B200" s="7" t="n"/>
-      <c r="C200" s="8" t="n"/>
+      <c r="B200" s="14" t="n"/>
+      <c r="C200" s="15" t="n"/>
       <c r="D200" s="9" t="n"/>
     </row>
-    <row r="201">
+    <row r="201" ht="15.75" customHeight="1" s="23">
       <c r="A201" s="6" t="n"/>
-      <c r="B201" s="7" t="n"/>
-      <c r="C201" s="8" t="n"/>
+      <c r="B201" s="14" t="n"/>
+      <c r="C201" s="15" t="n"/>
       <c r="D201" s="9" t="n"/>
     </row>
-    <row r="202">
+    <row r="202" ht="15.75" customHeight="1" s="23">
       <c r="A202" s="6" t="n"/>
-      <c r="B202" s="7" t="n"/>
-      <c r="C202" s="8" t="n"/>
+      <c r="B202" s="14" t="n"/>
+      <c r="C202" s="15" t="n"/>
       <c r="D202" s="9" t="n"/>
     </row>
-    <row r="203">
+    <row r="203" ht="15.75" customHeight="1" s="23">
       <c r="A203" s="6" t="n"/>
-      <c r="B203" s="7" t="n"/>
-      <c r="C203" s="8" t="n"/>
+      <c r="B203" s="14" t="n"/>
+      <c r="C203" s="15" t="n"/>
       <c r="D203" s="9" t="n"/>
     </row>
-    <row r="204">
+    <row r="204" ht="15.75" customHeight="1" s="23">
       <c r="A204" s="6" t="n"/>
-      <c r="B204" s="7" t="n"/>
-      <c r="C204" s="8" t="n"/>
+      <c r="B204" s="14" t="n"/>
+      <c r="C204" s="15" t="n"/>
       <c r="D204" s="9" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" ht="15.75" customHeight="1" s="23">
       <c r="A205" s="6" t="n"/>
-      <c r="B205" s="7" t="n"/>
-      <c r="C205" s="8" t="n"/>
+      <c r="B205" s="14" t="n"/>
+      <c r="C205" s="15" t="n"/>
       <c r="D205" s="9" t="n"/>
     </row>
-    <row r="206">
+    <row r="206" ht="15.75" customHeight="1" s="23">
       <c r="A206" s="6" t="n"/>
-      <c r="B206" s="7" t="n"/>
-      <c r="C206" s="8" t="n"/>
+      <c r="B206" s="14" t="n"/>
+      <c r="C206" s="15" t="n"/>
       <c r="D206" s="9" t="n"/>
     </row>
-    <row r="207">
+    <row r="207" ht="15.75" customHeight="1" s="23">
       <c r="A207" s="6" t="n"/>
-      <c r="B207" s="7" t="n"/>
-      <c r="C207" s="8" t="n"/>
+      <c r="B207" s="14" t="n"/>
+      <c r="C207" s="15" t="n"/>
       <c r="D207" s="9" t="n"/>
     </row>
-    <row r="208">
+    <row r="208" ht="15.75" customHeight="1" s="23">
       <c r="A208" s="6" t="n"/>
-      <c r="B208" s="7" t="n"/>
-      <c r="C208" s="8" t="n"/>
+      <c r="B208" s="14" t="n"/>
+      <c r="C208" s="15" t="n"/>
       <c r="D208" s="9" t="n"/>
     </row>
-    <row r="209">
+    <row r="209" ht="15.75" customHeight="1" s="23">
       <c r="A209" s="6" t="n"/>
-      <c r="B209" s="7" t="n"/>
-      <c r="C209" s="8" t="n"/>
+      <c r="B209" s="14" t="n"/>
+      <c r="C209" s="15" t="n"/>
       <c r="D209" s="9" t="n"/>
     </row>
-    <row r="210">
+    <row r="210" ht="15.75" customHeight="1" s="23">
       <c r="A210" s="6" t="n"/>
-      <c r="B210" s="7" t="n"/>
-      <c r="C210" s="8" t="n"/>
+      <c r="B210" s="14" t="n"/>
+      <c r="C210" s="15" t="n"/>
       <c r="D210" s="9" t="n"/>
     </row>
-    <row r="211">
+    <row r="211" ht="15.75" customHeight="1" s="23">
       <c r="A211" s="6" t="n"/>
-      <c r="B211" s="7" t="n"/>
-      <c r="C211" s="8" t="n"/>
+      <c r="B211" s="14" t="n"/>
+      <c r="C211" s="15" t="n"/>
       <c r="D211" s="9" t="n"/>
     </row>
-    <row r="212">
+    <row r="212" ht="15.75" customHeight="1" s="23">
       <c r="A212" s="6" t="n"/>
-      <c r="B212" s="7" t="n"/>
-      <c r="C212" s="8" t="n"/>
+      <c r="B212" s="14" t="n"/>
+      <c r="C212" s="15" t="n"/>
       <c r="D212" s="9" t="n"/>
     </row>
-    <row r="213">
+    <row r="213" ht="15.75" customHeight="1" s="23">
       <c r="A213" s="6" t="n"/>
-      <c r="B213" s="7" t="n"/>
-      <c r="C213" s="8" t="n"/>
+      <c r="B213" s="14" t="n"/>
+      <c r="C213" s="15" t="n"/>
       <c r="D213" s="9" t="n"/>
     </row>
-    <row r="214">
+    <row r="214" ht="15.75" customHeight="1" s="23">
       <c r="A214" s="6" t="n"/>
-      <c r="B214" s="7" t="n"/>
-      <c r="C214" s="8" t="n"/>
+      <c r="B214" s="14" t="n"/>
+      <c r="C214" s="15" t="n"/>
       <c r="D214" s="9" t="n"/>
     </row>
-    <row r="215">
+    <row r="215" ht="15.75" customHeight="1" s="23">
       <c r="A215" s="6" t="n"/>
-      <c r="B215" s="7" t="n"/>
-      <c r="C215" s="8" t="n"/>
+      <c r="B215" s="14" t="n"/>
+      <c r="C215" s="15" t="n"/>
       <c r="D215" s="9" t="n"/>
     </row>
-    <row r="216">
+    <row r="216" ht="15.75" customHeight="1" s="23">
       <c r="A216" s="6" t="n"/>
-      <c r="B216" s="7" t="n"/>
-      <c r="C216" s="8" t="n"/>
+      <c r="B216" s="14" t="n"/>
+      <c r="C216" s="15" t="n"/>
       <c r="D216" s="9" t="n"/>
     </row>
-    <row r="217">
+    <row r="217" ht="15.75" customHeight="1" s="23">
       <c r="A217" s="6" t="n"/>
-      <c r="B217" s="7" t="n"/>
-      <c r="C217" s="8" t="n"/>
+      <c r="B217" s="14" t="n"/>
+      <c r="C217" s="15" t="n"/>
       <c r="D217" s="9" t="n"/>
     </row>
-    <row r="218">
+    <row r="218" ht="15.75" customHeight="1" s="23">
       <c r="A218" s="6" t="n"/>
-      <c r="B218" s="7" t="n"/>
-      <c r="C218" s="8" t="n"/>
+      <c r="B218" s="14" t="n"/>
+      <c r="C218" s="15" t="n"/>
       <c r="D218" s="9" t="n"/>
     </row>
-    <row r="219">
+    <row r="219" ht="15.75" customHeight="1" s="23">
       <c r="A219" s="6" t="n"/>
-      <c r="B219" s="7" t="n"/>
-      <c r="C219" s="8" t="n"/>
+      <c r="B219" s="14" t="n"/>
+      <c r="C219" s="15" t="n"/>
       <c r="D219" s="9" t="n"/>
     </row>
-    <row r="220">
+    <row r="220" ht="15.75" customHeight="1" s="23">
       <c r="A220" s="6" t="n"/>
-      <c r="B220" s="7" t="n"/>
-      <c r="C220" s="8" t="n"/>
+      <c r="B220" s="14" t="n"/>
+      <c r="C220" s="15" t="n"/>
       <c r="D220" s="9" t="n"/>
     </row>
-    <row r="221">
+    <row r="221" ht="15.75" customHeight="1" s="23">
       <c r="A221" s="6" t="n"/>
-      <c r="B221" s="7" t="n"/>
-      <c r="C221" s="8" t="n"/>
+      <c r="B221" s="14" t="n"/>
+      <c r="C221" s="15" t="n"/>
       <c r="D221" s="9" t="n"/>
     </row>
-    <row r="222">
+    <row r="222" ht="15.75" customHeight="1" s="23">
       <c r="A222" s="6" t="n"/>
-      <c r="B222" s="7" t="n"/>
-      <c r="C222" s="8" t="n"/>
+      <c r="B222" s="14" t="n"/>
+      <c r="C222" s="15" t="n"/>
       <c r="D222" s="9" t="n"/>
     </row>
-    <row r="223">
+    <row r="223" ht="15.75" customHeight="1" s="23">
       <c r="A223" s="6" t="n"/>
-      <c r="B223" s="7" t="n"/>
-      <c r="C223" s="8" t="n"/>
+      <c r="B223" s="14" t="n"/>
+      <c r="C223" s="15" t="n"/>
       <c r="D223" s="9" t="n"/>
     </row>
-    <row r="224">
+    <row r="224" ht="15.75" customHeight="1" s="23">
       <c r="A224" s="6" t="n"/>
-      <c r="B224" s="7" t="n"/>
-      <c r="C224" s="8" t="n"/>
+      <c r="B224" s="14" t="n"/>
+      <c r="C224" s="15" t="n"/>
       <c r="D224" s="9" t="n"/>
     </row>
-    <row r="225">
+    <row r="225" ht="15.75" customHeight="1" s="23">
       <c r="A225" s="6" t="n"/>
-      <c r="B225" s="7" t="n"/>
-      <c r="C225" s="8" t="n"/>
+      <c r="B225" s="14" t="n"/>
+      <c r="C225" s="15" t="n"/>
       <c r="D225" s="9" t="n"/>
     </row>
-    <row r="226">
+    <row r="226" ht="15.75" customHeight="1" s="23">
       <c r="A226" s="6" t="n"/>
-      <c r="B226" s="7" t="n"/>
-      <c r="C226" s="8" t="n"/>
+      <c r="B226" s="14" t="n"/>
+      <c r="C226" s="15" t="n"/>
       <c r="D226" s="9" t="n"/>
     </row>
-    <row r="227">
+    <row r="227" ht="15.75" customHeight="1" s="23">
       <c r="A227" s="6" t="n"/>
-      <c r="B227" s="7" t="n"/>
-      <c r="C227" s="8" t="n"/>
+      <c r="B227" s="14" t="n"/>
+      <c r="C227" s="15" t="n"/>
       <c r="D227" s="9" t="n"/>
     </row>
-    <row r="228">
+    <row r="228" ht="15.75" customHeight="1" s="23">
       <c r="A228" s="6" t="n"/>
-      <c r="B228" s="7" t="n"/>
-      <c r="C228" s="8" t="n"/>
+      <c r="B228" s="14" t="n"/>
+      <c r="C228" s="15" t="n"/>
       <c r="D228" s="9" t="n"/>
     </row>
-    <row r="229">
+    <row r="229" ht="15.75" customHeight="1" s="23">
       <c r="A229" s="6" t="n"/>
-      <c r="B229" s="7" t="n"/>
-      <c r="C229" s="8" t="n"/>
+      <c r="B229" s="14" t="n"/>
+      <c r="C229" s="15" t="n"/>
       <c r="D229" s="9" t="n"/>
     </row>
-    <row r="230">
+    <row r="230" ht="15.75" customHeight="1" s="23">
       <c r="A230" s="6" t="n"/>
-      <c r="B230" s="7" t="n"/>
-      <c r="C230" s="8" t="n"/>
+      <c r="B230" s="14" t="n"/>
+      <c r="C230" s="15" t="n"/>
       <c r="D230" s="9" t="n"/>
     </row>
-    <row r="231">
+    <row r="231" ht="15.75" customHeight="1" s="23">
       <c r="A231" s="6" t="n"/>
-      <c r="B231" s="7" t="n"/>
-      <c r="C231" s="8" t="n"/>
+      <c r="B231" s="14" t="n"/>
+      <c r="C231" s="15" t="n"/>
       <c r="D231" s="9" t="n"/>
     </row>
-    <row r="232">
+    <row r="232" ht="15.75" customHeight="1" s="23">
       <c r="A232" s="6" t="n"/>
-      <c r="B232" s="7" t="n"/>
-      <c r="C232" s="8" t="n"/>
+      <c r="B232" s="14" t="n"/>
+      <c r="C232" s="15" t="n"/>
       <c r="D232" s="9" t="n"/>
     </row>
-    <row r="233">
+    <row r="233" ht="15.75" customHeight="1" s="23">
       <c r="A233" s="6" t="n"/>
-      <c r="B233" s="7" t="n"/>
-      <c r="C233" s="8" t="n"/>
+      <c r="B233" s="14" t="n"/>
+      <c r="C233" s="15" t="n"/>
       <c r="D233" s="9" t="n"/>
     </row>
-    <row r="234">
+    <row r="234" ht="15.75" customHeight="1" s="23">
       <c r="A234" s="6" t="n"/>
-      <c r="B234" s="7" t="n"/>
-      <c r="C234" s="8" t="n"/>
+      <c r="B234" s="14" t="n"/>
+      <c r="C234" s="15" t="n"/>
       <c r="D234" s="9" t="n"/>
     </row>
-    <row r="235">
+    <row r="235" ht="15.75" customHeight="1" s="23">
       <c r="A235" s="6" t="n"/>
-      <c r="B235" s="7" t="n"/>
-      <c r="C235" s="8" t="n"/>
+      <c r="B235" s="14" t="n"/>
+      <c r="C235" s="15" t="n"/>
       <c r="D235" s="9" t="n"/>
     </row>
-    <row r="236">
+    <row r="236" ht="15.75" customHeight="1" s="23">
       <c r="A236" s="6" t="n"/>
-      <c r="B236" s="7" t="n"/>
-      <c r="C236" s="8" t="n"/>
+      <c r="B236" s="14" t="n"/>
+      <c r="C236" s="15" t="n"/>
       <c r="D236" s="9" t="n"/>
     </row>
-    <row r="237">
+    <row r="237" ht="15.75" customHeight="1" s="23">
       <c r="A237" s="6" t="n"/>
-      <c r="B237" s="7" t="n"/>
-      <c r="C237" s="8" t="n"/>
+      <c r="B237" s="14" t="n"/>
+      <c r="C237" s="15" t="n"/>
       <c r="D237" s="9" t="n"/>
     </row>
-    <row r="238">
+    <row r="238" ht="15.75" customHeight="1" s="23">
       <c r="A238" s="6" t="n"/>
-      <c r="B238" s="7" t="n"/>
-      <c r="C238" s="8" t="n"/>
+      <c r="B238" s="14" t="n"/>
+      <c r="C238" s="15" t="n"/>
       <c r="D238" s="9" t="n"/>
     </row>
-    <row r="239">
+    <row r="239" ht="15.75" customHeight="1" s="23">
       <c r="A239" s="6" t="n"/>
-      <c r="B239" s="7" t="n"/>
-      <c r="C239" s="8" t="n"/>
+      <c r="B239" s="14" t="n"/>
+      <c r="C239" s="15" t="n"/>
       <c r="D239" s="9" t="n"/>
     </row>
-    <row r="240">
+    <row r="240" ht="15.75" customHeight="1" s="23">
       <c r="A240" s="6" t="n"/>
-      <c r="B240" s="7" t="n"/>
-      <c r="C240" s="8" t="n"/>
+      <c r="B240" s="14" t="n"/>
+      <c r="C240" s="15" t="n"/>
       <c r="D240" s="9" t="n"/>
     </row>
-    <row r="241">
+    <row r="241" ht="15.75" customHeight="1" s="23">
       <c r="A241" s="6" t="n"/>
-      <c r="B241" s="7" t="n"/>
-      <c r="C241" s="8" t="n"/>
+      <c r="B241" s="14" t="n"/>
+      <c r="C241" s="15" t="n"/>
       <c r="D241" s="9" t="n"/>
     </row>
-    <row r="242">
+    <row r="242" ht="15.75" customHeight="1" s="23">
       <c r="A242" s="6" t="n"/>
-      <c r="B242" s="7" t="n"/>
-      <c r="C242" s="8" t="n"/>
+      <c r="B242" s="14" t="n"/>
+      <c r="C242" s="15" t="n"/>
       <c r="D242" s="9" t="n"/>
     </row>
-    <row r="243">
+    <row r="243" ht="15.75" customHeight="1" s="23">
       <c r="A243" s="6" t="n"/>
-      <c r="B243" s="7" t="n"/>
-      <c r="C243" s="8" t="n"/>
+      <c r="B243" s="14" t="n"/>
+      <c r="C243" s="15" t="n"/>
       <c r="D243" s="9" t="n"/>
     </row>
-    <row r="244">
+    <row r="244" ht="15.75" customHeight="1" s="23">
       <c r="A244" s="6" t="n"/>
-      <c r="B244" s="7" t="n"/>
-      <c r="C244" s="8" t="n"/>
+      <c r="B244" s="14" t="n"/>
+      <c r="C244" s="15" t="n"/>
       <c r="D244" s="9" t="n"/>
     </row>
-    <row r="245">
+    <row r="245" ht="15.75" customHeight="1" s="23">
       <c r="A245" s="6" t="n"/>
-      <c r="B245" s="7" t="n"/>
-      <c r="C245" s="8" t="n"/>
+      <c r="B245" s="14" t="n"/>
+      <c r="C245" s="15" t="n"/>
       <c r="D245" s="9" t="n"/>
     </row>
-    <row r="246">
+    <row r="246" ht="15.75" customHeight="1" s="23">
       <c r="A246" s="6" t="n"/>
-      <c r="B246" s="7" t="n"/>
-      <c r="C246" s="8" t="n"/>
+      <c r="B246" s="14" t="n"/>
+      <c r="C246" s="15" t="n"/>
       <c r="D246" s="9" t="n"/>
     </row>
-    <row r="247">
+    <row r="247" ht="15.75" customHeight="1" s="23">
       <c r="A247" s="6" t="n"/>
-      <c r="B247" s="7" t="n"/>
-      <c r="C247" s="8" t="n"/>
+      <c r="B247" s="14" t="n"/>
+      <c r="C247" s="15" t="n"/>
       <c r="D247" s="9" t="n"/>
     </row>
-    <row r="248">
+    <row r="248" ht="15.75" customHeight="1" s="23">
       <c r="A248" s="6" t="n"/>
-      <c r="B248" s="7" t="n"/>
-      <c r="C248" s="8" t="n"/>
+      <c r="B248" s="14" t="n"/>
+      <c r="C248" s="15" t="n"/>
       <c r="D248" s="9" t="n"/>
     </row>
-    <row r="249">
+    <row r="249" ht="15.75" customHeight="1" s="23">
       <c r="A249" s="6" t="n"/>
-      <c r="B249" s="7" t="n"/>
-      <c r="C249" s="8" t="n"/>
+      <c r="B249" s="14" t="n"/>
+      <c r="C249" s="15" t="n"/>
       <c r="D249" s="9" t="n"/>
     </row>
-    <row r="250">
+    <row r="250" ht="15.75" customHeight="1" s="23">
       <c r="A250" s="6" t="n"/>
-      <c r="B250" s="7" t="n"/>
-      <c r="C250" s="8" t="n"/>
+      <c r="B250" s="14" t="n"/>
+      <c r="C250" s="15" t="n"/>
       <c r="D250" s="9" t="n"/>
     </row>
-    <row r="251">
+    <row r="251" ht="15.75" customHeight="1" s="23">
       <c r="A251" s="6" t="n"/>
-      <c r="B251" s="7" t="n"/>
-      <c r="C251" s="8" t="n"/>
+      <c r="B251" s="14" t="n"/>
+      <c r="C251" s="15" t="n"/>
       <c r="D251" s="9" t="n"/>
     </row>
-    <row r="252">
+    <row r="252" ht="15.75" customHeight="1" s="23">
       <c r="A252" s="6" t="n"/>
-      <c r="B252" s="7" t="n"/>
-      <c r="C252" s="8" t="n"/>
+      <c r="B252" s="14" t="n"/>
+      <c r="C252" s="15" t="n"/>
       <c r="D252" s="9" t="n"/>
     </row>
-    <row r="253">
+    <row r="253" ht="15.75" customHeight="1" s="23">
       <c r="A253" s="6" t="n"/>
-      <c r="B253" s="7" t="n"/>
-      <c r="C253" s="8" t="n"/>
+      <c r="B253" s="14" t="n"/>
+      <c r="C253" s="15" t="n"/>
       <c r="D253" s="9" t="n"/>
     </row>
-    <row r="254">
+    <row r="254" ht="15.75" customHeight="1" s="23">
       <c r="A254" s="6" t="n"/>
-      <c r="B254" s="7" t="n"/>
-      <c r="C254" s="8" t="n"/>
+      <c r="B254" s="14" t="n"/>
+      <c r="C254" s="15" t="n"/>
       <c r="D254" s="9" t="n"/>
     </row>
-    <row r="255">
-      <c r="A255" s="6" t="n"/>
-      <c r="B255" s="7" t="n"/>
-      <c r="C255" s="8" t="n"/>
-      <c r="D255" s="9" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="6" t="n"/>
-      <c r="B256" s="7" t="n"/>
-      <c r="C256" s="8" t="n"/>
-      <c r="D256" s="9" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="6" t="n"/>
-      <c r="B257" s="7" t="n"/>
-      <c r="C257" s="8" t="n"/>
-      <c r="D257" s="9" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="6" t="n"/>
-      <c r="B258" s="7" t="n"/>
-      <c r="C258" s="8" t="n"/>
-      <c r="D258" s="9" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="6" t="n"/>
-      <c r="B259" s="7" t="n"/>
-      <c r="C259" s="8" t="n"/>
-      <c r="D259" s="9" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="6" t="n"/>
-      <c r="B260" s="7" t="n"/>
-      <c r="C260" s="8" t="n"/>
-      <c r="D260" s="9" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="6" t="n"/>
-      <c r="B261" s="7" t="n"/>
-      <c r="C261" s="8" t="n"/>
-      <c r="D261" s="9" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="6" t="n"/>
-      <c r="B262" s="7" t="n"/>
-      <c r="C262" s="8" t="n"/>
-      <c r="D262" s="9" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="6" t="n"/>
-      <c r="B263" s="7" t="n"/>
-      <c r="C263" s="8" t="n"/>
-      <c r="D263" s="9" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="6" t="n"/>
-      <c r="B264" s="7" t="n"/>
-      <c r="C264" s="8" t="n"/>
-      <c r="D264" s="9" t="n"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="6" t="n"/>
-      <c r="B265" s="7" t="n"/>
-      <c r="C265" s="8" t="n"/>
-      <c r="D265" s="9" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="6" t="n"/>
-      <c r="B266" s="7" t="n"/>
-      <c r="C266" s="8" t="n"/>
-      <c r="D266" s="9" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="6" t="n"/>
-      <c r="B267" s="7" t="n"/>
-      <c r="C267" s="8" t="n"/>
-      <c r="D267" s="9" t="n"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="6" t="n"/>
-      <c r="B268" s="7" t="n"/>
-      <c r="C268" s="8" t="n"/>
-      <c r="D268" s="9" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="6" t="n"/>
-      <c r="B269" s="7" t="n"/>
-      <c r="C269" s="8" t="n"/>
-      <c r="D269" s="9" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="6" t="n"/>
-      <c r="B270" s="7" t="n"/>
-      <c r="C270" s="8" t="n"/>
-      <c r="D270" s="9" t="n"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="6" t="n"/>
-      <c r="B271" s="7" t="n"/>
-      <c r="C271" s="8" t="n"/>
-      <c r="D271" s="9" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="6" t="n"/>
-      <c r="B272" s="7" t="n"/>
-      <c r="C272" s="8" t="n"/>
-      <c r="D272" s="9" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="6" t="n"/>
-      <c r="B273" s="7" t="n"/>
-      <c r="C273" s="8" t="n"/>
-      <c r="D273" s="9" t="n"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="6" t="n"/>
-      <c r="B274" s="7" t="n"/>
-      <c r="C274" s="8" t="n"/>
-      <c r="D274" s="9" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="6" t="n"/>
-      <c r="B275" s="7" t="n"/>
-      <c r="C275" s="8" t="n"/>
-      <c r="D275" s="9" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="6" t="n"/>
-      <c r="B276" s="7" t="n"/>
-      <c r="C276" s="8" t="n"/>
-      <c r="D276" s="9" t="n"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="6" t="n"/>
-      <c r="B277" s="7" t="n"/>
-      <c r="C277" s="8" t="n"/>
-      <c r="D277" s="9" t="n"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="6" t="n"/>
-      <c r="B278" s="7" t="n"/>
-      <c r="C278" s="8" t="n"/>
-      <c r="D278" s="9" t="n"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="6" t="n"/>
-      <c r="B279" s="7" t="n"/>
-      <c r="C279" s="8" t="n"/>
-      <c r="D279" s="9" t="n"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="6" t="n"/>
-      <c r="B280" s="7" t="n"/>
-      <c r="C280" s="8" t="n"/>
-      <c r="D280" s="9" t="n"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="6" t="n"/>
-      <c r="B281" s="7" t="n"/>
-      <c r="C281" s="8" t="n"/>
-      <c r="D281" s="9" t="n"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="6" t="n"/>
-      <c r="B282" s="7" t="n"/>
-      <c r="C282" s="8" t="n"/>
-      <c r="D282" s="9" t="n"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="6" t="n"/>
-      <c r="B283" s="7" t="n"/>
-      <c r="C283" s="8" t="n"/>
-      <c r="D283" s="9" t="n"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="6" t="n"/>
-      <c r="B284" s="7" t="n"/>
-      <c r="C284" s="8" t="n"/>
-      <c r="D284" s="9" t="n"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="6" t="n"/>
-      <c r="B285" s="7" t="n"/>
-      <c r="C285" s="8" t="n"/>
-      <c r="D285" s="9" t="n"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="6" t="n"/>
-      <c r="B286" s="7" t="n"/>
-      <c r="C286" s="8" t="n"/>
-      <c r="D286" s="9" t="n"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="6" t="n"/>
-      <c r="B287" s="7" t="n"/>
-      <c r="C287" s="8" t="n"/>
-      <c r="D287" s="9" t="n"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="6" t="n"/>
-      <c r="B288" s="7" t="n"/>
-      <c r="C288" s="8" t="n"/>
-      <c r="D288" s="9" t="n"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="6" t="n"/>
-      <c r="B289" s="7" t="n"/>
-      <c r="C289" s="8" t="n"/>
-      <c r="D289" s="9" t="n"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="6" t="n"/>
-      <c r="B290" s="7" t="n"/>
-      <c r="C290" s="8" t="n"/>
-      <c r="D290" s="9" t="n"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="6" t="n"/>
-      <c r="B291" s="7" t="n"/>
-      <c r="C291" s="8" t="n"/>
-      <c r="D291" s="9" t="n"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="6" t="n"/>
-      <c r="B292" s="7" t="n"/>
-      <c r="C292" s="8" t="n"/>
-      <c r="D292" s="9" t="n"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="6" t="n"/>
-      <c r="B293" s="7" t="n"/>
-      <c r="C293" s="8" t="n"/>
-      <c r="D293" s="9" t="n"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="6" t="n"/>
-      <c r="B294" s="7" t="n"/>
-      <c r="C294" s="8" t="n"/>
-      <c r="D294" s="9" t="n"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="6" t="n"/>
-      <c r="B295" s="7" t="n"/>
-      <c r="C295" s="8" t="n"/>
-      <c r="D295" s="9" t="n"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="6" t="n"/>
-      <c r="B296" s="7" t="n"/>
-      <c r="C296" s="8" t="n"/>
-      <c r="D296" s="9" t="n"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="6" t="n"/>
-      <c r="B297" s="7" t="n"/>
-      <c r="C297" s="8" t="n"/>
-      <c r="D297" s="9" t="n"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="6" t="n"/>
-      <c r="B298" s="7" t="n"/>
-      <c r="C298" s="8" t="n"/>
-      <c r="D298" s="9" t="n"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="6" t="n"/>
-      <c r="B299" s="7" t="n"/>
-      <c r="C299" s="8" t="n"/>
-      <c r="D299" s="9" t="n"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="6" t="n"/>
-      <c r="B300" s="7" t="n"/>
-      <c r="C300" s="8" t="n"/>
-      <c r="D300" s="9" t="n"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="6" t="n"/>
-      <c r="B301" s="7" t="n"/>
-      <c r="C301" s="8" t="n"/>
-      <c r="D301" s="9" t="n"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="6" t="n"/>
-      <c r="B302" s="7" t="n"/>
-      <c r="C302" s="8" t="n"/>
-      <c r="D302" s="9" t="n"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="6" t="n"/>
-      <c r="B303" s="7" t="n"/>
-      <c r="C303" s="8" t="n"/>
-      <c r="D303" s="9" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="6" t="n"/>
-      <c r="B304" s="7" t="n"/>
-      <c r="C304" s="8" t="n"/>
-      <c r="D304" s="9" t="n"/>
-    </row>
+    <row r="255" ht="15.75" customHeight="1" s="23">
+      <c r="A255" s="22" t="n"/>
+      <c r="B255" s="22" t="n"/>
+    </row>
+    <row r="256" ht="15.75" customHeight="1" s="23">
+      <c r="A256" s="22" t="n"/>
+      <c r="B256" s="22" t="n"/>
+    </row>
+    <row r="257" ht="15.75" customHeight="1" s="23">
+      <c r="A257" s="22" t="n"/>
+      <c r="B257" s="22" t="n"/>
+    </row>
+    <row r="258" ht="15.75" customHeight="1" s="23">
+      <c r="A258" s="22" t="n"/>
+      <c r="B258" s="22" t="n"/>
+    </row>
+    <row r="259" ht="15.75" customHeight="1" s="23">
+      <c r="A259" s="22" t="n"/>
+      <c r="B259" s="22" t="n"/>
+    </row>
+    <row r="260" ht="15.75" customHeight="1" s="23">
+      <c r="A260" s="22" t="n"/>
+      <c r="B260" s="22" t="n"/>
+    </row>
+    <row r="261" ht="15.75" customHeight="1" s="23">
+      <c r="A261" s="22" t="n"/>
+      <c r="B261" s="22" t="n"/>
+    </row>
+    <row r="262" ht="15.75" customHeight="1" s="23">
+      <c r="A262" s="22" t="n"/>
+      <c r="B262" s="22" t="n"/>
+    </row>
+    <row r="263" ht="15.75" customHeight="1" s="23">
+      <c r="A263" s="22" t="n"/>
+      <c r="B263" s="22" t="n"/>
+    </row>
+    <row r="264" ht="15.75" customHeight="1" s="23">
+      <c r="A264" s="22" t="n"/>
+      <c r="B264" s="22" t="n"/>
+    </row>
+    <row r="265" ht="15.75" customHeight="1" s="23">
+      <c r="A265" s="22" t="n"/>
+      <c r="B265" s="22" t="n"/>
+    </row>
+    <row r="266" ht="15.75" customHeight="1" s="23">
+      <c r="A266" s="22" t="n"/>
+      <c r="B266" s="22" t="n"/>
+    </row>
+    <row r="267" ht="15.75" customHeight="1" s="23">
+      <c r="A267" s="22" t="n"/>
+      <c r="B267" s="22" t="n"/>
+    </row>
+    <row r="268" ht="15.75" customHeight="1" s="23">
+      <c r="A268" s="22" t="n"/>
+      <c r="B268" s="22" t="n"/>
+    </row>
+    <row r="269" ht="15.75" customHeight="1" s="23">
+      <c r="A269" s="22" t="n"/>
+      <c r="B269" s="22" t="n"/>
+    </row>
+    <row r="270" ht="15.75" customHeight="1" s="23">
+      <c r="A270" s="22" t="n"/>
+      <c r="B270" s="22" t="n"/>
+    </row>
+    <row r="271" ht="15.75" customHeight="1" s="23">
+      <c r="A271" s="22" t="n"/>
+      <c r="B271" s="22" t="n"/>
+    </row>
+    <row r="272" ht="15.75" customHeight="1" s="23">
+      <c r="A272" s="22" t="n"/>
+      <c r="B272" s="22" t="n"/>
+    </row>
+    <row r="273" ht="15.75" customHeight="1" s="23">
+      <c r="A273" s="22" t="n"/>
+      <c r="B273" s="22" t="n"/>
+    </row>
+    <row r="274" ht="15.75" customHeight="1" s="23">
+      <c r="A274" s="22" t="n"/>
+      <c r="B274" s="22" t="n"/>
+    </row>
+    <row r="275" ht="15.75" customHeight="1" s="23">
+      <c r="A275" s="22" t="n"/>
+      <c r="B275" s="22" t="n"/>
+    </row>
+    <row r="276" ht="15.75" customHeight="1" s="23">
+      <c r="A276" s="22" t="n"/>
+      <c r="B276" s="22" t="n"/>
+    </row>
+    <row r="277" ht="15.75" customHeight="1" s="23">
+      <c r="A277" s="22" t="n"/>
+      <c r="B277" s="22" t="n"/>
+    </row>
+    <row r="278" ht="15.75" customHeight="1" s="23">
+      <c r="A278" s="22" t="n"/>
+      <c r="B278" s="22" t="n"/>
+    </row>
+    <row r="279" ht="15.75" customHeight="1" s="23">
+      <c r="A279" s="22" t="n"/>
+      <c r="B279" s="22" t="n"/>
+    </row>
+    <row r="280" ht="15.75" customHeight="1" s="23">
+      <c r="A280" s="22" t="n"/>
+      <c r="B280" s="22" t="n"/>
+    </row>
+    <row r="281" ht="15.75" customHeight="1" s="23">
+      <c r="A281" s="22" t="n"/>
+      <c r="B281" s="22" t="n"/>
+    </row>
+    <row r="282" ht="15.75" customHeight="1" s="23">
+      <c r="A282" s="22" t="n"/>
+      <c r="B282" s="22" t="n"/>
+    </row>
+    <row r="283" ht="15.75" customHeight="1" s="23">
+      <c r="A283" s="22" t="n"/>
+      <c r="B283" s="22" t="n"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1" s="23">
+      <c r="A284" s="22" t="n"/>
+      <c r="B284" s="22" t="n"/>
+    </row>
+    <row r="285" ht="15.75" customHeight="1" s="23">
+      <c r="A285" s="22" t="n"/>
+      <c r="B285" s="22" t="n"/>
+    </row>
+    <row r="286" ht="15.75" customHeight="1" s="23">
+      <c r="A286" s="22" t="n"/>
+      <c r="B286" s="22" t="n"/>
+    </row>
+    <row r="287" ht="15.75" customHeight="1" s="23">
+      <c r="A287" s="22" t="n"/>
+      <c r="B287" s="22" t="n"/>
+    </row>
+    <row r="288" ht="15.75" customHeight="1" s="23">
+      <c r="A288" s="22" t="n"/>
+      <c r="B288" s="22" t="n"/>
+    </row>
+    <row r="289" ht="15.75" customHeight="1" s="23">
+      <c r="A289" s="22" t="n"/>
+      <c r="B289" s="22" t="n"/>
+    </row>
+    <row r="290" ht="15.75" customHeight="1" s="23">
+      <c r="A290" s="22" t="n"/>
+      <c r="B290" s="22" t="n"/>
+    </row>
+    <row r="291" ht="15.75" customHeight="1" s="23">
+      <c r="A291" s="22" t="n"/>
+      <c r="B291" s="22" t="n"/>
+    </row>
+    <row r="292" ht="15.75" customHeight="1" s="23">
+      <c r="A292" s="22" t="n"/>
+      <c r="B292" s="22" t="n"/>
+    </row>
+    <row r="293" ht="15.75" customHeight="1" s="23">
+      <c r="A293" s="22" t="n"/>
+      <c r="B293" s="22" t="n"/>
+    </row>
+    <row r="294" ht="15.75" customHeight="1" s="23">
+      <c r="A294" s="22" t="n"/>
+      <c r="B294" s="22" t="n"/>
+    </row>
+    <row r="295" ht="15.75" customHeight="1" s="23">
+      <c r="A295" s="22" t="n"/>
+      <c r="B295" s="22" t="n"/>
+    </row>
+    <row r="296" ht="15.75" customHeight="1" s="23">
+      <c r="A296" s="22" t="n"/>
+      <c r="B296" s="22" t="n"/>
+    </row>
+    <row r="297" ht="15.75" customHeight="1" s="23">
+      <c r="A297" s="22" t="n"/>
+      <c r="B297" s="22" t="n"/>
+    </row>
+    <row r="298" ht="15.75" customHeight="1" s="23">
+      <c r="A298" s="22" t="n"/>
+      <c r="B298" s="22" t="n"/>
+    </row>
+    <row r="299" ht="15.75" customHeight="1" s="23">
+      <c r="A299" s="22" t="n"/>
+      <c r="B299" s="22" t="n"/>
+    </row>
+    <row r="300" ht="15.75" customHeight="1" s="23">
+      <c r="A300" s="22" t="n"/>
+      <c r="B300" s="22" t="n"/>
+    </row>
+    <row r="301" ht="15.75" customHeight="1" s="23">
+      <c r="A301" s="22" t="n"/>
+      <c r="B301" s="22" t="n"/>
+    </row>
+    <row r="302" ht="15.75" customHeight="1" s="23">
+      <c r="A302" s="22" t="n"/>
+      <c r="B302" s="22" t="n"/>
+    </row>
+    <row r="303" ht="15.75" customHeight="1" s="23">
+      <c r="A303" s="22" t="n"/>
+      <c r="B303" s="22" t="n"/>
+    </row>
+    <row r="304" ht="15.75" customHeight="1" s="23">
+      <c r="A304" s="22" t="n"/>
+      <c r="B304" s="22" t="n"/>
+    </row>
+    <row r="305" ht="15.75" customHeight="1" s="23"/>
+    <row r="306" ht="15.75" customHeight="1" s="23"/>
+    <row r="307" ht="15.75" customHeight="1" s="23"/>
+    <row r="308" ht="15.75" customHeight="1" s="23"/>
+    <row r="309" ht="15.75" customHeight="1" s="23"/>
+    <row r="310" ht="15.75" customHeight="1" s="23"/>
+    <row r="311" ht="15.75" customHeight="1" s="23"/>
+    <row r="312" ht="15.75" customHeight="1" s="23"/>
+    <row r="313" ht="15.75" customHeight="1" s="23"/>
+    <row r="314" ht="15.75" customHeight="1" s="23"/>
+    <row r="315" ht="15.75" customHeight="1" s="23"/>
+    <row r="316" ht="15.75" customHeight="1" s="23"/>
+    <row r="317" ht="15.75" customHeight="1" s="23"/>
+    <row r="318" ht="15.75" customHeight="1" s="23"/>
+    <row r="319" ht="15.75" customHeight="1" s="23"/>
+    <row r="320" ht="15.75" customHeight="1" s="23"/>
+    <row r="321" ht="15.75" customHeight="1" s="23"/>
+    <row r="322" ht="15.75" customHeight="1" s="23"/>
+    <row r="323" ht="15.75" customHeight="1" s="23"/>
+    <row r="324" ht="15.75" customHeight="1" s="23"/>
+    <row r="325" ht="15.75" customHeight="1" s="23"/>
+    <row r="326" ht="15.75" customHeight="1" s="23"/>
+    <row r="327" ht="15.75" customHeight="1" s="23"/>
+    <row r="328" ht="15.75" customHeight="1" s="23"/>
+    <row r="329" ht="15.75" customHeight="1" s="23"/>
+    <row r="330" ht="15.75" customHeight="1" s="23"/>
+    <row r="331" ht="15.75" customHeight="1" s="23"/>
+    <row r="332" ht="15.75" customHeight="1" s="23"/>
+    <row r="333" ht="15.75" customHeight="1" s="23"/>
+    <row r="334" ht="15.75" customHeight="1" s="23"/>
+    <row r="335" ht="15.75" customHeight="1" s="23"/>
+    <row r="336" ht="15.75" customHeight="1" s="23"/>
+    <row r="337" ht="15.75" customHeight="1" s="23"/>
+    <row r="338" ht="15.75" customHeight="1" s="23"/>
+    <row r="339" ht="15.75" customHeight="1" s="23"/>
+    <row r="340" ht="15.75" customHeight="1" s="23"/>
+    <row r="341" ht="15.75" customHeight="1" s="23"/>
+    <row r="342" ht="15.75" customHeight="1" s="23"/>
+    <row r="343" ht="15.75" customHeight="1" s="23"/>
+    <row r="344" ht="15.75" customHeight="1" s="23"/>
+    <row r="345" ht="15.75" customHeight="1" s="23"/>
+    <row r="346" ht="15.75" customHeight="1" s="23"/>
+    <row r="347" ht="15.75" customHeight="1" s="23"/>
+    <row r="348" ht="15.75" customHeight="1" s="23"/>
+    <row r="349" ht="15.75" customHeight="1" s="23"/>
+    <row r="350" ht="15.75" customHeight="1" s="23"/>
+    <row r="351" ht="15.75" customHeight="1" s="23"/>
+    <row r="352" ht="15.75" customHeight="1" s="23"/>
+    <row r="353" ht="15.75" customHeight="1" s="23"/>
+    <row r="354" ht="15.75" customHeight="1" s="23"/>
+    <row r="355" ht="15.75" customHeight="1" s="23"/>
+    <row r="356" ht="15.75" customHeight="1" s="23"/>
+    <row r="357" ht="15.75" customHeight="1" s="23"/>
+    <row r="358" ht="15.75" customHeight="1" s="23"/>
+    <row r="359" ht="15.75" customHeight="1" s="23"/>
+    <row r="360" ht="15.75" customHeight="1" s="23"/>
+    <row r="361" ht="15.75" customHeight="1" s="23"/>
+    <row r="362" ht="15.75" customHeight="1" s="23"/>
+    <row r="363" ht="15.75" customHeight="1" s="23"/>
+    <row r="364" ht="15.75" customHeight="1" s="23"/>
+    <row r="365" ht="15.75" customHeight="1" s="23"/>
+    <row r="366" ht="15.75" customHeight="1" s="23"/>
+    <row r="367" ht="15.75" customHeight="1" s="23"/>
+    <row r="368" ht="15.75" customHeight="1" s="23"/>
+    <row r="369" ht="15.75" customHeight="1" s="23"/>
+    <row r="370" ht="15.75" customHeight="1" s="23"/>
+    <row r="371" ht="15.75" customHeight="1" s="23"/>
+    <row r="372" ht="15.75" customHeight="1" s="23"/>
+    <row r="373" ht="15.75" customHeight="1" s="23"/>
+    <row r="374" ht="15.75" customHeight="1" s="23"/>
+    <row r="375" ht="15.75" customHeight="1" s="23"/>
+    <row r="376" ht="15.75" customHeight="1" s="23"/>
+    <row r="377" ht="15.75" customHeight="1" s="23"/>
+    <row r="378" ht="15.75" customHeight="1" s="23"/>
+    <row r="379" ht="15.75" customHeight="1" s="23"/>
+    <row r="380" ht="15.75" customHeight="1" s="23"/>
+    <row r="381" ht="15.75" customHeight="1" s="23"/>
+    <row r="382" ht="15.75" customHeight="1" s="23"/>
+    <row r="383" ht="15.75" customHeight="1" s="23"/>
+    <row r="384" ht="15.75" customHeight="1" s="23"/>
+    <row r="385" ht="15.75" customHeight="1" s="23"/>
+    <row r="386" ht="15.75" customHeight="1" s="23"/>
+    <row r="387" ht="15.75" customHeight="1" s="23"/>
+    <row r="388" ht="15.75" customHeight="1" s="23"/>
+    <row r="389" ht="15.75" customHeight="1" s="23"/>
+    <row r="390" ht="15.75" customHeight="1" s="23"/>
+    <row r="391" ht="15.75" customHeight="1" s="23"/>
+    <row r="392" ht="15.75" customHeight="1" s="23"/>
+    <row r="393" ht="15.75" customHeight="1" s="23"/>
+    <row r="394" ht="15.75" customHeight="1" s="23"/>
+    <row r="395" ht="15.75" customHeight="1" s="23"/>
+    <row r="396" ht="15.75" customHeight="1" s="23"/>
+    <row r="397" ht="15.75" customHeight="1" s="23"/>
+    <row r="398" ht="15.75" customHeight="1" s="23"/>
+    <row r="399" ht="15.75" customHeight="1" s="23"/>
+    <row r="400" ht="15.75" customHeight="1" s="23"/>
+    <row r="401" ht="15.75" customHeight="1" s="23"/>
+    <row r="402" ht="15.75" customHeight="1" s="23"/>
+    <row r="403" ht="15.75" customHeight="1" s="23"/>
+    <row r="404" ht="15.75" customHeight="1" s="23"/>
+    <row r="405" ht="15.75" customHeight="1" s="23"/>
+    <row r="406" ht="15.75" customHeight="1" s="23"/>
+    <row r="407" ht="15.75" customHeight="1" s="23"/>
+    <row r="408" ht="15.75" customHeight="1" s="23"/>
+    <row r="409" ht="15.75" customHeight="1" s="23"/>
+    <row r="410" ht="15.75" customHeight="1" s="23"/>
+    <row r="411" ht="15.75" customHeight="1" s="23"/>
+    <row r="412" ht="15.75" customHeight="1" s="23"/>
+    <row r="413" ht="15.75" customHeight="1" s="23"/>
+    <row r="414" ht="15.75" customHeight="1" s="23"/>
+    <row r="415" ht="15.75" customHeight="1" s="23"/>
+    <row r="416" ht="15.75" customHeight="1" s="23"/>
+    <row r="417" ht="15.75" customHeight="1" s="23"/>
+    <row r="418" ht="15.75" customHeight="1" s="23"/>
+    <row r="419" ht="15.75" customHeight="1" s="23"/>
+    <row r="420" ht="15.75" customHeight="1" s="23"/>
+    <row r="421" ht="15.75" customHeight="1" s="23"/>
+    <row r="422" ht="15.75" customHeight="1" s="23"/>
+    <row r="423" ht="15.75" customHeight="1" s="23"/>
+    <row r="424" ht="15.75" customHeight="1" s="23"/>
+    <row r="425" ht="15.75" customHeight="1" s="23"/>
+    <row r="426" ht="15.75" customHeight="1" s="23"/>
+    <row r="427" ht="15.75" customHeight="1" s="23"/>
+    <row r="428" ht="15.75" customHeight="1" s="23"/>
+    <row r="429" ht="15.75" customHeight="1" s="23"/>
+    <row r="430" ht="15.75" customHeight="1" s="23"/>
+    <row r="431" ht="15.75" customHeight="1" s="23"/>
+    <row r="432" ht="15.75" customHeight="1" s="23"/>
+    <row r="433" ht="15.75" customHeight="1" s="23"/>
+    <row r="434" ht="15.75" customHeight="1" s="23"/>
+    <row r="435" ht="15.75" customHeight="1" s="23"/>
+    <row r="436" ht="15.75" customHeight="1" s="23"/>
+    <row r="437" ht="15.75" customHeight="1" s="23"/>
+    <row r="438" ht="15.75" customHeight="1" s="23"/>
+    <row r="439" ht="15.75" customHeight="1" s="23"/>
+    <row r="440" ht="15.75" customHeight="1" s="23"/>
+    <row r="441" ht="15.75" customHeight="1" s="23"/>
+    <row r="442" ht="15.75" customHeight="1" s="23"/>
+    <row r="443" ht="15.75" customHeight="1" s="23"/>
+    <row r="444" ht="15.75" customHeight="1" s="23"/>
+    <row r="445" ht="15.75" customHeight="1" s="23"/>
+    <row r="446" ht="15.75" customHeight="1" s="23"/>
+    <row r="447" ht="15.75" customHeight="1" s="23"/>
+    <row r="448" ht="15.75" customHeight="1" s="23"/>
+    <row r="449" ht="15.75" customHeight="1" s="23"/>
+    <row r="450" ht="15.75" customHeight="1" s="23"/>
+    <row r="451" ht="15.75" customHeight="1" s="23"/>
+    <row r="452" ht="15.75" customHeight="1" s="23"/>
+    <row r="453" ht="15.75" customHeight="1" s="23"/>
+    <row r="454" ht="15.75" customHeight="1" s="23"/>
+    <row r="455" ht="15.75" customHeight="1" s="23"/>
+    <row r="456" ht="15.75" customHeight="1" s="23"/>
+    <row r="457" ht="15.75" customHeight="1" s="23"/>
+    <row r="458" ht="15.75" customHeight="1" s="23"/>
+    <row r="459" ht="15.75" customHeight="1" s="23"/>
+    <row r="460" ht="15.75" customHeight="1" s="23"/>
+    <row r="461" ht="15.75" customHeight="1" s="23"/>
+    <row r="462" ht="15.75" customHeight="1" s="23"/>
+    <row r="463" ht="15.75" customHeight="1" s="23"/>
+    <row r="464" ht="15.75" customHeight="1" s="23"/>
+    <row r="465" ht="15.75" customHeight="1" s="23"/>
+    <row r="466" ht="15.75" customHeight="1" s="23"/>
+    <row r="467" ht="15.75" customHeight="1" s="23"/>
+    <row r="468" ht="15.75" customHeight="1" s="23"/>
+    <row r="469" ht="15.75" customHeight="1" s="23"/>
+    <row r="470" ht="15.75" customHeight="1" s="23"/>
+    <row r="471" ht="15.75" customHeight="1" s="23"/>
+    <row r="472" ht="15.75" customHeight="1" s="23"/>
+    <row r="473" ht="15.75" customHeight="1" s="23"/>
+    <row r="474" ht="15.75" customHeight="1" s="23"/>
+    <row r="475" ht="15.75" customHeight="1" s="23"/>
+    <row r="476" ht="15.75" customHeight="1" s="23"/>
+    <row r="477" ht="15.75" customHeight="1" s="23"/>
+    <row r="478" ht="15.75" customHeight="1" s="23"/>
+    <row r="479" ht="15.75" customHeight="1" s="23"/>
+    <row r="480" ht="15.75" customHeight="1" s="23"/>
+    <row r="481" ht="15.75" customHeight="1" s="23"/>
+    <row r="482" ht="15.75" customHeight="1" s="23"/>
+    <row r="483" ht="15.75" customHeight="1" s="23"/>
+    <row r="484" ht="15.75" customHeight="1" s="23"/>
+    <row r="485" ht="15.75" customHeight="1" s="23"/>
+    <row r="486" ht="15.75" customHeight="1" s="23"/>
+    <row r="487" ht="15.75" customHeight="1" s="23"/>
+    <row r="488" ht="15.75" customHeight="1" s="23"/>
+    <row r="489" ht="15.75" customHeight="1" s="23"/>
+    <row r="490" ht="15.75" customHeight="1" s="23"/>
+    <row r="491" ht="15.75" customHeight="1" s="23"/>
+    <row r="492" ht="15.75" customHeight="1" s="23"/>
+    <row r="493" ht="15.75" customHeight="1" s="23"/>
+    <row r="494" ht="15.75" customHeight="1" s="23"/>
+    <row r="495" ht="15.75" customHeight="1" s="23"/>
+    <row r="496" ht="15.75" customHeight="1" s="23"/>
+    <row r="497" ht="15.75" customHeight="1" s="23"/>
+    <row r="498" ht="15.75" customHeight="1" s="23"/>
+    <row r="499" ht="15.75" customHeight="1" s="23"/>
+    <row r="500" ht="15.75" customHeight="1" s="23"/>
+    <row r="501" ht="15.75" customHeight="1" s="23"/>
+    <row r="502" ht="15.75" customHeight="1" s="23"/>
+    <row r="503" ht="15.75" customHeight="1" s="23"/>
+    <row r="504" ht="15.75" customHeight="1" s="23"/>
+    <row r="505" ht="15.75" customHeight="1" s="23"/>
+    <row r="506" ht="15.75" customHeight="1" s="23"/>
+    <row r="507" ht="15.75" customHeight="1" s="23"/>
+    <row r="508" ht="15.75" customHeight="1" s="23"/>
+    <row r="509" ht="15.75" customHeight="1" s="23"/>
+    <row r="510" ht="15.75" customHeight="1" s="23"/>
+    <row r="511" ht="15.75" customHeight="1" s="23"/>
+    <row r="512" ht="15.75" customHeight="1" s="23"/>
+    <row r="513" ht="15.75" customHeight="1" s="23"/>
+    <row r="514" ht="15.75" customHeight="1" s="23"/>
+    <row r="515" ht="15.75" customHeight="1" s="23"/>
+    <row r="516" ht="15.75" customHeight="1" s="23"/>
+    <row r="517" ht="15.75" customHeight="1" s="23"/>
+    <row r="518" ht="15.75" customHeight="1" s="23"/>
+    <row r="519" ht="15.75" customHeight="1" s="23"/>
+    <row r="520" ht="15.75" customHeight="1" s="23"/>
+    <row r="521" ht="15.75" customHeight="1" s="23"/>
+    <row r="522" ht="15.75" customHeight="1" s="23"/>
+    <row r="523" ht="15.75" customHeight="1" s="23"/>
+    <row r="524" ht="15.75" customHeight="1" s="23"/>
+    <row r="525" ht="15.75" customHeight="1" s="23"/>
+    <row r="526" ht="15.75" customHeight="1" s="23"/>
+    <row r="527" ht="15.75" customHeight="1" s="23"/>
+    <row r="528" ht="15.75" customHeight="1" s="23"/>
+    <row r="529" ht="15.75" customHeight="1" s="23"/>
+    <row r="530" ht="15.75" customHeight="1" s="23"/>
+    <row r="531" ht="15.75" customHeight="1" s="23"/>
+    <row r="532" ht="15.75" customHeight="1" s="23"/>
+    <row r="533" ht="15.75" customHeight="1" s="23"/>
+    <row r="534" ht="15.75" customHeight="1" s="23"/>
+    <row r="535" ht="15.75" customHeight="1" s="23"/>
+    <row r="536" ht="15.75" customHeight="1" s="23"/>
+    <row r="537" ht="15.75" customHeight="1" s="23"/>
+    <row r="538" ht="15.75" customHeight="1" s="23"/>
+    <row r="539" ht="15.75" customHeight="1" s="23"/>
+    <row r="540" ht="15.75" customHeight="1" s="23"/>
+    <row r="541" ht="15.75" customHeight="1" s="23"/>
+    <row r="542" ht="15.75" customHeight="1" s="23"/>
+    <row r="543" ht="15.75" customHeight="1" s="23"/>
+    <row r="544" ht="15.75" customHeight="1" s="23"/>
+    <row r="545" ht="15.75" customHeight="1" s="23"/>
+    <row r="546" ht="15.75" customHeight="1" s="23"/>
+    <row r="547" ht="15.75" customHeight="1" s="23"/>
+    <row r="548" ht="15.75" customHeight="1" s="23"/>
+    <row r="549" ht="15.75" customHeight="1" s="23"/>
+    <row r="550" ht="15.75" customHeight="1" s="23"/>
+    <row r="551" ht="15.75" customHeight="1" s="23"/>
+    <row r="552" ht="15.75" customHeight="1" s="23"/>
+    <row r="553" ht="15.75" customHeight="1" s="23"/>
+    <row r="554" ht="15.75" customHeight="1" s="23"/>
+    <row r="555" ht="15.75" customHeight="1" s="23"/>
+    <row r="556" ht="15.75" customHeight="1" s="23"/>
+    <row r="557" ht="15.75" customHeight="1" s="23"/>
+    <row r="558" ht="15.75" customHeight="1" s="23"/>
+    <row r="559" ht="15.75" customHeight="1" s="23"/>
+    <row r="560" ht="15.75" customHeight="1" s="23"/>
+    <row r="561" ht="15.75" customHeight="1" s="23"/>
+    <row r="562" ht="15.75" customHeight="1" s="23"/>
+    <row r="563" ht="15.75" customHeight="1" s="23"/>
+    <row r="564" ht="15.75" customHeight="1" s="23"/>
+    <row r="565" ht="15.75" customHeight="1" s="23"/>
+    <row r="566" ht="15.75" customHeight="1" s="23"/>
+    <row r="567" ht="15.75" customHeight="1" s="23"/>
+    <row r="568" ht="15.75" customHeight="1" s="23"/>
+    <row r="569" ht="15.75" customHeight="1" s="23"/>
+    <row r="570" ht="15.75" customHeight="1" s="23"/>
+    <row r="571" ht="15.75" customHeight="1" s="23"/>
+    <row r="572" ht="15.75" customHeight="1" s="23"/>
+    <row r="573" ht="15.75" customHeight="1" s="23"/>
+    <row r="574" ht="15.75" customHeight="1" s="23"/>
+    <row r="575" ht="15.75" customHeight="1" s="23"/>
+    <row r="576" ht="15.75" customHeight="1" s="23"/>
+    <row r="577" ht="15.75" customHeight="1" s="23"/>
+    <row r="578" ht="15.75" customHeight="1" s="23"/>
+    <row r="579" ht="15.75" customHeight="1" s="23"/>
+    <row r="580" ht="15.75" customHeight="1" s="23"/>
+    <row r="581" ht="15.75" customHeight="1" s="23"/>
+    <row r="582" ht="15.75" customHeight="1" s="23"/>
+    <row r="583" ht="15.75" customHeight="1" s="23"/>
+    <row r="584" ht="15.75" customHeight="1" s="23"/>
+    <row r="585" ht="15.75" customHeight="1" s="23"/>
+    <row r="586" ht="15.75" customHeight="1" s="23"/>
+    <row r="587" ht="15.75" customHeight="1" s="23"/>
+    <row r="588" ht="15.75" customHeight="1" s="23"/>
+    <row r="589" ht="15.75" customHeight="1" s="23"/>
+    <row r="590" ht="15.75" customHeight="1" s="23"/>
+    <row r="591" ht="15.75" customHeight="1" s="23"/>
+    <row r="592" ht="15.75" customHeight="1" s="23"/>
+    <row r="593" ht="15.75" customHeight="1" s="23"/>
+    <row r="594" ht="15.75" customHeight="1" s="23"/>
+    <row r="595" ht="15.75" customHeight="1" s="23"/>
+    <row r="596" ht="15.75" customHeight="1" s="23"/>
+    <row r="597" ht="15.75" customHeight="1" s="23"/>
+    <row r="598" ht="15.75" customHeight="1" s="23"/>
+    <row r="599" ht="15.75" customHeight="1" s="23"/>
+    <row r="600" ht="15.75" customHeight="1" s="23"/>
+    <row r="601" ht="15.75" customHeight="1" s="23"/>
+    <row r="602" ht="15.75" customHeight="1" s="23"/>
+    <row r="603" ht="15.75" customHeight="1" s="23"/>
+    <row r="604" ht="15.75" customHeight="1" s="23"/>
+    <row r="605" ht="15.75" customHeight="1" s="23"/>
+    <row r="606" ht="15.75" customHeight="1" s="23"/>
+    <row r="607" ht="15.75" customHeight="1" s="23"/>
+    <row r="608" ht="15.75" customHeight="1" s="23"/>
+    <row r="609" ht="15.75" customHeight="1" s="23"/>
+    <row r="610" ht="15.75" customHeight="1" s="23"/>
+    <row r="611" ht="15.75" customHeight="1" s="23"/>
+    <row r="612" ht="15.75" customHeight="1" s="23"/>
+    <row r="613" ht="15.75" customHeight="1" s="23"/>
+    <row r="614" ht="15.75" customHeight="1" s="23"/>
+    <row r="615" ht="15.75" customHeight="1" s="23"/>
+    <row r="616" ht="15.75" customHeight="1" s="23"/>
+    <row r="617" ht="15.75" customHeight="1" s="23"/>
+    <row r="618" ht="15.75" customHeight="1" s="23"/>
+    <row r="619" ht="15.75" customHeight="1" s="23"/>
+    <row r="620" ht="15.75" customHeight="1" s="23"/>
+    <row r="621" ht="15.75" customHeight="1" s="23"/>
+    <row r="622" ht="15.75" customHeight="1" s="23"/>
+    <row r="623" ht="15.75" customHeight="1" s="23"/>
+    <row r="624" ht="15.75" customHeight="1" s="23"/>
+    <row r="625" ht="15.75" customHeight="1" s="23"/>
+    <row r="626" ht="15.75" customHeight="1" s="23"/>
+    <row r="627" ht="15.75" customHeight="1" s="23"/>
+    <row r="628" ht="15.75" customHeight="1" s="23"/>
+    <row r="629" ht="15.75" customHeight="1" s="23"/>
+    <row r="630" ht="15.75" customHeight="1" s="23"/>
+    <row r="631" ht="15.75" customHeight="1" s="23"/>
+    <row r="632" ht="15.75" customHeight="1" s="23"/>
+    <row r="633" ht="15.75" customHeight="1" s="23"/>
+    <row r="634" ht="15.75" customHeight="1" s="23"/>
+    <row r="635" ht="15.75" customHeight="1" s="23"/>
+    <row r="636" ht="15.75" customHeight="1" s="23"/>
+    <row r="637" ht="15.75" customHeight="1" s="23"/>
+    <row r="638" ht="15.75" customHeight="1" s="23"/>
+    <row r="639" ht="15.75" customHeight="1" s="23"/>
+    <row r="640" ht="15.75" customHeight="1" s="23"/>
+    <row r="641" ht="15.75" customHeight="1" s="23"/>
+    <row r="642" ht="15.75" customHeight="1" s="23"/>
+    <row r="643" ht="15.75" customHeight="1" s="23"/>
+    <row r="644" ht="15.75" customHeight="1" s="23"/>
+    <row r="645" ht="15.75" customHeight="1" s="23"/>
+    <row r="646" ht="15.75" customHeight="1" s="23"/>
+    <row r="647" ht="15.75" customHeight="1" s="23"/>
+    <row r="648" ht="15.75" customHeight="1" s="23"/>
+    <row r="649" ht="15.75" customHeight="1" s="23"/>
+    <row r="650" ht="15.75" customHeight="1" s="23"/>
+    <row r="651" ht="15.75" customHeight="1" s="23"/>
+    <row r="652" ht="15.75" customHeight="1" s="23"/>
+    <row r="653" ht="15.75" customHeight="1" s="23"/>
+    <row r="654" ht="15.75" customHeight="1" s="23"/>
+    <row r="655" ht="15.75" customHeight="1" s="23"/>
+    <row r="656" ht="15.75" customHeight="1" s="23"/>
+    <row r="657" ht="15.75" customHeight="1" s="23"/>
+    <row r="658" ht="15.75" customHeight="1" s="23"/>
+    <row r="659" ht="15.75" customHeight="1" s="23"/>
+    <row r="660" ht="15.75" customHeight="1" s="23"/>
+    <row r="661" ht="15.75" customHeight="1" s="23"/>
+    <row r="662" ht="15.75" customHeight="1" s="23"/>
+    <row r="663" ht="15.75" customHeight="1" s="23"/>
+    <row r="664" ht="15.75" customHeight="1" s="23"/>
+    <row r="665" ht="15.75" customHeight="1" s="23"/>
+    <row r="666" ht="15.75" customHeight="1" s="23"/>
+    <row r="667" ht="15.75" customHeight="1" s="23"/>
+    <row r="668" ht="15.75" customHeight="1" s="23"/>
+    <row r="669" ht="15.75" customHeight="1" s="23"/>
+    <row r="670" ht="15.75" customHeight="1" s="23"/>
+    <row r="671" ht="15.75" customHeight="1" s="23"/>
+    <row r="672" ht="15.75" customHeight="1" s="23"/>
+    <row r="673" ht="15.75" customHeight="1" s="23"/>
+    <row r="674" ht="15.75" customHeight="1" s="23"/>
+    <row r="675" ht="15.75" customHeight="1" s="23"/>
+    <row r="676" ht="15.75" customHeight="1" s="23"/>
+    <row r="677" ht="15.75" customHeight="1" s="23"/>
+    <row r="678" ht="15.75" customHeight="1" s="23"/>
+    <row r="679" ht="15.75" customHeight="1" s="23"/>
+    <row r="680" ht="15.75" customHeight="1" s="23"/>
+    <row r="681" ht="15.75" customHeight="1" s="23"/>
+    <row r="682" ht="15.75" customHeight="1" s="23"/>
+    <row r="683" ht="15.75" customHeight="1" s="23"/>
+    <row r="684" ht="15.75" customHeight="1" s="23"/>
+    <row r="685" ht="15.75" customHeight="1" s="23"/>
+    <row r="686" ht="15.75" customHeight="1" s="23"/>
+    <row r="687" ht="15.75" customHeight="1" s="23"/>
+    <row r="688" ht="15.75" customHeight="1" s="23"/>
+    <row r="689" ht="15.75" customHeight="1" s="23"/>
+    <row r="690" ht="15.75" customHeight="1" s="23"/>
+    <row r="691" ht="15.75" customHeight="1" s="23"/>
+    <row r="692" ht="15.75" customHeight="1" s="23"/>
+    <row r="693" ht="15.75" customHeight="1" s="23"/>
+    <row r="694" ht="15.75" customHeight="1" s="23"/>
+    <row r="695" ht="15.75" customHeight="1" s="23"/>
+    <row r="696" ht="15.75" customHeight="1" s="23"/>
+    <row r="697" ht="15.75" customHeight="1" s="23"/>
+    <row r="698" ht="15.75" customHeight="1" s="23"/>
+    <row r="699" ht="15.75" customHeight="1" s="23"/>
+    <row r="700" ht="15.75" customHeight="1" s="23"/>
+    <row r="701" ht="15.75" customHeight="1" s="23"/>
+    <row r="702" ht="15.75" customHeight="1" s="23"/>
+    <row r="703" ht="15.75" customHeight="1" s="23"/>
+    <row r="704" ht="15.75" customHeight="1" s="23"/>
+    <row r="705" ht="15.75" customHeight="1" s="23"/>
+    <row r="706" ht="15.75" customHeight="1" s="23"/>
+    <row r="707" ht="15.75" customHeight="1" s="23"/>
+    <row r="708" ht="15.75" customHeight="1" s="23"/>
+    <row r="709" ht="15.75" customHeight="1" s="23"/>
+    <row r="710" ht="15.75" customHeight="1" s="23"/>
+    <row r="711" ht="15.75" customHeight="1" s="23"/>
+    <row r="712" ht="15.75" customHeight="1" s="23"/>
+    <row r="713" ht="15.75" customHeight="1" s="23"/>
+    <row r="714" ht="15.75" customHeight="1" s="23"/>
+    <row r="715" ht="15.75" customHeight="1" s="23"/>
+    <row r="716" ht="15.75" customHeight="1" s="23"/>
+    <row r="717" ht="15.75" customHeight="1" s="23"/>
+    <row r="718" ht="15.75" customHeight="1" s="23"/>
+    <row r="719" ht="15.75" customHeight="1" s="23"/>
+    <row r="720" ht="15.75" customHeight="1" s="23"/>
+    <row r="721" ht="15.75" customHeight="1" s="23"/>
+    <row r="722" ht="15.75" customHeight="1" s="23"/>
+    <row r="723" ht="15.75" customHeight="1" s="23"/>
+    <row r="724" ht="15.75" customHeight="1" s="23"/>
+    <row r="725" ht="15.75" customHeight="1" s="23"/>
+    <row r="726" ht="15.75" customHeight="1" s="23"/>
+    <row r="727" ht="15.75" customHeight="1" s="23"/>
+    <row r="728" ht="15.75" customHeight="1" s="23"/>
+    <row r="729" ht="15.75" customHeight="1" s="23"/>
+    <row r="730" ht="15.75" customHeight="1" s="23"/>
+    <row r="731" ht="15.75" customHeight="1" s="23"/>
+    <row r="732" ht="15.75" customHeight="1" s="23"/>
+    <row r="733" ht="15.75" customHeight="1" s="23"/>
+    <row r="734" ht="15.75" customHeight="1" s="23"/>
+    <row r="735" ht="15.75" customHeight="1" s="23"/>
+    <row r="736" ht="15.75" customHeight="1" s="23"/>
+    <row r="737" ht="15.75" customHeight="1" s="23"/>
+    <row r="738" ht="15.75" customHeight="1" s="23"/>
+    <row r="739" ht="15.75" customHeight="1" s="23"/>
+    <row r="740" ht="15.75" customHeight="1" s="23"/>
+    <row r="741" ht="15.75" customHeight="1" s="23"/>
+    <row r="742" ht="15.75" customHeight="1" s="23"/>
+    <row r="743" ht="15.75" customHeight="1" s="23"/>
+    <row r="744" ht="15.75" customHeight="1" s="23"/>
+    <row r="745" ht="15.75" customHeight="1" s="23"/>
+    <row r="746" ht="15.75" customHeight="1" s="23"/>
+    <row r="747" ht="15.75" customHeight="1" s="23"/>
+    <row r="748" ht="15.75" customHeight="1" s="23"/>
+    <row r="749" ht="15.75" customHeight="1" s="23"/>
+    <row r="750" ht="15.75" customHeight="1" s="23"/>
+    <row r="751" ht="15.75" customHeight="1" s="23"/>
+    <row r="752" ht="15.75" customHeight="1" s="23"/>
+    <row r="753" ht="15.75" customHeight="1" s="23"/>
+    <row r="754" ht="15.75" customHeight="1" s="23"/>
+    <row r="755" ht="15.75" customHeight="1" s="23"/>
+    <row r="756" ht="15.75" customHeight="1" s="23"/>
+    <row r="757" ht="15.75" customHeight="1" s="23"/>
+    <row r="758" ht="15.75" customHeight="1" s="23"/>
+    <row r="759" ht="15.75" customHeight="1" s="23"/>
+    <row r="760" ht="15.75" customHeight="1" s="23"/>
+    <row r="761" ht="15.75" customHeight="1" s="23"/>
+    <row r="762" ht="15.75" customHeight="1" s="23"/>
+    <row r="763" ht="15.75" customHeight="1" s="23"/>
+    <row r="764" ht="15.75" customHeight="1" s="23"/>
+    <row r="765" ht="15.75" customHeight="1" s="23"/>
+    <row r="766" ht="15.75" customHeight="1" s="23"/>
+    <row r="767" ht="15.75" customHeight="1" s="23"/>
+    <row r="768" ht="15.75" customHeight="1" s="23"/>
+    <row r="769" ht="15.75" customHeight="1" s="23"/>
+    <row r="770" ht="15.75" customHeight="1" s="23"/>
+    <row r="771" ht="15.75" customHeight="1" s="23"/>
+    <row r="772" ht="15.75" customHeight="1" s="23"/>
+    <row r="773" ht="15.75" customHeight="1" s="23"/>
+    <row r="774" ht="15.75" customHeight="1" s="23"/>
+    <row r="775" ht="15.75" customHeight="1" s="23"/>
+    <row r="776" ht="15.75" customHeight="1" s="23"/>
+    <row r="777" ht="15.75" customHeight="1" s="23"/>
+    <row r="778" ht="15.75" customHeight="1" s="23"/>
+    <row r="779" ht="15.75" customHeight="1" s="23"/>
+    <row r="780" ht="15.75" customHeight="1" s="23"/>
+    <row r="781" ht="15.75" customHeight="1" s="23"/>
+    <row r="782" ht="15.75" customHeight="1" s="23"/>
+    <row r="783" ht="15.75" customHeight="1" s="23"/>
+    <row r="784" ht="15.75" customHeight="1" s="23"/>
+    <row r="785" ht="15.75" customHeight="1" s="23"/>
+    <row r="786" ht="15.75" customHeight="1" s="23"/>
+    <row r="787" ht="15.75" customHeight="1" s="23"/>
+    <row r="788" ht="15.75" customHeight="1" s="23"/>
+    <row r="789" ht="15.75" customHeight="1" s="23"/>
+    <row r="790" ht="15.75" customHeight="1" s="23"/>
+    <row r="791" ht="15.75" customHeight="1" s="23"/>
+    <row r="792" ht="15.75" customHeight="1" s="23"/>
+    <row r="793" ht="15.75" customHeight="1" s="23"/>
+    <row r="794" ht="15.75" customHeight="1" s="23"/>
+    <row r="795" ht="15.75" customHeight="1" s="23"/>
+    <row r="796" ht="15.75" customHeight="1" s="23"/>
+    <row r="797" ht="15.75" customHeight="1" s="23"/>
+    <row r="798" ht="15.75" customHeight="1" s="23"/>
+    <row r="799" ht="15.75" customHeight="1" s="23"/>
+    <row r="800" ht="15.75" customHeight="1" s="23"/>
+    <row r="801" ht="15.75" customHeight="1" s="23"/>
+    <row r="802" ht="15.75" customHeight="1" s="23"/>
+    <row r="803" ht="15.75" customHeight="1" s="23"/>
+    <row r="804" ht="15.75" customHeight="1" s="23"/>
+    <row r="805" ht="15.75" customHeight="1" s="23"/>
+    <row r="806" ht="15.75" customHeight="1" s="23"/>
+    <row r="807" ht="15.75" customHeight="1" s="23"/>
+    <row r="808" ht="15.75" customHeight="1" s="23"/>
+    <row r="809" ht="15.75" customHeight="1" s="23"/>
+    <row r="810" ht="15.75" customHeight="1" s="23"/>
+    <row r="811" ht="15.75" customHeight="1" s="23"/>
+    <row r="812" ht="15.75" customHeight="1" s="23"/>
+    <row r="813" ht="15.75" customHeight="1" s="23"/>
+    <row r="814" ht="15.75" customHeight="1" s="23"/>
+    <row r="815" ht="15.75" customHeight="1" s="23"/>
+    <row r="816" ht="15.75" customHeight="1" s="23"/>
+    <row r="817" ht="15.75" customHeight="1" s="23"/>
+    <row r="818" ht="15.75" customHeight="1" s="23"/>
+    <row r="819" ht="15.75" customHeight="1" s="23"/>
+    <row r="820" ht="15.75" customHeight="1" s="23"/>
+    <row r="821" ht="15.75" customHeight="1" s="23"/>
+    <row r="822" ht="15.75" customHeight="1" s="23"/>
+    <row r="823" ht="15.75" customHeight="1" s="23"/>
+    <row r="824" ht="15.75" customHeight="1" s="23"/>
+    <row r="825" ht="15.75" customHeight="1" s="23"/>
+    <row r="826" ht="15.75" customHeight="1" s="23"/>
+    <row r="827" ht="15.75" customHeight="1" s="23"/>
+    <row r="828" ht="15.75" customHeight="1" s="23"/>
+    <row r="829" ht="15.75" customHeight="1" s="23"/>
+    <row r="830" ht="15.75" customHeight="1" s="23"/>
+    <row r="831" ht="15.75" customHeight="1" s="23"/>
+    <row r="832" ht="15.75" customHeight="1" s="23"/>
+    <row r="833" ht="15.75" customHeight="1" s="23"/>
+    <row r="834" ht="15.75" customHeight="1" s="23"/>
+    <row r="835" ht="15.75" customHeight="1" s="23"/>
+    <row r="836" ht="15.75" customHeight="1" s="23"/>
+    <row r="837" ht="15.75" customHeight="1" s="23"/>
+    <row r="838" ht="15.75" customHeight="1" s="23"/>
+    <row r="839" ht="15.75" customHeight="1" s="23"/>
+    <row r="840" ht="15.75" customHeight="1" s="23"/>
+    <row r="841" ht="15.75" customHeight="1" s="23"/>
+    <row r="842" ht="15.75" customHeight="1" s="23"/>
+    <row r="843" ht="15.75" customHeight="1" s="23"/>
+    <row r="844" ht="15.75" customHeight="1" s="23"/>
+    <row r="845" ht="15.75" customHeight="1" s="23"/>
+    <row r="846" ht="15.75" customHeight="1" s="23"/>
+    <row r="847" ht="15.75" customHeight="1" s="23"/>
+    <row r="848" ht="15.75" customHeight="1" s="23"/>
+    <row r="849" ht="15.75" customHeight="1" s="23"/>
+    <row r="850" ht="15.75" customHeight="1" s="23"/>
+    <row r="851" ht="15.75" customHeight="1" s="23"/>
+    <row r="852" ht="15.75" customHeight="1" s="23"/>
+    <row r="853" ht="15.75" customHeight="1" s="23"/>
+    <row r="854" ht="15.75" customHeight="1" s="23"/>
+    <row r="855" ht="15.75" customHeight="1" s="23"/>
+    <row r="856" ht="15.75" customHeight="1" s="23"/>
+    <row r="857" ht="15.75" customHeight="1" s="23"/>
+    <row r="858" ht="15.75" customHeight="1" s="23"/>
+    <row r="859" ht="15.75" customHeight="1" s="23"/>
+    <row r="860" ht="15.75" customHeight="1" s="23"/>
+    <row r="861" ht="15.75" customHeight="1" s="23"/>
+    <row r="862" ht="15.75" customHeight="1" s="23"/>
+    <row r="863" ht="15.75" customHeight="1" s="23"/>
+    <row r="864" ht="15.75" customHeight="1" s="23"/>
+    <row r="865" ht="15.75" customHeight="1" s="23"/>
+    <row r="866" ht="15.75" customHeight="1" s="23"/>
+    <row r="867" ht="15.75" customHeight="1" s="23"/>
+    <row r="868" ht="15.75" customHeight="1" s="23"/>
+    <row r="869" ht="15.75" customHeight="1" s="23"/>
+    <row r="870" ht="15.75" customHeight="1" s="23"/>
+    <row r="871" ht="15.75" customHeight="1" s="23"/>
+    <row r="872" ht="15.75" customHeight="1" s="23"/>
+    <row r="873" ht="15.75" customHeight="1" s="23"/>
+    <row r="874" ht="15.75" customHeight="1" s="23"/>
+    <row r="875" ht="15.75" customHeight="1" s="23"/>
+    <row r="876" ht="15.75" customHeight="1" s="23"/>
+    <row r="877" ht="15.75" customHeight="1" s="23"/>
+    <row r="878" ht="15.75" customHeight="1" s="23"/>
+    <row r="879" ht="15.75" customHeight="1" s="23"/>
+    <row r="880" ht="15.75" customHeight="1" s="23"/>
+    <row r="881" ht="15.75" customHeight="1" s="23"/>
+    <row r="882" ht="15.75" customHeight="1" s="23"/>
+    <row r="883" ht="15.75" customHeight="1" s="23"/>
+    <row r="884" ht="15.75" customHeight="1" s="23"/>
+    <row r="885" ht="15.75" customHeight="1" s="23"/>
+    <row r="886" ht="15.75" customHeight="1" s="23"/>
+    <row r="887" ht="15.75" customHeight="1" s="23"/>
+    <row r="888" ht="15.75" customHeight="1" s="23"/>
+    <row r="889" ht="15.75" customHeight="1" s="23"/>
+    <row r="890" ht="15.75" customHeight="1" s="23"/>
+    <row r="891" ht="15.75" customHeight="1" s="23"/>
+    <row r="892" ht="15.75" customHeight="1" s="23"/>
+    <row r="893" ht="15.75" customHeight="1" s="23"/>
+    <row r="894" ht="15.75" customHeight="1" s="23"/>
+    <row r="895" ht="15.75" customHeight="1" s="23"/>
+    <row r="896" ht="15.75" customHeight="1" s="23"/>
+    <row r="897" ht="15.75" customHeight="1" s="23"/>
+    <row r="898" ht="15.75" customHeight="1" s="23"/>
+    <row r="899" ht="15.75" customHeight="1" s="23"/>
+    <row r="900" ht="15.75" customHeight="1" s="23"/>
+    <row r="901" ht="15.75" customHeight="1" s="23"/>
+    <row r="902" ht="15.75" customHeight="1" s="23"/>
+    <row r="903" ht="15.75" customHeight="1" s="23"/>
+    <row r="904" ht="15.75" customHeight="1" s="23"/>
+    <row r="905" ht="15.75" customHeight="1" s="23"/>
+    <row r="906" ht="15.75" customHeight="1" s="23"/>
+    <row r="907" ht="15.75" customHeight="1" s="23"/>
+    <row r="908" ht="15.75" customHeight="1" s="23"/>
+    <row r="909" ht="15.75" customHeight="1" s="23"/>
+    <row r="910" ht="15.75" customHeight="1" s="23"/>
+    <row r="911" ht="15.75" customHeight="1" s="23"/>
+    <row r="912" ht="15.75" customHeight="1" s="23"/>
+    <row r="913" ht="15.75" customHeight="1" s="23"/>
+    <row r="914" ht="15.75" customHeight="1" s="23"/>
+    <row r="915" ht="15.75" customHeight="1" s="23"/>
+    <row r="916" ht="15.75" customHeight="1" s="23"/>
+    <row r="917" ht="15.75" customHeight="1" s="23"/>
+    <row r="918" ht="15.75" customHeight="1" s="23"/>
+    <row r="919" ht="15.75" customHeight="1" s="23"/>
+    <row r="920" ht="15.75" customHeight="1" s="23"/>
+    <row r="921" ht="15.75" customHeight="1" s="23"/>
+    <row r="922" ht="15.75" customHeight="1" s="23"/>
+    <row r="923" ht="15.75" customHeight="1" s="23"/>
+    <row r="924" ht="15.75" customHeight="1" s="23"/>
+    <row r="925" ht="15.75" customHeight="1" s="23"/>
+    <row r="926" ht="15.75" customHeight="1" s="23"/>
+    <row r="927" ht="15.75" customHeight="1" s="23"/>
+    <row r="928" ht="15.75" customHeight="1" s="23"/>
+    <row r="929" ht="15.75" customHeight="1" s="23"/>
+    <row r="930" ht="15.75" customHeight="1" s="23"/>
+    <row r="931" ht="15.75" customHeight="1" s="23"/>
+    <row r="932" ht="15.75" customHeight="1" s="23"/>
+    <row r="933" ht="15.75" customHeight="1" s="23"/>
+    <row r="934" ht="15.75" customHeight="1" s="23"/>
+    <row r="935" ht="15.75" customHeight="1" s="23"/>
+    <row r="936" ht="15.75" customHeight="1" s="23"/>
+    <row r="937" ht="15.75" customHeight="1" s="23"/>
+    <row r="938" ht="15.75" customHeight="1" s="23"/>
+    <row r="939" ht="15.75" customHeight="1" s="23"/>
+    <row r="940" ht="15.75" customHeight="1" s="23"/>
+    <row r="941" ht="15.75" customHeight="1" s="23"/>
+    <row r="942" ht="15.75" customHeight="1" s="23"/>
+    <row r="943" ht="15.75" customHeight="1" s="23"/>
+    <row r="944" ht="15.75" customHeight="1" s="23"/>
+    <row r="945" ht="15.75" customHeight="1" s="23"/>
+    <row r="946" ht="15.75" customHeight="1" s="23"/>
+    <row r="947" ht="15.75" customHeight="1" s="23"/>
+    <row r="948" ht="15.75" customHeight="1" s="23"/>
+    <row r="949" ht="15.75" customHeight="1" s="23"/>
+    <row r="950" ht="15.75" customHeight="1" s="23"/>
+    <row r="951" ht="15.75" customHeight="1" s="23"/>
+    <row r="952" ht="15.75" customHeight="1" s="23"/>
+    <row r="953" ht="15.75" customHeight="1" s="23"/>
+    <row r="954" ht="15.75" customHeight="1" s="23"/>
+    <row r="955" ht="15.75" customHeight="1" s="23"/>
+    <row r="956" ht="15.75" customHeight="1" s="23"/>
+    <row r="957" ht="15.75" customHeight="1" s="23"/>
+    <row r="958" ht="15.75" customHeight="1" s="23"/>
+    <row r="959" ht="15.75" customHeight="1" s="23"/>
+    <row r="960" ht="15.75" customHeight="1" s="23"/>
+    <row r="961" ht="15.75" customHeight="1" s="23"/>
+    <row r="962" ht="15.75" customHeight="1" s="23"/>
+    <row r="963" ht="15.75" customHeight="1" s="23"/>
+    <row r="964" ht="15.75" customHeight="1" s="23"/>
+    <row r="965" ht="15.75" customHeight="1" s="23"/>
+    <row r="966" ht="15.75" customHeight="1" s="23"/>
+    <row r="967" ht="15.75" customHeight="1" s="23"/>
+    <row r="968" ht="15.75" customHeight="1" s="23"/>
+    <row r="969" ht="15.75" customHeight="1" s="23"/>
+    <row r="970" ht="15.75" customHeight="1" s="23"/>
+    <row r="971" ht="15.75" customHeight="1" s="23"/>
+    <row r="972" ht="15.75" customHeight="1" s="23"/>
+    <row r="973" ht="15.75" customHeight="1" s="23"/>
+    <row r="974" ht="15.75" customHeight="1" s="23"/>
+    <row r="975" ht="15.75" customHeight="1" s="23"/>
+    <row r="976" ht="15.75" customHeight="1" s="23"/>
+    <row r="977" ht="15.75" customHeight="1" s="23"/>
+    <row r="978" ht="15.75" customHeight="1" s="23"/>
+    <row r="979" ht="15.75" customHeight="1" s="23"/>
+    <row r="980" ht="15.75" customHeight="1" s="23"/>
+    <row r="981" ht="15.75" customHeight="1" s="23"/>
+    <row r="982" ht="15.75" customHeight="1" s="23"/>
+    <row r="983" ht="15.75" customHeight="1" s="23"/>
+    <row r="984" ht="15.75" customHeight="1" s="23"/>
+    <row r="985" ht="15.75" customHeight="1" s="23"/>
+    <row r="986" ht="15.75" customHeight="1" s="23"/>
+    <row r="987" ht="15.75" customHeight="1" s="23"/>
+    <row r="988" ht="15.75" customHeight="1" s="23"/>
+    <row r="989" ht="15.75" customHeight="1" s="23"/>
+    <row r="990" ht="15.75" customHeight="1" s="23"/>
+    <row r="991" ht="15.75" customHeight="1" s="23"/>
+    <row r="992" ht="15.75" customHeight="1" s="23"/>
+    <row r="993" ht="15.75" customHeight="1" s="23"/>
+    <row r="994" ht="15.75" customHeight="1" s="23"/>
+    <row r="995" ht="15.75" customHeight="1" s="23"/>
+    <row r="996" ht="15.75" customHeight="1" s="23"/>
+    <row r="997" ht="15.75" customHeight="1" s="23"/>
+    <row r="998" ht="15.75" customHeight="1" s="23"/>
+    <row r="999" ht="15.75" customHeight="1" s="23"/>
+    <row r="1000" ht="15.75" customHeight="1" s="23"/>
   </sheetData>
-  <conditionalFormatting sqref="A5:D304">
+  <conditionalFormatting sqref="A5:D1000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$B5="Einnahme"</formula>
     </cfRule>
@@ -3220,33 +4359,33 @@
     <dataValidation sqref="B5:B304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Einnahme,Ausgabe"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Datum" error="Bitte ein Datum aus 2025 eintragen." type="date" operator="between">
-      <formula1>45658</formula1>
-      <formula2>46022</formula2>
+    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Datum - Bitte ein Datum aus 2025 eintragen." type="date">
+      <formula1>45658.0</formula1>
+      <formula2>46022.0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I304"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" style="23" min="1" max="1"/>
+    <col width="12" customWidth="1" style="23" min="2" max="2"/>
+    <col width="30" customWidth="1" style="23" min="3" max="3"/>
+    <col width="14" customWidth="1" style="23" min="4" max="4"/>
+    <col width="3" customWidth="1" style="23" min="5" max="5"/>
+    <col width="20" customWidth="1" style="23" min="6" max="6"/>
+    <col width="16" customWidth="1" style="23" min="7" max="9"/>
+    <col width="8.710000000000001" customWidth="1" style="23" min="10" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3257,13 +4396,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Links jede Einnahme/Ausgabe als eigene Zeile eintragen (Ausgaben mit Minus). Rechts rechnet sich die Monatsübersicht automatisch: Differenz = Einnahmen − Ausgaben.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="23">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Datum</t>
@@ -3309,12 +4444,12 @@
       <c r="A5" s="6" t="n">
         <v>46031</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
@@ -3342,8 +4477,16 @@
       <c r="A6" s="6" t="n">
         <v>46052</v>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="8" t="n"/>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="n">
         <v>-15.9</v>
       </c>
@@ -3367,12 +4510,12 @@
       <c r="A7" s="6" t="n">
         <v>46063</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
@@ -3400,8 +4543,16 @@
       <c r="A8" s="6" t="n">
         <v>46080</v>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="8" t="n"/>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D8" s="9" t="n">
         <v>-15.9</v>
       </c>
@@ -3425,12 +4576,12 @@
       <c r="A9" s="6" t="n">
         <v>46091</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
@@ -3458,8 +4609,16 @@
       <c r="A10" s="6" t="n">
         <v>46092</v>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="8" t="n"/>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n">
         <v>-32.25</v>
       </c>
@@ -3483,8 +4642,16 @@
       <c r="A11" s="6" t="n">
         <v>46112</v>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="8" t="n"/>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="n">
         <v>-15.9</v>
       </c>
@@ -3508,12 +4675,12 @@
       <c r="A12" s="6" t="n">
         <v>46122</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
@@ -3541,12 +4708,12 @@
       <c r="A13" s="6" t="n">
         <v>46132</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Claude</t>
         </is>
@@ -3574,8 +4741,16 @@
       <c r="A14" s="6" t="n">
         <v>46142</v>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="8" t="n"/>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D14" s="9" t="n">
         <v>-15.9</v>
       </c>
@@ -3599,12 +4774,12 @@
       <c r="A15" s="6" t="n">
         <v>46150</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
@@ -3632,8 +4807,16 @@
       <c r="A16" s="6" t="n">
         <v>46154</v>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="8" t="n"/>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D16" s="9" t="n">
         <v>-15.9</v>
       </c>
@@ -3657,25 +4840,33 @@
       <c r="A17" s="6" t="n">
         <v>46161</v>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="8" t="n"/>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D17" s="9" t="n">
         <v>-21.42</v>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Gesamt 2026</t>
         </is>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="17">
         <f>SUM(G5:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="18">
         <f>SUM(H5:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="19">
         <f>SUM(I5:I16)</f>
         <v/>
       </c>
@@ -3684,8 +4875,16 @@
       <c r="A18" s="6" t="n">
         <v>46171</v>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="8" t="n"/>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D18" s="9" t="n">
         <v>-15.9</v>
       </c>
@@ -3694,12 +4893,12 @@
       <c r="A19" s="6" t="n">
         <v>46183</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
@@ -3707,26 +4906,19 @@
       <c r="D19" s="9" t="n">
         <v>560.23</v>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Kontrolle: Einträge außerhalb 2026</t>
-        </is>
-      </c>
-      <c r="I19" s="18">
-        <f>SUM($D$5:$D$304)-SUM(I5:I16)</f>
-        <v/>
-      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="I19" s="20" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
         <v>46191</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>V2T</t>
         </is>
@@ -3734,22 +4926,18 @@
       <c r="D20" s="9" t="n">
         <v>-39.9</v>
       </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>(sollte 0 sein – sonst fehlt bei einer Zeile die Art (Einnahme/Ausgabe) oder das Datum liegt in einem anderen Jahr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+      <c r="F20" s="21" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="23">
       <c r="A21" s="6" t="n">
         <v>46202</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -3758,26 +4946,34 @@
         <v>-7.95</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1" s="23">
       <c r="A22" s="6" t="n">
         <v>46203</v>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="8" t="n"/>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D22" s="9" t="n">
         <v>-15.9</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1" s="23">
       <c r="A23" s="6" t="n">
         <v>46213</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
@@ -3786,16 +4982,16 @@
         <v>178.48</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1" s="23">
       <c r="A24" s="6" t="n">
         <v>46223</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Claude</t>
         </is>
@@ -3804,16 +5000,16 @@
         <v>-21.42</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1" s="23">
       <c r="A25" s="6" t="n">
         <v>46232</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Whoop</t>
         </is>
@@ -3822,26 +5018,34 @@
         <v>-11.89</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1" s="23">
       <c r="A26" s="6" t="n">
         <v>46234</v>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="8" t="n"/>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D26" s="9" t="n">
         <v>-15.9</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1" s="23">
       <c r="A27" s="6" t="n">
         <v>46244</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
@@ -3850,16 +5054,16 @@
         <v>420.07</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1" s="23">
       <c r="A28" s="6" t="n">
         <v>46252</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>Claude</t>
         </is>
@@ -3868,16 +5072,16 @@
         <v>-21.42</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1" s="23">
       <c r="A29" s="6" t="n">
         <v>46262</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>Whoop</t>
         </is>
@@ -3886,26 +5090,34 @@
         <v>-11.89</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1" s="23">
       <c r="A30" s="6" t="n">
         <v>46265</v>
       </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="8" t="n"/>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D30" s="9" t="n">
         <v>-15.9</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1" s="23">
       <c r="A31" s="6" t="n">
         <v>46275</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
@@ -3914,16 +5126,16 @@
         <v>344.78</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1" s="23">
       <c r="A32" s="6" t="n">
         <v>46283</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>Claude</t>
         </is>
@@ -3932,16 +5144,16 @@
         <v>-21.42</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1" s="23">
       <c r="A33" s="6" t="n">
         <v>46294</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>Ausgabe</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>Whoop</t>
         </is>
@@ -3950,26 +5162,34 @@
         <v>-11.89</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1" s="23">
       <c r="A34" s="6" t="n">
         <v>46295</v>
       </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="8" t="n"/>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Kontoführung</t>
+        </is>
+      </c>
       <c r="D34" s="9" t="n">
         <v>-15.9</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1" s="23">
       <c r="A35" s="6" t="n">
         <v>46304</v>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>Einnahme</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
@@ -3978,1622 +5198,2180 @@
         <v>215.33</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1" s="23">
       <c r="A36" s="6" t="n"/>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="8" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="15" t="n"/>
       <c r="D36" s="9" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1" s="23">
       <c r="A37" s="6" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="8" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="15" t="n"/>
       <c r="D37" s="9" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1" s="23">
       <c r="A38" s="6" t="n"/>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="8" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="15" t="n"/>
       <c r="D38" s="9" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1" s="23">
       <c r="A39" s="6" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="8" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="15" t="n"/>
       <c r="D39" s="9" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1" s="23">
       <c r="A40" s="6" t="n"/>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="8" t="n"/>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="15" t="n"/>
       <c r="D40" s="9" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1" s="23">
       <c r="A41" s="6" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="8" t="n"/>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="15" t="n"/>
       <c r="D41" s="9" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1" s="23">
       <c r="A42" s="6" t="n"/>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="8" t="n"/>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="15" t="n"/>
       <c r="D42" s="9" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1" s="23">
       <c r="A43" s="6" t="n"/>
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="8" t="n"/>
+      <c r="B43" s="14" t="n"/>
+      <c r="C43" s="15" t="n"/>
       <c r="D43" s="9" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1" s="23">
       <c r="A44" s="6" t="n"/>
-      <c r="B44" s="7" t="n"/>
-      <c r="C44" s="8" t="n"/>
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="15" t="n"/>
       <c r="D44" s="9" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1" s="23">
       <c r="A45" s="6" t="n"/>
-      <c r="B45" s="7" t="n"/>
-      <c r="C45" s="8" t="n"/>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="15" t="n"/>
       <c r="D45" s="9" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1" s="23">
       <c r="A46" s="6" t="n"/>
-      <c r="B46" s="7" t="n"/>
-      <c r="C46" s="8" t="n"/>
+      <c r="B46" s="14" t="n"/>
+      <c r="C46" s="15" t="n"/>
       <c r="D46" s="9" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1" s="23">
       <c r="A47" s="6" t="n"/>
-      <c r="B47" s="7" t="n"/>
-      <c r="C47" s="8" t="n"/>
+      <c r="B47" s="14" t="n"/>
+      <c r="C47" s="15" t="n"/>
       <c r="D47" s="9" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1" s="23">
       <c r="A48" s="6" t="n"/>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="8" t="n"/>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="15" t="n"/>
       <c r="D48" s="9" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1" s="23">
       <c r="A49" s="6" t="n"/>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="8" t="n"/>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="15" t="n"/>
       <c r="D49" s="9" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1" s="23">
       <c r="A50" s="6" t="n"/>
-      <c r="B50" s="7" t="n"/>
-      <c r="C50" s="8" t="n"/>
+      <c r="B50" s="14" t="n"/>
+      <c r="C50" s="15" t="n"/>
       <c r="D50" s="9" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1" s="23">
       <c r="A51" s="6" t="n"/>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="8" t="n"/>
+      <c r="B51" s="14" t="n"/>
+      <c r="C51" s="15" t="n"/>
       <c r="D51" s="9" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1" s="23">
       <c r="A52" s="6" t="n"/>
-      <c r="B52" s="7" t="n"/>
-      <c r="C52" s="8" t="n"/>
+      <c r="B52" s="14" t="n"/>
+      <c r="C52" s="15" t="n"/>
       <c r="D52" s="9" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1" s="23">
       <c r="A53" s="6" t="n"/>
-      <c r="B53" s="7" t="n"/>
-      <c r="C53" s="8" t="n"/>
+      <c r="B53" s="14" t="n"/>
+      <c r="C53" s="15" t="n"/>
       <c r="D53" s="9" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1" s="23">
       <c r="A54" s="6" t="n"/>
-      <c r="B54" s="7" t="n"/>
-      <c r="C54" s="8" t="n"/>
+      <c r="B54" s="14" t="n"/>
+      <c r="C54" s="15" t="n"/>
       <c r="D54" s="9" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1" s="23">
       <c r="A55" s="6" t="n"/>
-      <c r="B55" s="7" t="n"/>
-      <c r="C55" s="8" t="n"/>
+      <c r="B55" s="14" t="n"/>
+      <c r="C55" s="15" t="n"/>
       <c r="D55" s="9" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1" s="23">
       <c r="A56" s="6" t="n"/>
-      <c r="B56" s="7" t="n"/>
-      <c r="C56" s="8" t="n"/>
+      <c r="B56" s="14" t="n"/>
+      <c r="C56" s="15" t="n"/>
       <c r="D56" s="9" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1" s="23">
       <c r="A57" s="6" t="n"/>
-      <c r="B57" s="7" t="n"/>
-      <c r="C57" s="8" t="n"/>
+      <c r="B57" s="14" t="n"/>
+      <c r="C57" s="15" t="n"/>
       <c r="D57" s="9" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1" s="23">
       <c r="A58" s="6" t="n"/>
-      <c r="B58" s="7" t="n"/>
-      <c r="C58" s="8" t="n"/>
+      <c r="B58" s="14" t="n"/>
+      <c r="C58" s="15" t="n"/>
       <c r="D58" s="9" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1" s="23">
       <c r="A59" s="6" t="n"/>
-      <c r="B59" s="7" t="n"/>
-      <c r="C59" s="8" t="n"/>
+      <c r="B59" s="14" t="n"/>
+      <c r="C59" s="15" t="n"/>
       <c r="D59" s="9" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1" s="23">
       <c r="A60" s="6" t="n"/>
-      <c r="B60" s="7" t="n"/>
-      <c r="C60" s="8" t="n"/>
+      <c r="B60" s="14" t="n"/>
+      <c r="C60" s="15" t="n"/>
       <c r="D60" s="9" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1" s="23">
       <c r="A61" s="6" t="n"/>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="8" t="n"/>
+      <c r="B61" s="14" t="n"/>
+      <c r="C61" s="15" t="n"/>
       <c r="D61" s="9" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1" s="23">
       <c r="A62" s="6" t="n"/>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="8" t="n"/>
+      <c r="B62" s="14" t="n"/>
+      <c r="C62" s="15" t="n"/>
       <c r="D62" s="9" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1" s="23">
       <c r="A63" s="6" t="n"/>
-      <c r="B63" s="7" t="n"/>
-      <c r="C63" s="8" t="n"/>
+      <c r="B63" s="14" t="n"/>
+      <c r="C63" s="15" t="n"/>
       <c r="D63" s="9" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1" s="23">
       <c r="A64" s="6" t="n"/>
-      <c r="B64" s="7" t="n"/>
-      <c r="C64" s="8" t="n"/>
+      <c r="B64" s="14" t="n"/>
+      <c r="C64" s="15" t="n"/>
       <c r="D64" s="9" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1" s="23">
       <c r="A65" s="6" t="n"/>
-      <c r="B65" s="7" t="n"/>
-      <c r="C65" s="8" t="n"/>
+      <c r="B65" s="14" t="n"/>
+      <c r="C65" s="15" t="n"/>
       <c r="D65" s="9" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1" s="23">
       <c r="A66" s="6" t="n"/>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="8" t="n"/>
+      <c r="B66" s="14" t="n"/>
+      <c r="C66" s="15" t="n"/>
       <c r="D66" s="9" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1" s="23">
       <c r="A67" s="6" t="n"/>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="8" t="n"/>
+      <c r="B67" s="14" t="n"/>
+      <c r="C67" s="15" t="n"/>
       <c r="D67" s="9" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1" s="23">
       <c r="A68" s="6" t="n"/>
-      <c r="B68" s="7" t="n"/>
-      <c r="C68" s="8" t="n"/>
+      <c r="B68" s="14" t="n"/>
+      <c r="C68" s="15" t="n"/>
       <c r="D68" s="9" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1" s="23">
       <c r="A69" s="6" t="n"/>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="8" t="n"/>
+      <c r="B69" s="14" t="n"/>
+      <c r="C69" s="15" t="n"/>
       <c r="D69" s="9" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1" s="23">
       <c r="A70" s="6" t="n"/>
-      <c r="B70" s="7" t="n"/>
-      <c r="C70" s="8" t="n"/>
+      <c r="B70" s="14" t="n"/>
+      <c r="C70" s="15" t="n"/>
       <c r="D70" s="9" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1" s="23">
       <c r="A71" s="6" t="n"/>
-      <c r="B71" s="7" t="n"/>
-      <c r="C71" s="8" t="n"/>
+      <c r="B71" s="14" t="n"/>
+      <c r="C71" s="15" t="n"/>
       <c r="D71" s="9" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1" s="23">
       <c r="A72" s="6" t="n"/>
-      <c r="B72" s="7" t="n"/>
-      <c r="C72" s="8" t="n"/>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="15" t="n"/>
       <c r="D72" s="9" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1" s="23">
       <c r="A73" s="6" t="n"/>
-      <c r="B73" s="7" t="n"/>
-      <c r="C73" s="8" t="n"/>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="D73" s="9" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1" s="23">
       <c r="A74" s="6" t="n"/>
-      <c r="B74" s="7" t="n"/>
-      <c r="C74" s="8" t="n"/>
+      <c r="B74" s="14" t="n"/>
+      <c r="C74" s="15" t="n"/>
       <c r="D74" s="9" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1" s="23">
       <c r="A75" s="6" t="n"/>
-      <c r="B75" s="7" t="n"/>
-      <c r="C75" s="8" t="n"/>
+      <c r="B75" s="14" t="n"/>
+      <c r="C75" s="15" t="n"/>
       <c r="D75" s="9" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1" s="23">
       <c r="A76" s="6" t="n"/>
-      <c r="B76" s="7" t="n"/>
-      <c r="C76" s="8" t="n"/>
+      <c r="B76" s="14" t="n"/>
+      <c r="C76" s="15" t="n"/>
       <c r="D76" s="9" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1" s="23">
       <c r="A77" s="6" t="n"/>
-      <c r="B77" s="7" t="n"/>
-      <c r="C77" s="8" t="n"/>
+      <c r="B77" s="14" t="n"/>
+      <c r="C77" s="15" t="n"/>
       <c r="D77" s="9" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1" s="23">
       <c r="A78" s="6" t="n"/>
-      <c r="B78" s="7" t="n"/>
-      <c r="C78" s="8" t="n"/>
+      <c r="B78" s="14" t="n"/>
+      <c r="C78" s="15" t="n"/>
       <c r="D78" s="9" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1" s="23">
       <c r="A79" s="6" t="n"/>
-      <c r="B79" s="7" t="n"/>
-      <c r="C79" s="8" t="n"/>
+      <c r="B79" s="14" t="n"/>
+      <c r="C79" s="15" t="n"/>
       <c r="D79" s="9" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1" s="23">
       <c r="A80" s="6" t="n"/>
-      <c r="B80" s="7" t="n"/>
-      <c r="C80" s="8" t="n"/>
+      <c r="B80" s="14" t="n"/>
+      <c r="C80" s="15" t="n"/>
       <c r="D80" s="9" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1" s="23">
       <c r="A81" s="6" t="n"/>
-      <c r="B81" s="7" t="n"/>
-      <c r="C81" s="8" t="n"/>
+      <c r="B81" s="14" t="n"/>
+      <c r="C81" s="15" t="n"/>
       <c r="D81" s="9" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1" s="23">
       <c r="A82" s="6" t="n"/>
-      <c r="B82" s="7" t="n"/>
-      <c r="C82" s="8" t="n"/>
+      <c r="B82" s="14" t="n"/>
+      <c r="C82" s="15" t="n"/>
       <c r="D82" s="9" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1" s="23">
       <c r="A83" s="6" t="n"/>
-      <c r="B83" s="7" t="n"/>
-      <c r="C83" s="8" t="n"/>
+      <c r="B83" s="14" t="n"/>
+      <c r="C83" s="15" t="n"/>
       <c r="D83" s="9" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1" s="23">
       <c r="A84" s="6" t="n"/>
-      <c r="B84" s="7" t="n"/>
-      <c r="C84" s="8" t="n"/>
+      <c r="B84" s="14" t="n"/>
+      <c r="C84" s="15" t="n"/>
       <c r="D84" s="9" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1" s="23">
       <c r="A85" s="6" t="n"/>
-      <c r="B85" s="7" t="n"/>
-      <c r="C85" s="8" t="n"/>
+      <c r="B85" s="14" t="n"/>
+      <c r="C85" s="15" t="n"/>
       <c r="D85" s="9" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1" s="23">
       <c r="A86" s="6" t="n"/>
-      <c r="B86" s="7" t="n"/>
-      <c r="C86" s="8" t="n"/>
+      <c r="B86" s="14" t="n"/>
+      <c r="C86" s="15" t="n"/>
       <c r="D86" s="9" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1" s="23">
       <c r="A87" s="6" t="n"/>
-      <c r="B87" s="7" t="n"/>
-      <c r="C87" s="8" t="n"/>
+      <c r="B87" s="14" t="n"/>
+      <c r="C87" s="15" t="n"/>
       <c r="D87" s="9" t="n"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1" s="23">
       <c r="A88" s="6" t="n"/>
-      <c r="B88" s="7" t="n"/>
-      <c r="C88" s="8" t="n"/>
+      <c r="B88" s="14" t="n"/>
+      <c r="C88" s="15" t="n"/>
       <c r="D88" s="9" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1" s="23">
       <c r="A89" s="6" t="n"/>
-      <c r="B89" s="7" t="n"/>
-      <c r="C89" s="8" t="n"/>
+      <c r="B89" s="14" t="n"/>
+      <c r="C89" s="15" t="n"/>
       <c r="D89" s="9" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1" s="23">
       <c r="A90" s="6" t="n"/>
-      <c r="B90" s="7" t="n"/>
-      <c r="C90" s="8" t="n"/>
+      <c r="B90" s="14" t="n"/>
+      <c r="C90" s="15" t="n"/>
       <c r="D90" s="9" t="n"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1" s="23">
       <c r="A91" s="6" t="n"/>
-      <c r="B91" s="7" t="n"/>
-      <c r="C91" s="8" t="n"/>
+      <c r="B91" s="14" t="n"/>
+      <c r="C91" s="15" t="n"/>
       <c r="D91" s="9" t="n"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1" s="23">
       <c r="A92" s="6" t="n"/>
-      <c r="B92" s="7" t="n"/>
-      <c r="C92" s="8" t="n"/>
+      <c r="B92" s="14" t="n"/>
+      <c r="C92" s="15" t="n"/>
       <c r="D92" s="9" t="n"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1" s="23">
       <c r="A93" s="6" t="n"/>
-      <c r="B93" s="7" t="n"/>
-      <c r="C93" s="8" t="n"/>
+      <c r="B93" s="14" t="n"/>
+      <c r="C93" s="15" t="n"/>
       <c r="D93" s="9" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1" s="23">
       <c r="A94" s="6" t="n"/>
-      <c r="B94" s="7" t="n"/>
-      <c r="C94" s="8" t="n"/>
+      <c r="B94" s="14" t="n"/>
+      <c r="C94" s="15" t="n"/>
       <c r="D94" s="9" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1" s="23">
       <c r="A95" s="6" t="n"/>
-      <c r="B95" s="7" t="n"/>
-      <c r="C95" s="8" t="n"/>
+      <c r="B95" s="14" t="n"/>
+      <c r="C95" s="15" t="n"/>
       <c r="D95" s="9" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1" s="23">
       <c r="A96" s="6" t="n"/>
-      <c r="B96" s="7" t="n"/>
-      <c r="C96" s="8" t="n"/>
+      <c r="B96" s="14" t="n"/>
+      <c r="C96" s="15" t="n"/>
       <c r="D96" s="9" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1" s="23">
       <c r="A97" s="6" t="n"/>
-      <c r="B97" s="7" t="n"/>
-      <c r="C97" s="8" t="n"/>
+      <c r="B97" s="14" t="n"/>
+      <c r="C97" s="15" t="n"/>
       <c r="D97" s="9" t="n"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1" s="23">
       <c r="A98" s="6" t="n"/>
-      <c r="B98" s="7" t="n"/>
-      <c r="C98" s="8" t="n"/>
+      <c r="B98" s="14" t="n"/>
+      <c r="C98" s="15" t="n"/>
       <c r="D98" s="9" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1" s="23">
       <c r="A99" s="6" t="n"/>
-      <c r="B99" s="7" t="n"/>
-      <c r="C99" s="8" t="n"/>
+      <c r="B99" s="14" t="n"/>
+      <c r="C99" s="15" t="n"/>
       <c r="D99" s="9" t="n"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1" s="23">
       <c r="A100" s="6" t="n"/>
-      <c r="B100" s="7" t="n"/>
-      <c r="C100" s="8" t="n"/>
+      <c r="B100" s="14" t="n"/>
+      <c r="C100" s="15" t="n"/>
       <c r="D100" s="9" t="n"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1" s="23">
       <c r="A101" s="6" t="n"/>
-      <c r="B101" s="7" t="n"/>
-      <c r="C101" s="8" t="n"/>
+      <c r="B101" s="14" t="n"/>
+      <c r="C101" s="15" t="n"/>
       <c r="D101" s="9" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1" s="23">
       <c r="A102" s="6" t="n"/>
-      <c r="B102" s="7" t="n"/>
-      <c r="C102" s="8" t="n"/>
+      <c r="B102" s="14" t="n"/>
+      <c r="C102" s="15" t="n"/>
       <c r="D102" s="9" t="n"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1" s="23">
       <c r="A103" s="6" t="n"/>
-      <c r="B103" s="7" t="n"/>
-      <c r="C103" s="8" t="n"/>
+      <c r="B103" s="14" t="n"/>
+      <c r="C103" s="15" t="n"/>
       <c r="D103" s="9" t="n"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1" s="23">
       <c r="A104" s="6" t="n"/>
-      <c r="B104" s="7" t="n"/>
-      <c r="C104" s="8" t="n"/>
+      <c r="B104" s="14" t="n"/>
+      <c r="C104" s="15" t="n"/>
       <c r="D104" s="9" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1" s="23">
       <c r="A105" s="6" t="n"/>
-      <c r="B105" s="7" t="n"/>
-      <c r="C105" s="8" t="n"/>
+      <c r="B105" s="14" t="n"/>
+      <c r="C105" s="15" t="n"/>
       <c r="D105" s="9" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1" s="23">
       <c r="A106" s="6" t="n"/>
-      <c r="B106" s="7" t="n"/>
-      <c r="C106" s="8" t="n"/>
+      <c r="B106" s="14" t="n"/>
+      <c r="C106" s="15" t="n"/>
       <c r="D106" s="9" t="n"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1" s="23">
       <c r="A107" s="6" t="n"/>
-      <c r="B107" s="7" t="n"/>
-      <c r="C107" s="8" t="n"/>
+      <c r="B107" s="14" t="n"/>
+      <c r="C107" s="15" t="n"/>
       <c r="D107" s="9" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1" s="23">
       <c r="A108" s="6" t="n"/>
-      <c r="B108" s="7" t="n"/>
-      <c r="C108" s="8" t="n"/>
+      <c r="B108" s="14" t="n"/>
+      <c r="C108" s="15" t="n"/>
       <c r="D108" s="9" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1" s="23">
       <c r="A109" s="6" t="n"/>
-      <c r="B109" s="7" t="n"/>
-      <c r="C109" s="8" t="n"/>
+      <c r="B109" s="14" t="n"/>
+      <c r="C109" s="15" t="n"/>
       <c r="D109" s="9" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1" s="23">
       <c r="A110" s="6" t="n"/>
-      <c r="B110" s="7" t="n"/>
-      <c r="C110" s="8" t="n"/>
+      <c r="B110" s="14" t="n"/>
+      <c r="C110" s="15" t="n"/>
       <c r="D110" s="9" t="n"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1" s="23">
       <c r="A111" s="6" t="n"/>
-      <c r="B111" s="7" t="n"/>
-      <c r="C111" s="8" t="n"/>
+      <c r="B111" s="14" t="n"/>
+      <c r="C111" s="15" t="n"/>
       <c r="D111" s="9" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1" s="23">
       <c r="A112" s="6" t="n"/>
-      <c r="B112" s="7" t="n"/>
-      <c r="C112" s="8" t="n"/>
+      <c r="B112" s="14" t="n"/>
+      <c r="C112" s="15" t="n"/>
       <c r="D112" s="9" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1" s="23">
       <c r="A113" s="6" t="n"/>
-      <c r="B113" s="7" t="n"/>
-      <c r="C113" s="8" t="n"/>
+      <c r="B113" s="14" t="n"/>
+      <c r="C113" s="15" t="n"/>
       <c r="D113" s="9" t="n"/>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1" s="23">
       <c r="A114" s="6" t="n"/>
-      <c r="B114" s="7" t="n"/>
-      <c r="C114" s="8" t="n"/>
+      <c r="B114" s="14" t="n"/>
+      <c r="C114" s="15" t="n"/>
       <c r="D114" s="9" t="n"/>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1" s="23">
       <c r="A115" s="6" t="n"/>
-      <c r="B115" s="7" t="n"/>
-      <c r="C115" s="8" t="n"/>
+      <c r="B115" s="14" t="n"/>
+      <c r="C115" s="15" t="n"/>
       <c r="D115" s="9" t="n"/>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1" s="23">
       <c r="A116" s="6" t="n"/>
-      <c r="B116" s="7" t="n"/>
-      <c r="C116" s="8" t="n"/>
+      <c r="B116" s="14" t="n"/>
+      <c r="C116" s="15" t="n"/>
       <c r="D116" s="9" t="n"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1" s="23">
       <c r="A117" s="6" t="n"/>
-      <c r="B117" s="7" t="n"/>
-      <c r="C117" s="8" t="n"/>
+      <c r="B117" s="14" t="n"/>
+      <c r="C117" s="15" t="n"/>
       <c r="D117" s="9" t="n"/>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1" s="23">
       <c r="A118" s="6" t="n"/>
-      <c r="B118" s="7" t="n"/>
-      <c r="C118" s="8" t="n"/>
+      <c r="B118" s="14" t="n"/>
+      <c r="C118" s="15" t="n"/>
       <c r="D118" s="9" t="n"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1" s="23">
       <c r="A119" s="6" t="n"/>
-      <c r="B119" s="7" t="n"/>
-      <c r="C119" s="8" t="n"/>
+      <c r="B119" s="14" t="n"/>
+      <c r="C119" s="15" t="n"/>
       <c r="D119" s="9" t="n"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1" s="23">
       <c r="A120" s="6" t="n"/>
-      <c r="B120" s="7" t="n"/>
-      <c r="C120" s="8" t="n"/>
+      <c r="B120" s="14" t="n"/>
+      <c r="C120" s="15" t="n"/>
       <c r="D120" s="9" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1" s="23">
       <c r="A121" s="6" t="n"/>
-      <c r="B121" s="7" t="n"/>
-      <c r="C121" s="8" t="n"/>
+      <c r="B121" s="14" t="n"/>
+      <c r="C121" s="15" t="n"/>
       <c r="D121" s="9" t="n"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1" s="23">
       <c r="A122" s="6" t="n"/>
-      <c r="B122" s="7" t="n"/>
-      <c r="C122" s="8" t="n"/>
+      <c r="B122" s="14" t="n"/>
+      <c r="C122" s="15" t="n"/>
       <c r="D122" s="9" t="n"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1" s="23">
       <c r="A123" s="6" t="n"/>
-      <c r="B123" s="7" t="n"/>
-      <c r="C123" s="8" t="n"/>
+      <c r="B123" s="14" t="n"/>
+      <c r="C123" s="15" t="n"/>
       <c r="D123" s="9" t="n"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1" s="23">
       <c r="A124" s="6" t="n"/>
-      <c r="B124" s="7" t="n"/>
-      <c r="C124" s="8" t="n"/>
+      <c r="B124" s="14" t="n"/>
+      <c r="C124" s="15" t="n"/>
       <c r="D124" s="9" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1" s="23">
       <c r="A125" s="6" t="n"/>
-      <c r="B125" s="7" t="n"/>
-      <c r="C125" s="8" t="n"/>
+      <c r="B125" s="14" t="n"/>
+      <c r="C125" s="15" t="n"/>
       <c r="D125" s="9" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1" s="23">
       <c r="A126" s="6" t="n"/>
-      <c r="B126" s="7" t="n"/>
-      <c r="C126" s="8" t="n"/>
+      <c r="B126" s="14" t="n"/>
+      <c r="C126" s="15" t="n"/>
       <c r="D126" s="9" t="n"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1" s="23">
       <c r="A127" s="6" t="n"/>
-      <c r="B127" s="7" t="n"/>
-      <c r="C127" s="8" t="n"/>
+      <c r="B127" s="14" t="n"/>
+      <c r="C127" s="15" t="n"/>
       <c r="D127" s="9" t="n"/>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1" s="23">
       <c r="A128" s="6" t="n"/>
-      <c r="B128" s="7" t="n"/>
-      <c r="C128" s="8" t="n"/>
+      <c r="B128" s="14" t="n"/>
+      <c r="C128" s="15" t="n"/>
       <c r="D128" s="9" t="n"/>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1" s="23">
       <c r="A129" s="6" t="n"/>
-      <c r="B129" s="7" t="n"/>
-      <c r="C129" s="8" t="n"/>
+      <c r="B129" s="14" t="n"/>
+      <c r="C129" s="15" t="n"/>
       <c r="D129" s="9" t="n"/>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1" s="23">
       <c r="A130" s="6" t="n"/>
-      <c r="B130" s="7" t="n"/>
-      <c r="C130" s="8" t="n"/>
+      <c r="B130" s="14" t="n"/>
+      <c r="C130" s="15" t="n"/>
       <c r="D130" s="9" t="n"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1" s="23">
       <c r="A131" s="6" t="n"/>
-      <c r="B131" s="7" t="n"/>
-      <c r="C131" s="8" t="n"/>
+      <c r="B131" s="14" t="n"/>
+      <c r="C131" s="15" t="n"/>
       <c r="D131" s="9" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1" s="23">
       <c r="A132" s="6" t="n"/>
-      <c r="B132" s="7" t="n"/>
-      <c r="C132" s="8" t="n"/>
+      <c r="B132" s="14" t="n"/>
+      <c r="C132" s="15" t="n"/>
       <c r="D132" s="9" t="n"/>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1" s="23">
       <c r="A133" s="6" t="n"/>
-      <c r="B133" s="7" t="n"/>
-      <c r="C133" s="8" t="n"/>
+      <c r="B133" s="14" t="n"/>
+      <c r="C133" s="15" t="n"/>
       <c r="D133" s="9" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1" s="23">
       <c r="A134" s="6" t="n"/>
-      <c r="B134" s="7" t="n"/>
-      <c r="C134" s="8" t="n"/>
+      <c r="B134" s="14" t="n"/>
+      <c r="C134" s="15" t="n"/>
       <c r="D134" s="9" t="n"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1" s="23">
       <c r="A135" s="6" t="n"/>
-      <c r="B135" s="7" t="n"/>
-      <c r="C135" s="8" t="n"/>
+      <c r="B135" s="14" t="n"/>
+      <c r="C135" s="15" t="n"/>
       <c r="D135" s="9" t="n"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1" s="23">
       <c r="A136" s="6" t="n"/>
-      <c r="B136" s="7" t="n"/>
-      <c r="C136" s="8" t="n"/>
+      <c r="B136" s="14" t="n"/>
+      <c r="C136" s="15" t="n"/>
       <c r="D136" s="9" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1" s="23">
       <c r="A137" s="6" t="n"/>
-      <c r="B137" s="7" t="n"/>
-      <c r="C137" s="8" t="n"/>
+      <c r="B137" s="14" t="n"/>
+      <c r="C137" s="15" t="n"/>
       <c r="D137" s="9" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1" s="23">
       <c r="A138" s="6" t="n"/>
-      <c r="B138" s="7" t="n"/>
-      <c r="C138" s="8" t="n"/>
+      <c r="B138" s="14" t="n"/>
+      <c r="C138" s="15" t="n"/>
       <c r="D138" s="9" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1" s="23">
       <c r="A139" s="6" t="n"/>
-      <c r="B139" s="7" t="n"/>
-      <c r="C139" s="8" t="n"/>
+      <c r="B139" s="14" t="n"/>
+      <c r="C139" s="15" t="n"/>
       <c r="D139" s="9" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1" s="23">
       <c r="A140" s="6" t="n"/>
-      <c r="B140" s="7" t="n"/>
-      <c r="C140" s="8" t="n"/>
+      <c r="B140" s="14" t="n"/>
+      <c r="C140" s="15" t="n"/>
       <c r="D140" s="9" t="n"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1" s="23">
       <c r="A141" s="6" t="n"/>
-      <c r="B141" s="7" t="n"/>
-      <c r="C141" s="8" t="n"/>
+      <c r="B141" s="14" t="n"/>
+      <c r="C141" s="15" t="n"/>
       <c r="D141" s="9" t="n"/>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1" s="23">
       <c r="A142" s="6" t="n"/>
-      <c r="B142" s="7" t="n"/>
-      <c r="C142" s="8" t="n"/>
+      <c r="B142" s="14" t="n"/>
+      <c r="C142" s="15" t="n"/>
       <c r="D142" s="9" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1" s="23">
       <c r="A143" s="6" t="n"/>
-      <c r="B143" s="7" t="n"/>
-      <c r="C143" s="8" t="n"/>
+      <c r="B143" s="14" t="n"/>
+      <c r="C143" s="15" t="n"/>
       <c r="D143" s="9" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1" s="23">
       <c r="A144" s="6" t="n"/>
-      <c r="B144" s="7" t="n"/>
-      <c r="C144" s="8" t="n"/>
+      <c r="B144" s="14" t="n"/>
+      <c r="C144" s="15" t="n"/>
       <c r="D144" s="9" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1" s="23">
       <c r="A145" s="6" t="n"/>
-      <c r="B145" s="7" t="n"/>
-      <c r="C145" s="8" t="n"/>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="15" t="n"/>
       <c r="D145" s="9" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1" s="23">
       <c r="A146" s="6" t="n"/>
-      <c r="B146" s="7" t="n"/>
-      <c r="C146" s="8" t="n"/>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="15" t="n"/>
       <c r="D146" s="9" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1" s="23">
       <c r="A147" s="6" t="n"/>
-      <c r="B147" s="7" t="n"/>
-      <c r="C147" s="8" t="n"/>
+      <c r="B147" s="14" t="n"/>
+      <c r="C147" s="15" t="n"/>
       <c r="D147" s="9" t="n"/>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1" s="23">
       <c r="A148" s="6" t="n"/>
-      <c r="B148" s="7" t="n"/>
-      <c r="C148" s="8" t="n"/>
+      <c r="B148" s="14" t="n"/>
+      <c r="C148" s="15" t="n"/>
       <c r="D148" s="9" t="n"/>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1" s="23">
       <c r="A149" s="6" t="n"/>
-      <c r="B149" s="7" t="n"/>
-      <c r="C149" s="8" t="n"/>
+      <c r="B149" s="14" t="n"/>
+      <c r="C149" s="15" t="n"/>
       <c r="D149" s="9" t="n"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1" s="23">
       <c r="A150" s="6" t="n"/>
-      <c r="B150" s="7" t="n"/>
-      <c r="C150" s="8" t="n"/>
+      <c r="B150" s="14" t="n"/>
+      <c r="C150" s="15" t="n"/>
       <c r="D150" s="9" t="n"/>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1" s="23">
       <c r="A151" s="6" t="n"/>
-      <c r="B151" s="7" t="n"/>
-      <c r="C151" s="8" t="n"/>
+      <c r="B151" s="14" t="n"/>
+      <c r="C151" s="15" t="n"/>
       <c r="D151" s="9" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1" s="23">
       <c r="A152" s="6" t="n"/>
-      <c r="B152" s="7" t="n"/>
-      <c r="C152" s="8" t="n"/>
+      <c r="B152" s="14" t="n"/>
+      <c r="C152" s="15" t="n"/>
       <c r="D152" s="9" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1" s="23">
       <c r="A153" s="6" t="n"/>
-      <c r="B153" s="7" t="n"/>
-      <c r="C153" s="8" t="n"/>
+      <c r="B153" s="14" t="n"/>
+      <c r="C153" s="15" t="n"/>
       <c r="D153" s="9" t="n"/>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1" s="23">
       <c r="A154" s="6" t="n"/>
-      <c r="B154" s="7" t="n"/>
-      <c r="C154" s="8" t="n"/>
+      <c r="B154" s="14" t="n"/>
+      <c r="C154" s="15" t="n"/>
       <c r="D154" s="9" t="n"/>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1" s="23">
       <c r="A155" s="6" t="n"/>
-      <c r="B155" s="7" t="n"/>
-      <c r="C155" s="8" t="n"/>
+      <c r="B155" s="14" t="n"/>
+      <c r="C155" s="15" t="n"/>
       <c r="D155" s="9" t="n"/>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1" s="23">
       <c r="A156" s="6" t="n"/>
-      <c r="B156" s="7" t="n"/>
-      <c r="C156" s="8" t="n"/>
+      <c r="B156" s="14" t="n"/>
+      <c r="C156" s="15" t="n"/>
       <c r="D156" s="9" t="n"/>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1" s="23">
       <c r="A157" s="6" t="n"/>
-      <c r="B157" s="7" t="n"/>
-      <c r="C157" s="8" t="n"/>
+      <c r="B157" s="14" t="n"/>
+      <c r="C157" s="15" t="n"/>
       <c r="D157" s="9" t="n"/>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1" s="23">
       <c r="A158" s="6" t="n"/>
-      <c r="B158" s="7" t="n"/>
-      <c r="C158" s="8" t="n"/>
+      <c r="B158" s="14" t="n"/>
+      <c r="C158" s="15" t="n"/>
       <c r="D158" s="9" t="n"/>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1" s="23">
       <c r="A159" s="6" t="n"/>
-      <c r="B159" s="7" t="n"/>
-      <c r="C159" s="8" t="n"/>
+      <c r="B159" s="14" t="n"/>
+      <c r="C159" s="15" t="n"/>
       <c r="D159" s="9" t="n"/>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1" s="23">
       <c r="A160" s="6" t="n"/>
-      <c r="B160" s="7" t="n"/>
-      <c r="C160" s="8" t="n"/>
+      <c r="B160" s="14" t="n"/>
+      <c r="C160" s="15" t="n"/>
       <c r="D160" s="9" t="n"/>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1" s="23">
       <c r="A161" s="6" t="n"/>
-      <c r="B161" s="7" t="n"/>
-      <c r="C161" s="8" t="n"/>
+      <c r="B161" s="14" t="n"/>
+      <c r="C161" s="15" t="n"/>
       <c r="D161" s="9" t="n"/>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1" s="23">
       <c r="A162" s="6" t="n"/>
-      <c r="B162" s="7" t="n"/>
-      <c r="C162" s="8" t="n"/>
+      <c r="B162" s="14" t="n"/>
+      <c r="C162" s="15" t="n"/>
       <c r="D162" s="9" t="n"/>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1" s="23">
       <c r="A163" s="6" t="n"/>
-      <c r="B163" s="7" t="n"/>
-      <c r="C163" s="8" t="n"/>
+      <c r="B163" s="14" t="n"/>
+      <c r="C163" s="15" t="n"/>
       <c r="D163" s="9" t="n"/>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1" s="23">
       <c r="A164" s="6" t="n"/>
-      <c r="B164" s="7" t="n"/>
-      <c r="C164" s="8" t="n"/>
+      <c r="B164" s="14" t="n"/>
+      <c r="C164" s="15" t="n"/>
       <c r="D164" s="9" t="n"/>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1" s="23">
       <c r="A165" s="6" t="n"/>
-      <c r="B165" s="7" t="n"/>
-      <c r="C165" s="8" t="n"/>
+      <c r="B165" s="14" t="n"/>
+      <c r="C165" s="15" t="n"/>
       <c r="D165" s="9" t="n"/>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1" s="23">
       <c r="A166" s="6" t="n"/>
-      <c r="B166" s="7" t="n"/>
-      <c r="C166" s="8" t="n"/>
+      <c r="B166" s="14" t="n"/>
+      <c r="C166" s="15" t="n"/>
       <c r="D166" s="9" t="n"/>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1" s="23">
       <c r="A167" s="6" t="n"/>
-      <c r="B167" s="7" t="n"/>
-      <c r="C167" s="8" t="n"/>
+      <c r="B167" s="14" t="n"/>
+      <c r="C167" s="15" t="n"/>
       <c r="D167" s="9" t="n"/>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1" s="23">
       <c r="A168" s="6" t="n"/>
-      <c r="B168" s="7" t="n"/>
-      <c r="C168" s="8" t="n"/>
+      <c r="B168" s="14" t="n"/>
+      <c r="C168" s="15" t="n"/>
       <c r="D168" s="9" t="n"/>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1" s="23">
       <c r="A169" s="6" t="n"/>
-      <c r="B169" s="7" t="n"/>
-      <c r="C169" s="8" t="n"/>
+      <c r="B169" s="14" t="n"/>
+      <c r="C169" s="15" t="n"/>
       <c r="D169" s="9" t="n"/>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1" s="23">
       <c r="A170" s="6" t="n"/>
-      <c r="B170" s="7" t="n"/>
-      <c r="C170" s="8" t="n"/>
+      <c r="B170" s="14" t="n"/>
+      <c r="C170" s="15" t="n"/>
       <c r="D170" s="9" t="n"/>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1" s="23">
       <c r="A171" s="6" t="n"/>
-      <c r="B171" s="7" t="n"/>
-      <c r="C171" s="8" t="n"/>
+      <c r="B171" s="14" t="n"/>
+      <c r="C171" s="15" t="n"/>
       <c r="D171" s="9" t="n"/>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1" s="23">
       <c r="A172" s="6" t="n"/>
-      <c r="B172" s="7" t="n"/>
-      <c r="C172" s="8" t="n"/>
+      <c r="B172" s="14" t="n"/>
+      <c r="C172" s="15" t="n"/>
       <c r="D172" s="9" t="n"/>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1" s="23">
       <c r="A173" s="6" t="n"/>
-      <c r="B173" s="7" t="n"/>
-      <c r="C173" s="8" t="n"/>
+      <c r="B173" s="14" t="n"/>
+      <c r="C173" s="15" t="n"/>
       <c r="D173" s="9" t="n"/>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1" s="23">
       <c r="A174" s="6" t="n"/>
-      <c r="B174" s="7" t="n"/>
-      <c r="C174" s="8" t="n"/>
+      <c r="B174" s="14" t="n"/>
+      <c r="C174" s="15" t="n"/>
       <c r="D174" s="9" t="n"/>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1" s="23">
       <c r="A175" s="6" t="n"/>
-      <c r="B175" s="7" t="n"/>
-      <c r="C175" s="8" t="n"/>
+      <c r="B175" s="14" t="n"/>
+      <c r="C175" s="15" t="n"/>
       <c r="D175" s="9" t="n"/>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1" s="23">
       <c r="A176" s="6" t="n"/>
-      <c r="B176" s="7" t="n"/>
-      <c r="C176" s="8" t="n"/>
+      <c r="B176" s="14" t="n"/>
+      <c r="C176" s="15" t="n"/>
       <c r="D176" s="9" t="n"/>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1" s="23">
       <c r="A177" s="6" t="n"/>
-      <c r="B177" s="7" t="n"/>
-      <c r="C177" s="8" t="n"/>
+      <c r="B177" s="14" t="n"/>
+      <c r="C177" s="15" t="n"/>
       <c r="D177" s="9" t="n"/>
     </row>
-    <row r="178">
+    <row r="178" ht="15.75" customHeight="1" s="23">
       <c r="A178" s="6" t="n"/>
-      <c r="B178" s="7" t="n"/>
-      <c r="C178" s="8" t="n"/>
+      <c r="B178" s="14" t="n"/>
+      <c r="C178" s="15" t="n"/>
       <c r="D178" s="9" t="n"/>
     </row>
-    <row r="179">
+    <row r="179" ht="15.75" customHeight="1" s="23">
       <c r="A179" s="6" t="n"/>
-      <c r="B179" s="7" t="n"/>
-      <c r="C179" s="8" t="n"/>
+      <c r="B179" s="14" t="n"/>
+      <c r="C179" s="15" t="n"/>
       <c r="D179" s="9" t="n"/>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1" s="23">
       <c r="A180" s="6" t="n"/>
-      <c r="B180" s="7" t="n"/>
-      <c r="C180" s="8" t="n"/>
+      <c r="B180" s="14" t="n"/>
+      <c r="C180" s="15" t="n"/>
       <c r="D180" s="9" t="n"/>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1" s="23">
       <c r="A181" s="6" t="n"/>
-      <c r="B181" s="7" t="n"/>
-      <c r="C181" s="8" t="n"/>
+      <c r="B181" s="14" t="n"/>
+      <c r="C181" s="15" t="n"/>
       <c r="D181" s="9" t="n"/>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1" s="23">
       <c r="A182" s="6" t="n"/>
-      <c r="B182" s="7" t="n"/>
-      <c r="C182" s="8" t="n"/>
+      <c r="B182" s="14" t="n"/>
+      <c r="C182" s="15" t="n"/>
       <c r="D182" s="9" t="n"/>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1" s="23">
       <c r="A183" s="6" t="n"/>
-      <c r="B183" s="7" t="n"/>
-      <c r="C183" s="8" t="n"/>
+      <c r="B183" s="14" t="n"/>
+      <c r="C183" s="15" t="n"/>
       <c r="D183" s="9" t="n"/>
     </row>
-    <row r="184">
+    <row r="184" ht="15.75" customHeight="1" s="23">
       <c r="A184" s="6" t="n"/>
-      <c r="B184" s="7" t="n"/>
-      <c r="C184" s="8" t="n"/>
+      <c r="B184" s="14" t="n"/>
+      <c r="C184" s="15" t="n"/>
       <c r="D184" s="9" t="n"/>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1" s="23">
       <c r="A185" s="6" t="n"/>
-      <c r="B185" s="7" t="n"/>
-      <c r="C185" s="8" t="n"/>
+      <c r="B185" s="14" t="n"/>
+      <c r="C185" s="15" t="n"/>
       <c r="D185" s="9" t="n"/>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1" s="23">
       <c r="A186" s="6" t="n"/>
-      <c r="B186" s="7" t="n"/>
-      <c r="C186" s="8" t="n"/>
+      <c r="B186" s="14" t="n"/>
+      <c r="C186" s="15" t="n"/>
       <c r="D186" s="9" t="n"/>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1" s="23">
       <c r="A187" s="6" t="n"/>
-      <c r="B187" s="7" t="n"/>
-      <c r="C187" s="8" t="n"/>
+      <c r="B187" s="14" t="n"/>
+      <c r="C187" s="15" t="n"/>
       <c r="D187" s="9" t="n"/>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1" s="23">
       <c r="A188" s="6" t="n"/>
-      <c r="B188" s="7" t="n"/>
-      <c r="C188" s="8" t="n"/>
+      <c r="B188" s="14" t="n"/>
+      <c r="C188" s="15" t="n"/>
       <c r="D188" s="9" t="n"/>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1" s="23">
       <c r="A189" s="6" t="n"/>
-      <c r="B189" s="7" t="n"/>
-      <c r="C189" s="8" t="n"/>
+      <c r="B189" s="14" t="n"/>
+      <c r="C189" s="15" t="n"/>
       <c r="D189" s="9" t="n"/>
     </row>
-    <row r="190">
+    <row r="190" ht="15.75" customHeight="1" s="23">
       <c r="A190" s="6" t="n"/>
-      <c r="B190" s="7" t="n"/>
-      <c r="C190" s="8" t="n"/>
+      <c r="B190" s="14" t="n"/>
+      <c r="C190" s="15" t="n"/>
       <c r="D190" s="9" t="n"/>
     </row>
-    <row r="191">
+    <row r="191" ht="15.75" customHeight="1" s="23">
       <c r="A191" s="6" t="n"/>
-      <c r="B191" s="7" t="n"/>
-      <c r="C191" s="8" t="n"/>
+      <c r="B191" s="14" t="n"/>
+      <c r="C191" s="15" t="n"/>
       <c r="D191" s="9" t="n"/>
     </row>
-    <row r="192">
+    <row r="192" ht="15.75" customHeight="1" s="23">
       <c r="A192" s="6" t="n"/>
-      <c r="B192" s="7" t="n"/>
-      <c r="C192" s="8" t="n"/>
+      <c r="B192" s="14" t="n"/>
+      <c r="C192" s="15" t="n"/>
       <c r="D192" s="9" t="n"/>
     </row>
-    <row r="193">
+    <row r="193" ht="15.75" customHeight="1" s="23">
       <c r="A193" s="6" t="n"/>
-      <c r="B193" s="7" t="n"/>
-      <c r="C193" s="8" t="n"/>
+      <c r="B193" s="14" t="n"/>
+      <c r="C193" s="15" t="n"/>
       <c r="D193" s="9" t="n"/>
     </row>
-    <row r="194">
+    <row r="194" ht="15.75" customHeight="1" s="23">
       <c r="A194" s="6" t="n"/>
-      <c r="B194" s="7" t="n"/>
-      <c r="C194" s="8" t="n"/>
+      <c r="B194" s="14" t="n"/>
+      <c r="C194" s="15" t="n"/>
       <c r="D194" s="9" t="n"/>
     </row>
-    <row r="195">
+    <row r="195" ht="15.75" customHeight="1" s="23">
       <c r="A195" s="6" t="n"/>
-      <c r="B195" s="7" t="n"/>
-      <c r="C195" s="8" t="n"/>
+      <c r="B195" s="14" t="n"/>
+      <c r="C195" s="15" t="n"/>
       <c r="D195" s="9" t="n"/>
     </row>
-    <row r="196">
+    <row r="196" ht="15.75" customHeight="1" s="23">
       <c r="A196" s="6" t="n"/>
-      <c r="B196" s="7" t="n"/>
-      <c r="C196" s="8" t="n"/>
+      <c r="B196" s="14" t="n"/>
+      <c r="C196" s="15" t="n"/>
       <c r="D196" s="9" t="n"/>
     </row>
-    <row r="197">
+    <row r="197" ht="15.75" customHeight="1" s="23">
       <c r="A197" s="6" t="n"/>
-      <c r="B197" s="7" t="n"/>
-      <c r="C197" s="8" t="n"/>
+      <c r="B197" s="14" t="n"/>
+      <c r="C197" s="15" t="n"/>
       <c r="D197" s="9" t="n"/>
     </row>
-    <row r="198">
+    <row r="198" ht="15.75" customHeight="1" s="23">
       <c r="A198" s="6" t="n"/>
-      <c r="B198" s="7" t="n"/>
-      <c r="C198" s="8" t="n"/>
+      <c r="B198" s="14" t="n"/>
+      <c r="C198" s="15" t="n"/>
       <c r="D198" s="9" t="n"/>
     </row>
-    <row r="199">
+    <row r="199" ht="15.75" customHeight="1" s="23">
       <c r="A199" s="6" t="n"/>
-      <c r="B199" s="7" t="n"/>
-      <c r="C199" s="8" t="n"/>
+      <c r="B199" s="14" t="n"/>
+      <c r="C199" s="15" t="n"/>
       <c r="D199" s="9" t="n"/>
     </row>
-    <row r="200">
+    <row r="200" ht="15.75" customHeight="1" s="23">
       <c r="A200" s="6" t="n"/>
-      <c r="B200" s="7" t="n"/>
-      <c r="C200" s="8" t="n"/>
+      <c r="B200" s="14" t="n"/>
+      <c r="C200" s="15" t="n"/>
       <c r="D200" s="9" t="n"/>
     </row>
-    <row r="201">
+    <row r="201" ht="15.75" customHeight="1" s="23">
       <c r="A201" s="6" t="n"/>
-      <c r="B201" s="7" t="n"/>
-      <c r="C201" s="8" t="n"/>
+      <c r="B201" s="14" t="n"/>
+      <c r="C201" s="15" t="n"/>
       <c r="D201" s="9" t="n"/>
     </row>
-    <row r="202">
+    <row r="202" ht="15.75" customHeight="1" s="23">
       <c r="A202" s="6" t="n"/>
-      <c r="B202" s="7" t="n"/>
-      <c r="C202" s="8" t="n"/>
+      <c r="B202" s="14" t="n"/>
+      <c r="C202" s="15" t="n"/>
       <c r="D202" s="9" t="n"/>
     </row>
-    <row r="203">
+    <row r="203" ht="15.75" customHeight="1" s="23">
       <c r="A203" s="6" t="n"/>
-      <c r="B203" s="7" t="n"/>
-      <c r="C203" s="8" t="n"/>
+      <c r="B203" s="14" t="n"/>
+      <c r="C203" s="15" t="n"/>
       <c r="D203" s="9" t="n"/>
     </row>
-    <row r="204">
+    <row r="204" ht="15.75" customHeight="1" s="23">
       <c r="A204" s="6" t="n"/>
-      <c r="B204" s="7" t="n"/>
-      <c r="C204" s="8" t="n"/>
+      <c r="B204" s="14" t="n"/>
+      <c r="C204" s="15" t="n"/>
       <c r="D204" s="9" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" ht="15.75" customHeight="1" s="23">
       <c r="A205" s="6" t="n"/>
-      <c r="B205" s="7" t="n"/>
-      <c r="C205" s="8" t="n"/>
+      <c r="B205" s="14" t="n"/>
+      <c r="C205" s="15" t="n"/>
       <c r="D205" s="9" t="n"/>
     </row>
-    <row r="206">
+    <row r="206" ht="15.75" customHeight="1" s="23">
       <c r="A206" s="6" t="n"/>
-      <c r="B206" s="7" t="n"/>
-      <c r="C206" s="8" t="n"/>
+      <c r="B206" s="14" t="n"/>
+      <c r="C206" s="15" t="n"/>
       <c r="D206" s="9" t="n"/>
     </row>
-    <row r="207">
+    <row r="207" ht="15.75" customHeight="1" s="23">
       <c r="A207" s="6" t="n"/>
-      <c r="B207" s="7" t="n"/>
-      <c r="C207" s="8" t="n"/>
+      <c r="B207" s="14" t="n"/>
+      <c r="C207" s="15" t="n"/>
       <c r="D207" s="9" t="n"/>
     </row>
-    <row r="208">
+    <row r="208" ht="15.75" customHeight="1" s="23">
       <c r="A208" s="6" t="n"/>
-      <c r="B208" s="7" t="n"/>
-      <c r="C208" s="8" t="n"/>
+      <c r="B208" s="14" t="n"/>
+      <c r="C208" s="15" t="n"/>
       <c r="D208" s="9" t="n"/>
     </row>
-    <row r="209">
+    <row r="209" ht="15.75" customHeight="1" s="23">
       <c r="A209" s="6" t="n"/>
-      <c r="B209" s="7" t="n"/>
-      <c r="C209" s="8" t="n"/>
+      <c r="B209" s="14" t="n"/>
+      <c r="C209" s="15" t="n"/>
       <c r="D209" s="9" t="n"/>
     </row>
-    <row r="210">
+    <row r="210" ht="15.75" customHeight="1" s="23">
       <c r="A210" s="6" t="n"/>
-      <c r="B210" s="7" t="n"/>
-      <c r="C210" s="8" t="n"/>
+      <c r="B210" s="14" t="n"/>
+      <c r="C210" s="15" t="n"/>
       <c r="D210" s="9" t="n"/>
     </row>
-    <row r="211">
+    <row r="211" ht="15.75" customHeight="1" s="23">
       <c r="A211" s="6" t="n"/>
-      <c r="B211" s="7" t="n"/>
-      <c r="C211" s="8" t="n"/>
+      <c r="B211" s="14" t="n"/>
+      <c r="C211" s="15" t="n"/>
       <c r="D211" s="9" t="n"/>
     </row>
-    <row r="212">
+    <row r="212" ht="15.75" customHeight="1" s="23">
       <c r="A212" s="6" t="n"/>
-      <c r="B212" s="7" t="n"/>
-      <c r="C212" s="8" t="n"/>
+      <c r="B212" s="14" t="n"/>
+      <c r="C212" s="15" t="n"/>
       <c r="D212" s="9" t="n"/>
     </row>
-    <row r="213">
+    <row r="213" ht="15.75" customHeight="1" s="23">
       <c r="A213" s="6" t="n"/>
-      <c r="B213" s="7" t="n"/>
-      <c r="C213" s="8" t="n"/>
+      <c r="B213" s="14" t="n"/>
+      <c r="C213" s="15" t="n"/>
       <c r="D213" s="9" t="n"/>
     </row>
-    <row r="214">
+    <row r="214" ht="15.75" customHeight="1" s="23">
       <c r="A214" s="6" t="n"/>
-      <c r="B214" s="7" t="n"/>
-      <c r="C214" s="8" t="n"/>
+      <c r="B214" s="14" t="n"/>
+      <c r="C214" s="15" t="n"/>
       <c r="D214" s="9" t="n"/>
     </row>
-    <row r="215">
+    <row r="215" ht="15.75" customHeight="1" s="23">
       <c r="A215" s="6" t="n"/>
-      <c r="B215" s="7" t="n"/>
-      <c r="C215" s="8" t="n"/>
+      <c r="B215" s="14" t="n"/>
+      <c r="C215" s="15" t="n"/>
       <c r="D215" s="9" t="n"/>
     </row>
-    <row r="216">
+    <row r="216" ht="15.75" customHeight="1" s="23">
       <c r="A216" s="6" t="n"/>
-      <c r="B216" s="7" t="n"/>
-      <c r="C216" s="8" t="n"/>
+      <c r="B216" s="14" t="n"/>
+      <c r="C216" s="15" t="n"/>
       <c r="D216" s="9" t="n"/>
     </row>
-    <row r="217">
+    <row r="217" ht="15.75" customHeight="1" s="23">
       <c r="A217" s="6" t="n"/>
-      <c r="B217" s="7" t="n"/>
-      <c r="C217" s="8" t="n"/>
+      <c r="B217" s="14" t="n"/>
+      <c r="C217" s="15" t="n"/>
       <c r="D217" s="9" t="n"/>
     </row>
-    <row r="218">
+    <row r="218" ht="15.75" customHeight="1" s="23">
       <c r="A218" s="6" t="n"/>
-      <c r="B218" s="7" t="n"/>
-      <c r="C218" s="8" t="n"/>
+      <c r="B218" s="14" t="n"/>
+      <c r="C218" s="15" t="n"/>
       <c r="D218" s="9" t="n"/>
     </row>
-    <row r="219">
+    <row r="219" ht="15.75" customHeight="1" s="23">
       <c r="A219" s="6" t="n"/>
-      <c r="B219" s="7" t="n"/>
-      <c r="C219" s="8" t="n"/>
+      <c r="B219" s="14" t="n"/>
+      <c r="C219" s="15" t="n"/>
       <c r="D219" s="9" t="n"/>
     </row>
-    <row r="220">
+    <row r="220" ht="15.75" customHeight="1" s="23">
       <c r="A220" s="6" t="n"/>
-      <c r="B220" s="7" t="n"/>
-      <c r="C220" s="8" t="n"/>
+      <c r="B220" s="14" t="n"/>
+      <c r="C220" s="15" t="n"/>
       <c r="D220" s="9" t="n"/>
     </row>
-    <row r="221">
+    <row r="221" ht="15.75" customHeight="1" s="23">
       <c r="A221" s="6" t="n"/>
-      <c r="B221" s="7" t="n"/>
-      <c r="C221" s="8" t="n"/>
+      <c r="B221" s="14" t="n"/>
+      <c r="C221" s="15" t="n"/>
       <c r="D221" s="9" t="n"/>
     </row>
-    <row r="222">
+    <row r="222" ht="15.75" customHeight="1" s="23">
       <c r="A222" s="6" t="n"/>
-      <c r="B222" s="7" t="n"/>
-      <c r="C222" s="8" t="n"/>
+      <c r="B222" s="14" t="n"/>
+      <c r="C222" s="15" t="n"/>
       <c r="D222" s="9" t="n"/>
     </row>
-    <row r="223">
+    <row r="223" ht="15.75" customHeight="1" s="23">
       <c r="A223" s="6" t="n"/>
-      <c r="B223" s="7" t="n"/>
-      <c r="C223" s="8" t="n"/>
+      <c r="B223" s="14" t="n"/>
+      <c r="C223" s="15" t="n"/>
       <c r="D223" s="9" t="n"/>
     </row>
-    <row r="224">
+    <row r="224" ht="15.75" customHeight="1" s="23">
       <c r="A224" s="6" t="n"/>
-      <c r="B224" s="7" t="n"/>
-      <c r="C224" s="8" t="n"/>
+      <c r="B224" s="14" t="n"/>
+      <c r="C224" s="15" t="n"/>
       <c r="D224" s="9" t="n"/>
     </row>
-    <row r="225">
+    <row r="225" ht="15.75" customHeight="1" s="23">
       <c r="A225" s="6" t="n"/>
-      <c r="B225" s="7" t="n"/>
-      <c r="C225" s="8" t="n"/>
+      <c r="B225" s="14" t="n"/>
+      <c r="C225" s="15" t="n"/>
       <c r="D225" s="9" t="n"/>
     </row>
-    <row r="226">
+    <row r="226" ht="15.75" customHeight="1" s="23">
       <c r="A226" s="6" t="n"/>
-      <c r="B226" s="7" t="n"/>
-      <c r="C226" s="8" t="n"/>
+      <c r="B226" s="14" t="n"/>
+      <c r="C226" s="15" t="n"/>
       <c r="D226" s="9" t="n"/>
     </row>
-    <row r="227">
+    <row r="227" ht="15.75" customHeight="1" s="23">
       <c r="A227" s="6" t="n"/>
-      <c r="B227" s="7" t="n"/>
-      <c r="C227" s="8" t="n"/>
+      <c r="B227" s="14" t="n"/>
+      <c r="C227" s="15" t="n"/>
       <c r="D227" s="9" t="n"/>
     </row>
-    <row r="228">
+    <row r="228" ht="15.75" customHeight="1" s="23">
       <c r="A228" s="6" t="n"/>
-      <c r="B228" s="7" t="n"/>
-      <c r="C228" s="8" t="n"/>
+      <c r="B228" s="14" t="n"/>
+      <c r="C228" s="15" t="n"/>
       <c r="D228" s="9" t="n"/>
     </row>
-    <row r="229">
+    <row r="229" ht="15.75" customHeight="1" s="23">
       <c r="A229" s="6" t="n"/>
-      <c r="B229" s="7" t="n"/>
-      <c r="C229" s="8" t="n"/>
+      <c r="B229" s="14" t="n"/>
+      <c r="C229" s="15" t="n"/>
       <c r="D229" s="9" t="n"/>
     </row>
-    <row r="230">
+    <row r="230" ht="15.75" customHeight="1" s="23">
       <c r="A230" s="6" t="n"/>
-      <c r="B230" s="7" t="n"/>
-      <c r="C230" s="8" t="n"/>
+      <c r="B230" s="14" t="n"/>
+      <c r="C230" s="15" t="n"/>
       <c r="D230" s="9" t="n"/>
     </row>
-    <row r="231">
+    <row r="231" ht="15.75" customHeight="1" s="23">
       <c r="A231" s="6" t="n"/>
-      <c r="B231" s="7" t="n"/>
-      <c r="C231" s="8" t="n"/>
+      <c r="B231" s="14" t="n"/>
+      <c r="C231" s="15" t="n"/>
       <c r="D231" s="9" t="n"/>
     </row>
-    <row r="232">
+    <row r="232" ht="15.75" customHeight="1" s="23">
       <c r="A232" s="6" t="n"/>
-      <c r="B232" s="7" t="n"/>
-      <c r="C232" s="8" t="n"/>
+      <c r="B232" s="14" t="n"/>
+      <c r="C232" s="15" t="n"/>
       <c r="D232" s="9" t="n"/>
     </row>
-    <row r="233">
+    <row r="233" ht="15.75" customHeight="1" s="23">
       <c r="A233" s="6" t="n"/>
-      <c r="B233" s="7" t="n"/>
-      <c r="C233" s="8" t="n"/>
+      <c r="B233" s="14" t="n"/>
+      <c r="C233" s="15" t="n"/>
       <c r="D233" s="9" t="n"/>
     </row>
-    <row r="234">
+    <row r="234" ht="15.75" customHeight="1" s="23">
       <c r="A234" s="6" t="n"/>
-      <c r="B234" s="7" t="n"/>
-      <c r="C234" s="8" t="n"/>
+      <c r="B234" s="14" t="n"/>
+      <c r="C234" s="15" t="n"/>
       <c r="D234" s="9" t="n"/>
     </row>
-    <row r="235">
+    <row r="235" ht="15.75" customHeight="1" s="23">
       <c r="A235" s="6" t="n"/>
-      <c r="B235" s="7" t="n"/>
-      <c r="C235" s="8" t="n"/>
+      <c r="B235" s="14" t="n"/>
+      <c r="C235" s="15" t="n"/>
       <c r="D235" s="9" t="n"/>
     </row>
-    <row r="236">
-      <c r="A236" s="6" t="n"/>
-      <c r="B236" s="7" t="n"/>
-      <c r="C236" s="8" t="n"/>
-      <c r="D236" s="9" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="6" t="n"/>
-      <c r="B237" s="7" t="n"/>
-      <c r="C237" s="8" t="n"/>
-      <c r="D237" s="9" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="6" t="n"/>
-      <c r="B238" s="7" t="n"/>
-      <c r="C238" s="8" t="n"/>
-      <c r="D238" s="9" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="6" t="n"/>
-      <c r="B239" s="7" t="n"/>
-      <c r="C239" s="8" t="n"/>
-      <c r="D239" s="9" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="6" t="n"/>
-      <c r="B240" s="7" t="n"/>
-      <c r="C240" s="8" t="n"/>
-      <c r="D240" s="9" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="6" t="n"/>
-      <c r="B241" s="7" t="n"/>
-      <c r="C241" s="8" t="n"/>
-      <c r="D241" s="9" t="n"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="6" t="n"/>
-      <c r="B242" s="7" t="n"/>
-      <c r="C242" s="8" t="n"/>
-      <c r="D242" s="9" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="6" t="n"/>
-      <c r="B243" s="7" t="n"/>
-      <c r="C243" s="8" t="n"/>
-      <c r="D243" s="9" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="6" t="n"/>
-      <c r="B244" s="7" t="n"/>
-      <c r="C244" s="8" t="n"/>
-      <c r="D244" s="9" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="6" t="n"/>
-      <c r="B245" s="7" t="n"/>
-      <c r="C245" s="8" t="n"/>
-      <c r="D245" s="9" t="n"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="6" t="n"/>
-      <c r="B246" s="7" t="n"/>
-      <c r="C246" s="8" t="n"/>
-      <c r="D246" s="9" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="6" t="n"/>
-      <c r="B247" s="7" t="n"/>
-      <c r="C247" s="8" t="n"/>
-      <c r="D247" s="9" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="6" t="n"/>
-      <c r="B248" s="7" t="n"/>
-      <c r="C248" s="8" t="n"/>
-      <c r="D248" s="9" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="6" t="n"/>
-      <c r="B249" s="7" t="n"/>
-      <c r="C249" s="8" t="n"/>
-      <c r="D249" s="9" t="n"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="6" t="n"/>
-      <c r="B250" s="7" t="n"/>
-      <c r="C250" s="8" t="n"/>
-      <c r="D250" s="9" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="6" t="n"/>
-      <c r="B251" s="7" t="n"/>
-      <c r="C251" s="8" t="n"/>
-      <c r="D251" s="9" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="6" t="n"/>
-      <c r="B252" s="7" t="n"/>
-      <c r="C252" s="8" t="n"/>
-      <c r="D252" s="9" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="6" t="n"/>
-      <c r="B253" s="7" t="n"/>
-      <c r="C253" s="8" t="n"/>
-      <c r="D253" s="9" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="6" t="n"/>
-      <c r="B254" s="7" t="n"/>
-      <c r="C254" s="8" t="n"/>
-      <c r="D254" s="9" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="6" t="n"/>
-      <c r="B255" s="7" t="n"/>
-      <c r="C255" s="8" t="n"/>
-      <c r="D255" s="9" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="6" t="n"/>
-      <c r="B256" s="7" t="n"/>
-      <c r="C256" s="8" t="n"/>
-      <c r="D256" s="9" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="6" t="n"/>
-      <c r="B257" s="7" t="n"/>
-      <c r="C257" s="8" t="n"/>
-      <c r="D257" s="9" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="6" t="n"/>
-      <c r="B258" s="7" t="n"/>
-      <c r="C258" s="8" t="n"/>
-      <c r="D258" s="9" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="6" t="n"/>
-      <c r="B259" s="7" t="n"/>
-      <c r="C259" s="8" t="n"/>
-      <c r="D259" s="9" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="6" t="n"/>
-      <c r="B260" s="7" t="n"/>
-      <c r="C260" s="8" t="n"/>
-      <c r="D260" s="9" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="6" t="n"/>
-      <c r="B261" s="7" t="n"/>
-      <c r="C261" s="8" t="n"/>
-      <c r="D261" s="9" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="6" t="n"/>
-      <c r="B262" s="7" t="n"/>
-      <c r="C262" s="8" t="n"/>
-      <c r="D262" s="9" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="6" t="n"/>
-      <c r="B263" s="7" t="n"/>
-      <c r="C263" s="8" t="n"/>
-      <c r="D263" s="9" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="6" t="n"/>
-      <c r="B264" s="7" t="n"/>
-      <c r="C264" s="8" t="n"/>
-      <c r="D264" s="9" t="n"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="6" t="n"/>
-      <c r="B265" s="7" t="n"/>
-      <c r="C265" s="8" t="n"/>
-      <c r="D265" s="9" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="6" t="n"/>
-      <c r="B266" s="7" t="n"/>
-      <c r="C266" s="8" t="n"/>
-      <c r="D266" s="9" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="6" t="n"/>
-      <c r="B267" s="7" t="n"/>
-      <c r="C267" s="8" t="n"/>
-      <c r="D267" s="9" t="n"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="6" t="n"/>
-      <c r="B268" s="7" t="n"/>
-      <c r="C268" s="8" t="n"/>
-      <c r="D268" s="9" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="6" t="n"/>
-      <c r="B269" s="7" t="n"/>
-      <c r="C269" s="8" t="n"/>
-      <c r="D269" s="9" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="6" t="n"/>
-      <c r="B270" s="7" t="n"/>
-      <c r="C270" s="8" t="n"/>
-      <c r="D270" s="9" t="n"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="6" t="n"/>
-      <c r="B271" s="7" t="n"/>
-      <c r="C271" s="8" t="n"/>
-      <c r="D271" s="9" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="6" t="n"/>
-      <c r="B272" s="7" t="n"/>
-      <c r="C272" s="8" t="n"/>
-      <c r="D272" s="9" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="6" t="n"/>
-      <c r="B273" s="7" t="n"/>
-      <c r="C273" s="8" t="n"/>
-      <c r="D273" s="9" t="n"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="6" t="n"/>
-      <c r="B274" s="7" t="n"/>
-      <c r="C274" s="8" t="n"/>
-      <c r="D274" s="9" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="6" t="n"/>
-      <c r="B275" s="7" t="n"/>
-      <c r="C275" s="8" t="n"/>
-      <c r="D275" s="9" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="6" t="n"/>
-      <c r="B276" s="7" t="n"/>
-      <c r="C276" s="8" t="n"/>
-      <c r="D276" s="9" t="n"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="6" t="n"/>
-      <c r="B277" s="7" t="n"/>
-      <c r="C277" s="8" t="n"/>
-      <c r="D277" s="9" t="n"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="6" t="n"/>
-      <c r="B278" s="7" t="n"/>
-      <c r="C278" s="8" t="n"/>
-      <c r="D278" s="9" t="n"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="6" t="n"/>
-      <c r="B279" s="7" t="n"/>
-      <c r="C279" s="8" t="n"/>
-      <c r="D279" s="9" t="n"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="6" t="n"/>
-      <c r="B280" s="7" t="n"/>
-      <c r="C280" s="8" t="n"/>
-      <c r="D280" s="9" t="n"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="6" t="n"/>
-      <c r="B281" s="7" t="n"/>
-      <c r="C281" s="8" t="n"/>
-      <c r="D281" s="9" t="n"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="6" t="n"/>
-      <c r="B282" s="7" t="n"/>
-      <c r="C282" s="8" t="n"/>
-      <c r="D282" s="9" t="n"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="6" t="n"/>
-      <c r="B283" s="7" t="n"/>
-      <c r="C283" s="8" t="n"/>
-      <c r="D283" s="9" t="n"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="6" t="n"/>
-      <c r="B284" s="7" t="n"/>
-      <c r="C284" s="8" t="n"/>
-      <c r="D284" s="9" t="n"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="6" t="n"/>
-      <c r="B285" s="7" t="n"/>
-      <c r="C285" s="8" t="n"/>
-      <c r="D285" s="9" t="n"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="6" t="n"/>
-      <c r="B286" s="7" t="n"/>
-      <c r="C286" s="8" t="n"/>
-      <c r="D286" s="9" t="n"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="6" t="n"/>
-      <c r="B287" s="7" t="n"/>
-      <c r="C287" s="8" t="n"/>
-      <c r="D287" s="9" t="n"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="6" t="n"/>
-      <c r="B288" s="7" t="n"/>
-      <c r="C288" s="8" t="n"/>
-      <c r="D288" s="9" t="n"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="6" t="n"/>
-      <c r="B289" s="7" t="n"/>
-      <c r="C289" s="8" t="n"/>
-      <c r="D289" s="9" t="n"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="6" t="n"/>
-      <c r="B290" s="7" t="n"/>
-      <c r="C290" s="8" t="n"/>
-      <c r="D290" s="9" t="n"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="6" t="n"/>
-      <c r="B291" s="7" t="n"/>
-      <c r="C291" s="8" t="n"/>
-      <c r="D291" s="9" t="n"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="6" t="n"/>
-      <c r="B292" s="7" t="n"/>
-      <c r="C292" s="8" t="n"/>
-      <c r="D292" s="9" t="n"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="6" t="n"/>
-      <c r="B293" s="7" t="n"/>
-      <c r="C293" s="8" t="n"/>
-      <c r="D293" s="9" t="n"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="6" t="n"/>
-      <c r="B294" s="7" t="n"/>
-      <c r="C294" s="8" t="n"/>
-      <c r="D294" s="9" t="n"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="6" t="n"/>
-      <c r="B295" s="7" t="n"/>
-      <c r="C295" s="8" t="n"/>
-      <c r="D295" s="9" t="n"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="6" t="n"/>
-      <c r="B296" s="7" t="n"/>
-      <c r="C296" s="8" t="n"/>
-      <c r="D296" s="9" t="n"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="6" t="n"/>
-      <c r="B297" s="7" t="n"/>
-      <c r="C297" s="8" t="n"/>
-      <c r="D297" s="9" t="n"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="6" t="n"/>
-      <c r="B298" s="7" t="n"/>
-      <c r="C298" s="8" t="n"/>
-      <c r="D298" s="9" t="n"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="6" t="n"/>
-      <c r="B299" s="7" t="n"/>
-      <c r="C299" s="8" t="n"/>
-      <c r="D299" s="9" t="n"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="6" t="n"/>
-      <c r="B300" s="7" t="n"/>
-      <c r="C300" s="8" t="n"/>
-      <c r="D300" s="9" t="n"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="6" t="n"/>
-      <c r="B301" s="7" t="n"/>
-      <c r="C301" s="8" t="n"/>
-      <c r="D301" s="9" t="n"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="6" t="n"/>
-      <c r="B302" s="7" t="n"/>
-      <c r="C302" s="8" t="n"/>
-      <c r="D302" s="9" t="n"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="6" t="n"/>
-      <c r="B303" s="7" t="n"/>
-      <c r="C303" s="8" t="n"/>
-      <c r="D303" s="9" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="6" t="n"/>
-      <c r="B304" s="7" t="n"/>
-      <c r="C304" s="8" t="n"/>
-      <c r="D304" s="9" t="n"/>
-    </row>
+    <row r="236" ht="15.75" customHeight="1" s="23">
+      <c r="A236" s="22" t="n"/>
+      <c r="B236" s="22" t="n"/>
+    </row>
+    <row r="237" ht="15.75" customHeight="1" s="23">
+      <c r="A237" s="22" t="n"/>
+      <c r="B237" s="22" t="n"/>
+    </row>
+    <row r="238" ht="15.75" customHeight="1" s="23">
+      <c r="A238" s="22" t="n"/>
+      <c r="B238" s="22" t="n"/>
+    </row>
+    <row r="239" ht="15.75" customHeight="1" s="23">
+      <c r="A239" s="22" t="n"/>
+      <c r="B239" s="22" t="n"/>
+    </row>
+    <row r="240" ht="15.75" customHeight="1" s="23">
+      <c r="A240" s="22" t="n"/>
+      <c r="B240" s="22" t="n"/>
+    </row>
+    <row r="241" ht="15.75" customHeight="1" s="23">
+      <c r="A241" s="22" t="n"/>
+      <c r="B241" s="22" t="n"/>
+    </row>
+    <row r="242" ht="15.75" customHeight="1" s="23">
+      <c r="A242" s="22" t="n"/>
+      <c r="B242" s="22" t="n"/>
+    </row>
+    <row r="243" ht="15.75" customHeight="1" s="23">
+      <c r="A243" s="22" t="n"/>
+      <c r="B243" s="22" t="n"/>
+    </row>
+    <row r="244" ht="15.75" customHeight="1" s="23">
+      <c r="A244" s="22" t="n"/>
+      <c r="B244" s="22" t="n"/>
+    </row>
+    <row r="245" ht="15.75" customHeight="1" s="23">
+      <c r="A245" s="22" t="n"/>
+      <c r="B245" s="22" t="n"/>
+    </row>
+    <row r="246" ht="15.75" customHeight="1" s="23">
+      <c r="A246" s="22" t="n"/>
+      <c r="B246" s="22" t="n"/>
+    </row>
+    <row r="247" ht="15.75" customHeight="1" s="23">
+      <c r="A247" s="22" t="n"/>
+      <c r="B247" s="22" t="n"/>
+    </row>
+    <row r="248" ht="15.75" customHeight="1" s="23">
+      <c r="A248" s="22" t="n"/>
+      <c r="B248" s="22" t="n"/>
+    </row>
+    <row r="249" ht="15.75" customHeight="1" s="23">
+      <c r="A249" s="22" t="n"/>
+      <c r="B249" s="22" t="n"/>
+    </row>
+    <row r="250" ht="15.75" customHeight="1" s="23">
+      <c r="A250" s="22" t="n"/>
+      <c r="B250" s="22" t="n"/>
+    </row>
+    <row r="251" ht="15.75" customHeight="1" s="23">
+      <c r="A251" s="22" t="n"/>
+      <c r="B251" s="22" t="n"/>
+    </row>
+    <row r="252" ht="15.75" customHeight="1" s="23">
+      <c r="A252" s="22" t="n"/>
+      <c r="B252" s="22" t="n"/>
+    </row>
+    <row r="253" ht="15.75" customHeight="1" s="23">
+      <c r="A253" s="22" t="n"/>
+      <c r="B253" s="22" t="n"/>
+    </row>
+    <row r="254" ht="15.75" customHeight="1" s="23">
+      <c r="A254" s="22" t="n"/>
+      <c r="B254" s="22" t="n"/>
+    </row>
+    <row r="255" ht="15.75" customHeight="1" s="23">
+      <c r="A255" s="22" t="n"/>
+      <c r="B255" s="22" t="n"/>
+    </row>
+    <row r="256" ht="15.75" customHeight="1" s="23">
+      <c r="A256" s="22" t="n"/>
+      <c r="B256" s="22" t="n"/>
+    </row>
+    <row r="257" ht="15.75" customHeight="1" s="23">
+      <c r="A257" s="22" t="n"/>
+      <c r="B257" s="22" t="n"/>
+    </row>
+    <row r="258" ht="15.75" customHeight="1" s="23">
+      <c r="A258" s="22" t="n"/>
+      <c r="B258" s="22" t="n"/>
+    </row>
+    <row r="259" ht="15.75" customHeight="1" s="23">
+      <c r="A259" s="22" t="n"/>
+      <c r="B259" s="22" t="n"/>
+    </row>
+    <row r="260" ht="15.75" customHeight="1" s="23">
+      <c r="A260" s="22" t="n"/>
+      <c r="B260" s="22" t="n"/>
+    </row>
+    <row r="261" ht="15.75" customHeight="1" s="23">
+      <c r="A261" s="22" t="n"/>
+      <c r="B261" s="22" t="n"/>
+    </row>
+    <row r="262" ht="15.75" customHeight="1" s="23">
+      <c r="A262" s="22" t="n"/>
+      <c r="B262" s="22" t="n"/>
+    </row>
+    <row r="263" ht="15.75" customHeight="1" s="23">
+      <c r="A263" s="22" t="n"/>
+      <c r="B263" s="22" t="n"/>
+    </row>
+    <row r="264" ht="15.75" customHeight="1" s="23">
+      <c r="A264" s="22" t="n"/>
+      <c r="B264" s="22" t="n"/>
+    </row>
+    <row r="265" ht="15.75" customHeight="1" s="23">
+      <c r="A265" s="22" t="n"/>
+      <c r="B265" s="22" t="n"/>
+    </row>
+    <row r="266" ht="15.75" customHeight="1" s="23">
+      <c r="A266" s="22" t="n"/>
+      <c r="B266" s="22" t="n"/>
+    </row>
+    <row r="267" ht="15.75" customHeight="1" s="23">
+      <c r="A267" s="22" t="n"/>
+      <c r="B267" s="22" t="n"/>
+    </row>
+    <row r="268" ht="15.75" customHeight="1" s="23">
+      <c r="A268" s="22" t="n"/>
+      <c r="B268" s="22" t="n"/>
+    </row>
+    <row r="269" ht="15.75" customHeight="1" s="23">
+      <c r="A269" s="22" t="n"/>
+      <c r="B269" s="22" t="n"/>
+    </row>
+    <row r="270" ht="15.75" customHeight="1" s="23">
+      <c r="A270" s="22" t="n"/>
+      <c r="B270" s="22" t="n"/>
+    </row>
+    <row r="271" ht="15.75" customHeight="1" s="23">
+      <c r="A271" s="22" t="n"/>
+      <c r="B271" s="22" t="n"/>
+    </row>
+    <row r="272" ht="15.75" customHeight="1" s="23">
+      <c r="A272" s="22" t="n"/>
+      <c r="B272" s="22" t="n"/>
+    </row>
+    <row r="273" ht="15.75" customHeight="1" s="23">
+      <c r="A273" s="22" t="n"/>
+      <c r="B273" s="22" t="n"/>
+    </row>
+    <row r="274" ht="15.75" customHeight="1" s="23">
+      <c r="A274" s="22" t="n"/>
+      <c r="B274" s="22" t="n"/>
+    </row>
+    <row r="275" ht="15.75" customHeight="1" s="23">
+      <c r="A275" s="22" t="n"/>
+      <c r="B275" s="22" t="n"/>
+    </row>
+    <row r="276" ht="15.75" customHeight="1" s="23">
+      <c r="A276" s="22" t="n"/>
+      <c r="B276" s="22" t="n"/>
+    </row>
+    <row r="277" ht="15.75" customHeight="1" s="23">
+      <c r="A277" s="22" t="n"/>
+      <c r="B277" s="22" t="n"/>
+    </row>
+    <row r="278" ht="15.75" customHeight="1" s="23">
+      <c r="A278" s="22" t="n"/>
+      <c r="B278" s="22" t="n"/>
+    </row>
+    <row r="279" ht="15.75" customHeight="1" s="23">
+      <c r="A279" s="22" t="n"/>
+      <c r="B279" s="22" t="n"/>
+    </row>
+    <row r="280" ht="15.75" customHeight="1" s="23">
+      <c r="A280" s="22" t="n"/>
+      <c r="B280" s="22" t="n"/>
+    </row>
+    <row r="281" ht="15.75" customHeight="1" s="23">
+      <c r="A281" s="22" t="n"/>
+      <c r="B281" s="22" t="n"/>
+    </row>
+    <row r="282" ht="15.75" customHeight="1" s="23">
+      <c r="A282" s="22" t="n"/>
+      <c r="B282" s="22" t="n"/>
+    </row>
+    <row r="283" ht="15.75" customHeight="1" s="23">
+      <c r="A283" s="22" t="n"/>
+      <c r="B283" s="22" t="n"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1" s="23">
+      <c r="A284" s="22" t="n"/>
+      <c r="B284" s="22" t="n"/>
+    </row>
+    <row r="285" ht="15.75" customHeight="1" s="23">
+      <c r="A285" s="22" t="n"/>
+      <c r="B285" s="22" t="n"/>
+    </row>
+    <row r="286" ht="15.75" customHeight="1" s="23">
+      <c r="A286" s="22" t="n"/>
+      <c r="B286" s="22" t="n"/>
+    </row>
+    <row r="287" ht="15.75" customHeight="1" s="23">
+      <c r="A287" s="22" t="n"/>
+      <c r="B287" s="22" t="n"/>
+    </row>
+    <row r="288" ht="15.75" customHeight="1" s="23">
+      <c r="A288" s="22" t="n"/>
+      <c r="B288" s="22" t="n"/>
+    </row>
+    <row r="289" ht="15.75" customHeight="1" s="23">
+      <c r="A289" s="22" t="n"/>
+      <c r="B289" s="22" t="n"/>
+    </row>
+    <row r="290" ht="15.75" customHeight="1" s="23">
+      <c r="A290" s="22" t="n"/>
+      <c r="B290" s="22" t="n"/>
+    </row>
+    <row r="291" ht="15.75" customHeight="1" s="23">
+      <c r="A291" s="22" t="n"/>
+      <c r="B291" s="22" t="n"/>
+    </row>
+    <row r="292" ht="15.75" customHeight="1" s="23">
+      <c r="A292" s="22" t="n"/>
+      <c r="B292" s="22" t="n"/>
+    </row>
+    <row r="293" ht="15.75" customHeight="1" s="23">
+      <c r="A293" s="22" t="n"/>
+      <c r="B293" s="22" t="n"/>
+    </row>
+    <row r="294" ht="15.75" customHeight="1" s="23">
+      <c r="A294" s="22" t="n"/>
+      <c r="B294" s="22" t="n"/>
+    </row>
+    <row r="295" ht="15.75" customHeight="1" s="23">
+      <c r="A295" s="22" t="n"/>
+      <c r="B295" s="22" t="n"/>
+    </row>
+    <row r="296" ht="15.75" customHeight="1" s="23">
+      <c r="A296" s="22" t="n"/>
+      <c r="B296" s="22" t="n"/>
+    </row>
+    <row r="297" ht="15.75" customHeight="1" s="23">
+      <c r="A297" s="22" t="n"/>
+      <c r="B297" s="22" t="n"/>
+    </row>
+    <row r="298" ht="15.75" customHeight="1" s="23">
+      <c r="A298" s="22" t="n"/>
+      <c r="B298" s="22" t="n"/>
+    </row>
+    <row r="299" ht="15.75" customHeight="1" s="23">
+      <c r="A299" s="22" t="n"/>
+      <c r="B299" s="22" t="n"/>
+    </row>
+    <row r="300" ht="15.75" customHeight="1" s="23">
+      <c r="A300" s="22" t="n"/>
+      <c r="B300" s="22" t="n"/>
+    </row>
+    <row r="301" ht="15.75" customHeight="1" s="23">
+      <c r="A301" s="22" t="n"/>
+      <c r="B301" s="22" t="n"/>
+    </row>
+    <row r="302" ht="15.75" customHeight="1" s="23">
+      <c r="A302" s="22" t="n"/>
+      <c r="B302" s="22" t="n"/>
+    </row>
+    <row r="303" ht="15.75" customHeight="1" s="23">
+      <c r="A303" s="22" t="n"/>
+      <c r="B303" s="22" t="n"/>
+    </row>
+    <row r="304" ht="15.75" customHeight="1" s="23">
+      <c r="A304" s="22" t="n"/>
+      <c r="B304" s="22" t="n"/>
+    </row>
+    <row r="305" ht="15.75" customHeight="1" s="23"/>
+    <row r="306" ht="15.75" customHeight="1" s="23"/>
+    <row r="307" ht="15.75" customHeight="1" s="23"/>
+    <row r="308" ht="15.75" customHeight="1" s="23"/>
+    <row r="309" ht="15.75" customHeight="1" s="23"/>
+    <row r="310" ht="15.75" customHeight="1" s="23"/>
+    <row r="311" ht="15.75" customHeight="1" s="23"/>
+    <row r="312" ht="15.75" customHeight="1" s="23"/>
+    <row r="313" ht="15.75" customHeight="1" s="23"/>
+    <row r="314" ht="15.75" customHeight="1" s="23"/>
+    <row r="315" ht="15.75" customHeight="1" s="23"/>
+    <row r="316" ht="15.75" customHeight="1" s="23"/>
+    <row r="317" ht="15.75" customHeight="1" s="23"/>
+    <row r="318" ht="15.75" customHeight="1" s="23"/>
+    <row r="319" ht="15.75" customHeight="1" s="23"/>
+    <row r="320" ht="15.75" customHeight="1" s="23"/>
+    <row r="321" ht="15.75" customHeight="1" s="23"/>
+    <row r="322" ht="15.75" customHeight="1" s="23"/>
+    <row r="323" ht="15.75" customHeight="1" s="23"/>
+    <row r="324" ht="15.75" customHeight="1" s="23"/>
+    <row r="325" ht="15.75" customHeight="1" s="23"/>
+    <row r="326" ht="15.75" customHeight="1" s="23"/>
+    <row r="327" ht="15.75" customHeight="1" s="23"/>
+    <row r="328" ht="15.75" customHeight="1" s="23"/>
+    <row r="329" ht="15.75" customHeight="1" s="23"/>
+    <row r="330" ht="15.75" customHeight="1" s="23"/>
+    <row r="331" ht="15.75" customHeight="1" s="23"/>
+    <row r="332" ht="15.75" customHeight="1" s="23"/>
+    <row r="333" ht="15.75" customHeight="1" s="23"/>
+    <row r="334" ht="15.75" customHeight="1" s="23"/>
+    <row r="335" ht="15.75" customHeight="1" s="23"/>
+    <row r="336" ht="15.75" customHeight="1" s="23"/>
+    <row r="337" ht="15.75" customHeight="1" s="23"/>
+    <row r="338" ht="15.75" customHeight="1" s="23"/>
+    <row r="339" ht="15.75" customHeight="1" s="23"/>
+    <row r="340" ht="15.75" customHeight="1" s="23"/>
+    <row r="341" ht="15.75" customHeight="1" s="23"/>
+    <row r="342" ht="15.75" customHeight="1" s="23"/>
+    <row r="343" ht="15.75" customHeight="1" s="23"/>
+    <row r="344" ht="15.75" customHeight="1" s="23"/>
+    <row r="345" ht="15.75" customHeight="1" s="23"/>
+    <row r="346" ht="15.75" customHeight="1" s="23"/>
+    <row r="347" ht="15.75" customHeight="1" s="23"/>
+    <row r="348" ht="15.75" customHeight="1" s="23"/>
+    <row r="349" ht="15.75" customHeight="1" s="23"/>
+    <row r="350" ht="15.75" customHeight="1" s="23"/>
+    <row r="351" ht="15.75" customHeight="1" s="23"/>
+    <row r="352" ht="15.75" customHeight="1" s="23"/>
+    <row r="353" ht="15.75" customHeight="1" s="23"/>
+    <row r="354" ht="15.75" customHeight="1" s="23"/>
+    <row r="355" ht="15.75" customHeight="1" s="23"/>
+    <row r="356" ht="15.75" customHeight="1" s="23"/>
+    <row r="357" ht="15.75" customHeight="1" s="23"/>
+    <row r="358" ht="15.75" customHeight="1" s="23"/>
+    <row r="359" ht="15.75" customHeight="1" s="23"/>
+    <row r="360" ht="15.75" customHeight="1" s="23"/>
+    <row r="361" ht="15.75" customHeight="1" s="23"/>
+    <row r="362" ht="15.75" customHeight="1" s="23"/>
+    <row r="363" ht="15.75" customHeight="1" s="23"/>
+    <row r="364" ht="15.75" customHeight="1" s="23"/>
+    <row r="365" ht="15.75" customHeight="1" s="23"/>
+    <row r="366" ht="15.75" customHeight="1" s="23"/>
+    <row r="367" ht="15.75" customHeight="1" s="23"/>
+    <row r="368" ht="15.75" customHeight="1" s="23"/>
+    <row r="369" ht="15.75" customHeight="1" s="23"/>
+    <row r="370" ht="15.75" customHeight="1" s="23"/>
+    <row r="371" ht="15.75" customHeight="1" s="23"/>
+    <row r="372" ht="15.75" customHeight="1" s="23"/>
+    <row r="373" ht="15.75" customHeight="1" s="23"/>
+    <row r="374" ht="15.75" customHeight="1" s="23"/>
+    <row r="375" ht="15.75" customHeight="1" s="23"/>
+    <row r="376" ht="15.75" customHeight="1" s="23"/>
+    <row r="377" ht="15.75" customHeight="1" s="23"/>
+    <row r="378" ht="15.75" customHeight="1" s="23"/>
+    <row r="379" ht="15.75" customHeight="1" s="23"/>
+    <row r="380" ht="15.75" customHeight="1" s="23"/>
+    <row r="381" ht="15.75" customHeight="1" s="23"/>
+    <row r="382" ht="15.75" customHeight="1" s="23"/>
+    <row r="383" ht="15.75" customHeight="1" s="23"/>
+    <row r="384" ht="15.75" customHeight="1" s="23"/>
+    <row r="385" ht="15.75" customHeight="1" s="23"/>
+    <row r="386" ht="15.75" customHeight="1" s="23"/>
+    <row r="387" ht="15.75" customHeight="1" s="23"/>
+    <row r="388" ht="15.75" customHeight="1" s="23"/>
+    <row r="389" ht="15.75" customHeight="1" s="23"/>
+    <row r="390" ht="15.75" customHeight="1" s="23"/>
+    <row r="391" ht="15.75" customHeight="1" s="23"/>
+    <row r="392" ht="15.75" customHeight="1" s="23"/>
+    <row r="393" ht="15.75" customHeight="1" s="23"/>
+    <row r="394" ht="15.75" customHeight="1" s="23"/>
+    <row r="395" ht="15.75" customHeight="1" s="23"/>
+    <row r="396" ht="15.75" customHeight="1" s="23"/>
+    <row r="397" ht="15.75" customHeight="1" s="23"/>
+    <row r="398" ht="15.75" customHeight="1" s="23"/>
+    <row r="399" ht="15.75" customHeight="1" s="23"/>
+    <row r="400" ht="15.75" customHeight="1" s="23"/>
+    <row r="401" ht="15.75" customHeight="1" s="23"/>
+    <row r="402" ht="15.75" customHeight="1" s="23"/>
+    <row r="403" ht="15.75" customHeight="1" s="23"/>
+    <row r="404" ht="15.75" customHeight="1" s="23"/>
+    <row r="405" ht="15.75" customHeight="1" s="23"/>
+    <row r="406" ht="15.75" customHeight="1" s="23"/>
+    <row r="407" ht="15.75" customHeight="1" s="23"/>
+    <row r="408" ht="15.75" customHeight="1" s="23"/>
+    <row r="409" ht="15.75" customHeight="1" s="23"/>
+    <row r="410" ht="15.75" customHeight="1" s="23"/>
+    <row r="411" ht="15.75" customHeight="1" s="23"/>
+    <row r="412" ht="15.75" customHeight="1" s="23"/>
+    <row r="413" ht="15.75" customHeight="1" s="23"/>
+    <row r="414" ht="15.75" customHeight="1" s="23"/>
+    <row r="415" ht="15.75" customHeight="1" s="23"/>
+    <row r="416" ht="15.75" customHeight="1" s="23"/>
+    <row r="417" ht="15.75" customHeight="1" s="23"/>
+    <row r="418" ht="15.75" customHeight="1" s="23"/>
+    <row r="419" ht="15.75" customHeight="1" s="23"/>
+    <row r="420" ht="15.75" customHeight="1" s="23"/>
+    <row r="421" ht="15.75" customHeight="1" s="23"/>
+    <row r="422" ht="15.75" customHeight="1" s="23"/>
+    <row r="423" ht="15.75" customHeight="1" s="23"/>
+    <row r="424" ht="15.75" customHeight="1" s="23"/>
+    <row r="425" ht="15.75" customHeight="1" s="23"/>
+    <row r="426" ht="15.75" customHeight="1" s="23"/>
+    <row r="427" ht="15.75" customHeight="1" s="23"/>
+    <row r="428" ht="15.75" customHeight="1" s="23"/>
+    <row r="429" ht="15.75" customHeight="1" s="23"/>
+    <row r="430" ht="15.75" customHeight="1" s="23"/>
+    <row r="431" ht="15.75" customHeight="1" s="23"/>
+    <row r="432" ht="15.75" customHeight="1" s="23"/>
+    <row r="433" ht="15.75" customHeight="1" s="23"/>
+    <row r="434" ht="15.75" customHeight="1" s="23"/>
+    <row r="435" ht="15.75" customHeight="1" s="23"/>
+    <row r="436" ht="15.75" customHeight="1" s="23"/>
+    <row r="437" ht="15.75" customHeight="1" s="23"/>
+    <row r="438" ht="15.75" customHeight="1" s="23"/>
+    <row r="439" ht="15.75" customHeight="1" s="23"/>
+    <row r="440" ht="15.75" customHeight="1" s="23"/>
+    <row r="441" ht="15.75" customHeight="1" s="23"/>
+    <row r="442" ht="15.75" customHeight="1" s="23"/>
+    <row r="443" ht="15.75" customHeight="1" s="23"/>
+    <row r="444" ht="15.75" customHeight="1" s="23"/>
+    <row r="445" ht="15.75" customHeight="1" s="23"/>
+    <row r="446" ht="15.75" customHeight="1" s="23"/>
+    <row r="447" ht="15.75" customHeight="1" s="23"/>
+    <row r="448" ht="15.75" customHeight="1" s="23"/>
+    <row r="449" ht="15.75" customHeight="1" s="23"/>
+    <row r="450" ht="15.75" customHeight="1" s="23"/>
+    <row r="451" ht="15.75" customHeight="1" s="23"/>
+    <row r="452" ht="15.75" customHeight="1" s="23"/>
+    <row r="453" ht="15.75" customHeight="1" s="23"/>
+    <row r="454" ht="15.75" customHeight="1" s="23"/>
+    <row r="455" ht="15.75" customHeight="1" s="23"/>
+    <row r="456" ht="15.75" customHeight="1" s="23"/>
+    <row r="457" ht="15.75" customHeight="1" s="23"/>
+    <row r="458" ht="15.75" customHeight="1" s="23"/>
+    <row r="459" ht="15.75" customHeight="1" s="23"/>
+    <row r="460" ht="15.75" customHeight="1" s="23"/>
+    <row r="461" ht="15.75" customHeight="1" s="23"/>
+    <row r="462" ht="15.75" customHeight="1" s="23"/>
+    <row r="463" ht="15.75" customHeight="1" s="23"/>
+    <row r="464" ht="15.75" customHeight="1" s="23"/>
+    <row r="465" ht="15.75" customHeight="1" s="23"/>
+    <row r="466" ht="15.75" customHeight="1" s="23"/>
+    <row r="467" ht="15.75" customHeight="1" s="23"/>
+    <row r="468" ht="15.75" customHeight="1" s="23"/>
+    <row r="469" ht="15.75" customHeight="1" s="23"/>
+    <row r="470" ht="15.75" customHeight="1" s="23"/>
+    <row r="471" ht="15.75" customHeight="1" s="23"/>
+    <row r="472" ht="15.75" customHeight="1" s="23"/>
+    <row r="473" ht="15.75" customHeight="1" s="23"/>
+    <row r="474" ht="15.75" customHeight="1" s="23"/>
+    <row r="475" ht="15.75" customHeight="1" s="23"/>
+    <row r="476" ht="15.75" customHeight="1" s="23"/>
+    <row r="477" ht="15.75" customHeight="1" s="23"/>
+    <row r="478" ht="15.75" customHeight="1" s="23"/>
+    <row r="479" ht="15.75" customHeight="1" s="23"/>
+    <row r="480" ht="15.75" customHeight="1" s="23"/>
+    <row r="481" ht="15.75" customHeight="1" s="23"/>
+    <row r="482" ht="15.75" customHeight="1" s="23"/>
+    <row r="483" ht="15.75" customHeight="1" s="23"/>
+    <row r="484" ht="15.75" customHeight="1" s="23"/>
+    <row r="485" ht="15.75" customHeight="1" s="23"/>
+    <row r="486" ht="15.75" customHeight="1" s="23"/>
+    <row r="487" ht="15.75" customHeight="1" s="23"/>
+    <row r="488" ht="15.75" customHeight="1" s="23"/>
+    <row r="489" ht="15.75" customHeight="1" s="23"/>
+    <row r="490" ht="15.75" customHeight="1" s="23"/>
+    <row r="491" ht="15.75" customHeight="1" s="23"/>
+    <row r="492" ht="15.75" customHeight="1" s="23"/>
+    <row r="493" ht="15.75" customHeight="1" s="23"/>
+    <row r="494" ht="15.75" customHeight="1" s="23"/>
+    <row r="495" ht="15.75" customHeight="1" s="23"/>
+    <row r="496" ht="15.75" customHeight="1" s="23"/>
+    <row r="497" ht="15.75" customHeight="1" s="23"/>
+    <row r="498" ht="15.75" customHeight="1" s="23"/>
+    <row r="499" ht="15.75" customHeight="1" s="23"/>
+    <row r="500" ht="15.75" customHeight="1" s="23"/>
+    <row r="501" ht="15.75" customHeight="1" s="23"/>
+    <row r="502" ht="15.75" customHeight="1" s="23"/>
+    <row r="503" ht="15.75" customHeight="1" s="23"/>
+    <row r="504" ht="15.75" customHeight="1" s="23"/>
+    <row r="505" ht="15.75" customHeight="1" s="23"/>
+    <row r="506" ht="15.75" customHeight="1" s="23"/>
+    <row r="507" ht="15.75" customHeight="1" s="23"/>
+    <row r="508" ht="15.75" customHeight="1" s="23"/>
+    <row r="509" ht="15.75" customHeight="1" s="23"/>
+    <row r="510" ht="15.75" customHeight="1" s="23"/>
+    <row r="511" ht="15.75" customHeight="1" s="23"/>
+    <row r="512" ht="15.75" customHeight="1" s="23"/>
+    <row r="513" ht="15.75" customHeight="1" s="23"/>
+    <row r="514" ht="15.75" customHeight="1" s="23"/>
+    <row r="515" ht="15.75" customHeight="1" s="23"/>
+    <row r="516" ht="15.75" customHeight="1" s="23"/>
+    <row r="517" ht="15.75" customHeight="1" s="23"/>
+    <row r="518" ht="15.75" customHeight="1" s="23"/>
+    <row r="519" ht="15.75" customHeight="1" s="23"/>
+    <row r="520" ht="15.75" customHeight="1" s="23"/>
+    <row r="521" ht="15.75" customHeight="1" s="23"/>
+    <row r="522" ht="15.75" customHeight="1" s="23"/>
+    <row r="523" ht="15.75" customHeight="1" s="23"/>
+    <row r="524" ht="15.75" customHeight="1" s="23"/>
+    <row r="525" ht="15.75" customHeight="1" s="23"/>
+    <row r="526" ht="15.75" customHeight="1" s="23"/>
+    <row r="527" ht="15.75" customHeight="1" s="23"/>
+    <row r="528" ht="15.75" customHeight="1" s="23"/>
+    <row r="529" ht="15.75" customHeight="1" s="23"/>
+    <row r="530" ht="15.75" customHeight="1" s="23"/>
+    <row r="531" ht="15.75" customHeight="1" s="23"/>
+    <row r="532" ht="15.75" customHeight="1" s="23"/>
+    <row r="533" ht="15.75" customHeight="1" s="23"/>
+    <row r="534" ht="15.75" customHeight="1" s="23"/>
+    <row r="535" ht="15.75" customHeight="1" s="23"/>
+    <row r="536" ht="15.75" customHeight="1" s="23"/>
+    <row r="537" ht="15.75" customHeight="1" s="23"/>
+    <row r="538" ht="15.75" customHeight="1" s="23"/>
+    <row r="539" ht="15.75" customHeight="1" s="23"/>
+    <row r="540" ht="15.75" customHeight="1" s="23"/>
+    <row r="541" ht="15.75" customHeight="1" s="23"/>
+    <row r="542" ht="15.75" customHeight="1" s="23"/>
+    <row r="543" ht="15.75" customHeight="1" s="23"/>
+    <row r="544" ht="15.75" customHeight="1" s="23"/>
+    <row r="545" ht="15.75" customHeight="1" s="23"/>
+    <row r="546" ht="15.75" customHeight="1" s="23"/>
+    <row r="547" ht="15.75" customHeight="1" s="23"/>
+    <row r="548" ht="15.75" customHeight="1" s="23"/>
+    <row r="549" ht="15.75" customHeight="1" s="23"/>
+    <row r="550" ht="15.75" customHeight="1" s="23"/>
+    <row r="551" ht="15.75" customHeight="1" s="23"/>
+    <row r="552" ht="15.75" customHeight="1" s="23"/>
+    <row r="553" ht="15.75" customHeight="1" s="23"/>
+    <row r="554" ht="15.75" customHeight="1" s="23"/>
+    <row r="555" ht="15.75" customHeight="1" s="23"/>
+    <row r="556" ht="15.75" customHeight="1" s="23"/>
+    <row r="557" ht="15.75" customHeight="1" s="23"/>
+    <row r="558" ht="15.75" customHeight="1" s="23"/>
+    <row r="559" ht="15.75" customHeight="1" s="23"/>
+    <row r="560" ht="15.75" customHeight="1" s="23"/>
+    <row r="561" ht="15.75" customHeight="1" s="23"/>
+    <row r="562" ht="15.75" customHeight="1" s="23"/>
+    <row r="563" ht="15.75" customHeight="1" s="23"/>
+    <row r="564" ht="15.75" customHeight="1" s="23"/>
+    <row r="565" ht="15.75" customHeight="1" s="23"/>
+    <row r="566" ht="15.75" customHeight="1" s="23"/>
+    <row r="567" ht="15.75" customHeight="1" s="23"/>
+    <row r="568" ht="15.75" customHeight="1" s="23"/>
+    <row r="569" ht="15.75" customHeight="1" s="23"/>
+    <row r="570" ht="15.75" customHeight="1" s="23"/>
+    <row r="571" ht="15.75" customHeight="1" s="23"/>
+    <row r="572" ht="15.75" customHeight="1" s="23"/>
+    <row r="573" ht="15.75" customHeight="1" s="23"/>
+    <row r="574" ht="15.75" customHeight="1" s="23"/>
+    <row r="575" ht="15.75" customHeight="1" s="23"/>
+    <row r="576" ht="15.75" customHeight="1" s="23"/>
+    <row r="577" ht="15.75" customHeight="1" s="23"/>
+    <row r="578" ht="15.75" customHeight="1" s="23"/>
+    <row r="579" ht="15.75" customHeight="1" s="23"/>
+    <row r="580" ht="15.75" customHeight="1" s="23"/>
+    <row r="581" ht="15.75" customHeight="1" s="23"/>
+    <row r="582" ht="15.75" customHeight="1" s="23"/>
+    <row r="583" ht="15.75" customHeight="1" s="23"/>
+    <row r="584" ht="15.75" customHeight="1" s="23"/>
+    <row r="585" ht="15.75" customHeight="1" s="23"/>
+    <row r="586" ht="15.75" customHeight="1" s="23"/>
+    <row r="587" ht="15.75" customHeight="1" s="23"/>
+    <row r="588" ht="15.75" customHeight="1" s="23"/>
+    <row r="589" ht="15.75" customHeight="1" s="23"/>
+    <row r="590" ht="15.75" customHeight="1" s="23"/>
+    <row r="591" ht="15.75" customHeight="1" s="23"/>
+    <row r="592" ht="15.75" customHeight="1" s="23"/>
+    <row r="593" ht="15.75" customHeight="1" s="23"/>
+    <row r="594" ht="15.75" customHeight="1" s="23"/>
+    <row r="595" ht="15.75" customHeight="1" s="23"/>
+    <row r="596" ht="15.75" customHeight="1" s="23"/>
+    <row r="597" ht="15.75" customHeight="1" s="23"/>
+    <row r="598" ht="15.75" customHeight="1" s="23"/>
+    <row r="599" ht="15.75" customHeight="1" s="23"/>
+    <row r="600" ht="15.75" customHeight="1" s="23"/>
+    <row r="601" ht="15.75" customHeight="1" s="23"/>
+    <row r="602" ht="15.75" customHeight="1" s="23"/>
+    <row r="603" ht="15.75" customHeight="1" s="23"/>
+    <row r="604" ht="15.75" customHeight="1" s="23"/>
+    <row r="605" ht="15.75" customHeight="1" s="23"/>
+    <row r="606" ht="15.75" customHeight="1" s="23"/>
+    <row r="607" ht="15.75" customHeight="1" s="23"/>
+    <row r="608" ht="15.75" customHeight="1" s="23"/>
+    <row r="609" ht="15.75" customHeight="1" s="23"/>
+    <row r="610" ht="15.75" customHeight="1" s="23"/>
+    <row r="611" ht="15.75" customHeight="1" s="23"/>
+    <row r="612" ht="15.75" customHeight="1" s="23"/>
+    <row r="613" ht="15.75" customHeight="1" s="23"/>
+    <row r="614" ht="15.75" customHeight="1" s="23"/>
+    <row r="615" ht="15.75" customHeight="1" s="23"/>
+    <row r="616" ht="15.75" customHeight="1" s="23"/>
+    <row r="617" ht="15.75" customHeight="1" s="23"/>
+    <row r="618" ht="15.75" customHeight="1" s="23"/>
+    <row r="619" ht="15.75" customHeight="1" s="23"/>
+    <row r="620" ht="15.75" customHeight="1" s="23"/>
+    <row r="621" ht="15.75" customHeight="1" s="23"/>
+    <row r="622" ht="15.75" customHeight="1" s="23"/>
+    <row r="623" ht="15.75" customHeight="1" s="23"/>
+    <row r="624" ht="15.75" customHeight="1" s="23"/>
+    <row r="625" ht="15.75" customHeight="1" s="23"/>
+    <row r="626" ht="15.75" customHeight="1" s="23"/>
+    <row r="627" ht="15.75" customHeight="1" s="23"/>
+    <row r="628" ht="15.75" customHeight="1" s="23"/>
+    <row r="629" ht="15.75" customHeight="1" s="23"/>
+    <row r="630" ht="15.75" customHeight="1" s="23"/>
+    <row r="631" ht="15.75" customHeight="1" s="23"/>
+    <row r="632" ht="15.75" customHeight="1" s="23"/>
+    <row r="633" ht="15.75" customHeight="1" s="23"/>
+    <row r="634" ht="15.75" customHeight="1" s="23"/>
+    <row r="635" ht="15.75" customHeight="1" s="23"/>
+    <row r="636" ht="15.75" customHeight="1" s="23"/>
+    <row r="637" ht="15.75" customHeight="1" s="23"/>
+    <row r="638" ht="15.75" customHeight="1" s="23"/>
+    <row r="639" ht="15.75" customHeight="1" s="23"/>
+    <row r="640" ht="15.75" customHeight="1" s="23"/>
+    <row r="641" ht="15.75" customHeight="1" s="23"/>
+    <row r="642" ht="15.75" customHeight="1" s="23"/>
+    <row r="643" ht="15.75" customHeight="1" s="23"/>
+    <row r="644" ht="15.75" customHeight="1" s="23"/>
+    <row r="645" ht="15.75" customHeight="1" s="23"/>
+    <row r="646" ht="15.75" customHeight="1" s="23"/>
+    <row r="647" ht="15.75" customHeight="1" s="23"/>
+    <row r="648" ht="15.75" customHeight="1" s="23"/>
+    <row r="649" ht="15.75" customHeight="1" s="23"/>
+    <row r="650" ht="15.75" customHeight="1" s="23"/>
+    <row r="651" ht="15.75" customHeight="1" s="23"/>
+    <row r="652" ht="15.75" customHeight="1" s="23"/>
+    <row r="653" ht="15.75" customHeight="1" s="23"/>
+    <row r="654" ht="15.75" customHeight="1" s="23"/>
+    <row r="655" ht="15.75" customHeight="1" s="23"/>
+    <row r="656" ht="15.75" customHeight="1" s="23"/>
+    <row r="657" ht="15.75" customHeight="1" s="23"/>
+    <row r="658" ht="15.75" customHeight="1" s="23"/>
+    <row r="659" ht="15.75" customHeight="1" s="23"/>
+    <row r="660" ht="15.75" customHeight="1" s="23"/>
+    <row r="661" ht="15.75" customHeight="1" s="23"/>
+    <row r="662" ht="15.75" customHeight="1" s="23"/>
+    <row r="663" ht="15.75" customHeight="1" s="23"/>
+    <row r="664" ht="15.75" customHeight="1" s="23"/>
+    <row r="665" ht="15.75" customHeight="1" s="23"/>
+    <row r="666" ht="15.75" customHeight="1" s="23"/>
+    <row r="667" ht="15.75" customHeight="1" s="23"/>
+    <row r="668" ht="15.75" customHeight="1" s="23"/>
+    <row r="669" ht="15.75" customHeight="1" s="23"/>
+    <row r="670" ht="15.75" customHeight="1" s="23"/>
+    <row r="671" ht="15.75" customHeight="1" s="23"/>
+    <row r="672" ht="15.75" customHeight="1" s="23"/>
+    <row r="673" ht="15.75" customHeight="1" s="23"/>
+    <row r="674" ht="15.75" customHeight="1" s="23"/>
+    <row r="675" ht="15.75" customHeight="1" s="23"/>
+    <row r="676" ht="15.75" customHeight="1" s="23"/>
+    <row r="677" ht="15.75" customHeight="1" s="23"/>
+    <row r="678" ht="15.75" customHeight="1" s="23"/>
+    <row r="679" ht="15.75" customHeight="1" s="23"/>
+    <row r="680" ht="15.75" customHeight="1" s="23"/>
+    <row r="681" ht="15.75" customHeight="1" s="23"/>
+    <row r="682" ht="15.75" customHeight="1" s="23"/>
+    <row r="683" ht="15.75" customHeight="1" s="23"/>
+    <row r="684" ht="15.75" customHeight="1" s="23"/>
+    <row r="685" ht="15.75" customHeight="1" s="23"/>
+    <row r="686" ht="15.75" customHeight="1" s="23"/>
+    <row r="687" ht="15.75" customHeight="1" s="23"/>
+    <row r="688" ht="15.75" customHeight="1" s="23"/>
+    <row r="689" ht="15.75" customHeight="1" s="23"/>
+    <row r="690" ht="15.75" customHeight="1" s="23"/>
+    <row r="691" ht="15.75" customHeight="1" s="23"/>
+    <row r="692" ht="15.75" customHeight="1" s="23"/>
+    <row r="693" ht="15.75" customHeight="1" s="23"/>
+    <row r="694" ht="15.75" customHeight="1" s="23"/>
+    <row r="695" ht="15.75" customHeight="1" s="23"/>
+    <row r="696" ht="15.75" customHeight="1" s="23"/>
+    <row r="697" ht="15.75" customHeight="1" s="23"/>
+    <row r="698" ht="15.75" customHeight="1" s="23"/>
+    <row r="699" ht="15.75" customHeight="1" s="23"/>
+    <row r="700" ht="15.75" customHeight="1" s="23"/>
+    <row r="701" ht="15.75" customHeight="1" s="23"/>
+    <row r="702" ht="15.75" customHeight="1" s="23"/>
+    <row r="703" ht="15.75" customHeight="1" s="23"/>
+    <row r="704" ht="15.75" customHeight="1" s="23"/>
+    <row r="705" ht="15.75" customHeight="1" s="23"/>
+    <row r="706" ht="15.75" customHeight="1" s="23"/>
+    <row r="707" ht="15.75" customHeight="1" s="23"/>
+    <row r="708" ht="15.75" customHeight="1" s="23"/>
+    <row r="709" ht="15.75" customHeight="1" s="23"/>
+    <row r="710" ht="15.75" customHeight="1" s="23"/>
+    <row r="711" ht="15.75" customHeight="1" s="23"/>
+    <row r="712" ht="15.75" customHeight="1" s="23"/>
+    <row r="713" ht="15.75" customHeight="1" s="23"/>
+    <row r="714" ht="15.75" customHeight="1" s="23"/>
+    <row r="715" ht="15.75" customHeight="1" s="23"/>
+    <row r="716" ht="15.75" customHeight="1" s="23"/>
+    <row r="717" ht="15.75" customHeight="1" s="23"/>
+    <row r="718" ht="15.75" customHeight="1" s="23"/>
+    <row r="719" ht="15.75" customHeight="1" s="23"/>
+    <row r="720" ht="15.75" customHeight="1" s="23"/>
+    <row r="721" ht="15.75" customHeight="1" s="23"/>
+    <row r="722" ht="15.75" customHeight="1" s="23"/>
+    <row r="723" ht="15.75" customHeight="1" s="23"/>
+    <row r="724" ht="15.75" customHeight="1" s="23"/>
+    <row r="725" ht="15.75" customHeight="1" s="23"/>
+    <row r="726" ht="15.75" customHeight="1" s="23"/>
+    <row r="727" ht="15.75" customHeight="1" s="23"/>
+    <row r="728" ht="15.75" customHeight="1" s="23"/>
+    <row r="729" ht="15.75" customHeight="1" s="23"/>
+    <row r="730" ht="15.75" customHeight="1" s="23"/>
+    <row r="731" ht="15.75" customHeight="1" s="23"/>
+    <row r="732" ht="15.75" customHeight="1" s="23"/>
+    <row r="733" ht="15.75" customHeight="1" s="23"/>
+    <row r="734" ht="15.75" customHeight="1" s="23"/>
+    <row r="735" ht="15.75" customHeight="1" s="23"/>
+    <row r="736" ht="15.75" customHeight="1" s="23"/>
+    <row r="737" ht="15.75" customHeight="1" s="23"/>
+    <row r="738" ht="15.75" customHeight="1" s="23"/>
+    <row r="739" ht="15.75" customHeight="1" s="23"/>
+    <row r="740" ht="15.75" customHeight="1" s="23"/>
+    <row r="741" ht="15.75" customHeight="1" s="23"/>
+    <row r="742" ht="15.75" customHeight="1" s="23"/>
+    <row r="743" ht="15.75" customHeight="1" s="23"/>
+    <row r="744" ht="15.75" customHeight="1" s="23"/>
+    <row r="745" ht="15.75" customHeight="1" s="23"/>
+    <row r="746" ht="15.75" customHeight="1" s="23"/>
+    <row r="747" ht="15.75" customHeight="1" s="23"/>
+    <row r="748" ht="15.75" customHeight="1" s="23"/>
+    <row r="749" ht="15.75" customHeight="1" s="23"/>
+    <row r="750" ht="15.75" customHeight="1" s="23"/>
+    <row r="751" ht="15.75" customHeight="1" s="23"/>
+    <row r="752" ht="15.75" customHeight="1" s="23"/>
+    <row r="753" ht="15.75" customHeight="1" s="23"/>
+    <row r="754" ht="15.75" customHeight="1" s="23"/>
+    <row r="755" ht="15.75" customHeight="1" s="23"/>
+    <row r="756" ht="15.75" customHeight="1" s="23"/>
+    <row r="757" ht="15.75" customHeight="1" s="23"/>
+    <row r="758" ht="15.75" customHeight="1" s="23"/>
+    <row r="759" ht="15.75" customHeight="1" s="23"/>
+    <row r="760" ht="15.75" customHeight="1" s="23"/>
+    <row r="761" ht="15.75" customHeight="1" s="23"/>
+    <row r="762" ht="15.75" customHeight="1" s="23"/>
+    <row r="763" ht="15.75" customHeight="1" s="23"/>
+    <row r="764" ht="15.75" customHeight="1" s="23"/>
+    <row r="765" ht="15.75" customHeight="1" s="23"/>
+    <row r="766" ht="15.75" customHeight="1" s="23"/>
+    <row r="767" ht="15.75" customHeight="1" s="23"/>
+    <row r="768" ht="15.75" customHeight="1" s="23"/>
+    <row r="769" ht="15.75" customHeight="1" s="23"/>
+    <row r="770" ht="15.75" customHeight="1" s="23"/>
+    <row r="771" ht="15.75" customHeight="1" s="23"/>
+    <row r="772" ht="15.75" customHeight="1" s="23"/>
+    <row r="773" ht="15.75" customHeight="1" s="23"/>
+    <row r="774" ht="15.75" customHeight="1" s="23"/>
+    <row r="775" ht="15.75" customHeight="1" s="23"/>
+    <row r="776" ht="15.75" customHeight="1" s="23"/>
+    <row r="777" ht="15.75" customHeight="1" s="23"/>
+    <row r="778" ht="15.75" customHeight="1" s="23"/>
+    <row r="779" ht="15.75" customHeight="1" s="23"/>
+    <row r="780" ht="15.75" customHeight="1" s="23"/>
+    <row r="781" ht="15.75" customHeight="1" s="23"/>
+    <row r="782" ht="15.75" customHeight="1" s="23"/>
+    <row r="783" ht="15.75" customHeight="1" s="23"/>
+    <row r="784" ht="15.75" customHeight="1" s="23"/>
+    <row r="785" ht="15.75" customHeight="1" s="23"/>
+    <row r="786" ht="15.75" customHeight="1" s="23"/>
+    <row r="787" ht="15.75" customHeight="1" s="23"/>
+    <row r="788" ht="15.75" customHeight="1" s="23"/>
+    <row r="789" ht="15.75" customHeight="1" s="23"/>
+    <row r="790" ht="15.75" customHeight="1" s="23"/>
+    <row r="791" ht="15.75" customHeight="1" s="23"/>
+    <row r="792" ht="15.75" customHeight="1" s="23"/>
+    <row r="793" ht="15.75" customHeight="1" s="23"/>
+    <row r="794" ht="15.75" customHeight="1" s="23"/>
+    <row r="795" ht="15.75" customHeight="1" s="23"/>
+    <row r="796" ht="15.75" customHeight="1" s="23"/>
+    <row r="797" ht="15.75" customHeight="1" s="23"/>
+    <row r="798" ht="15.75" customHeight="1" s="23"/>
+    <row r="799" ht="15.75" customHeight="1" s="23"/>
+    <row r="800" ht="15.75" customHeight="1" s="23"/>
+    <row r="801" ht="15.75" customHeight="1" s="23"/>
+    <row r="802" ht="15.75" customHeight="1" s="23"/>
+    <row r="803" ht="15.75" customHeight="1" s="23"/>
+    <row r="804" ht="15.75" customHeight="1" s="23"/>
+    <row r="805" ht="15.75" customHeight="1" s="23"/>
+    <row r="806" ht="15.75" customHeight="1" s="23"/>
+    <row r="807" ht="15.75" customHeight="1" s="23"/>
+    <row r="808" ht="15.75" customHeight="1" s="23"/>
+    <row r="809" ht="15.75" customHeight="1" s="23"/>
+    <row r="810" ht="15.75" customHeight="1" s="23"/>
+    <row r="811" ht="15.75" customHeight="1" s="23"/>
+    <row r="812" ht="15.75" customHeight="1" s="23"/>
+    <row r="813" ht="15.75" customHeight="1" s="23"/>
+    <row r="814" ht="15.75" customHeight="1" s="23"/>
+    <row r="815" ht="15.75" customHeight="1" s="23"/>
+    <row r="816" ht="15.75" customHeight="1" s="23"/>
+    <row r="817" ht="15.75" customHeight="1" s="23"/>
+    <row r="818" ht="15.75" customHeight="1" s="23"/>
+    <row r="819" ht="15.75" customHeight="1" s="23"/>
+    <row r="820" ht="15.75" customHeight="1" s="23"/>
+    <row r="821" ht="15.75" customHeight="1" s="23"/>
+    <row r="822" ht="15.75" customHeight="1" s="23"/>
+    <row r="823" ht="15.75" customHeight="1" s="23"/>
+    <row r="824" ht="15.75" customHeight="1" s="23"/>
+    <row r="825" ht="15.75" customHeight="1" s="23"/>
+    <row r="826" ht="15.75" customHeight="1" s="23"/>
+    <row r="827" ht="15.75" customHeight="1" s="23"/>
+    <row r="828" ht="15.75" customHeight="1" s="23"/>
+    <row r="829" ht="15.75" customHeight="1" s="23"/>
+    <row r="830" ht="15.75" customHeight="1" s="23"/>
+    <row r="831" ht="15.75" customHeight="1" s="23"/>
+    <row r="832" ht="15.75" customHeight="1" s="23"/>
+    <row r="833" ht="15.75" customHeight="1" s="23"/>
+    <row r="834" ht="15.75" customHeight="1" s="23"/>
+    <row r="835" ht="15.75" customHeight="1" s="23"/>
+    <row r="836" ht="15.75" customHeight="1" s="23"/>
+    <row r="837" ht="15.75" customHeight="1" s="23"/>
+    <row r="838" ht="15.75" customHeight="1" s="23"/>
+    <row r="839" ht="15.75" customHeight="1" s="23"/>
+    <row r="840" ht="15.75" customHeight="1" s="23"/>
+    <row r="841" ht="15.75" customHeight="1" s="23"/>
+    <row r="842" ht="15.75" customHeight="1" s="23"/>
+    <row r="843" ht="15.75" customHeight="1" s="23"/>
+    <row r="844" ht="15.75" customHeight="1" s="23"/>
+    <row r="845" ht="15.75" customHeight="1" s="23"/>
+    <row r="846" ht="15.75" customHeight="1" s="23"/>
+    <row r="847" ht="15.75" customHeight="1" s="23"/>
+    <row r="848" ht="15.75" customHeight="1" s="23"/>
+    <row r="849" ht="15.75" customHeight="1" s="23"/>
+    <row r="850" ht="15.75" customHeight="1" s="23"/>
+    <row r="851" ht="15.75" customHeight="1" s="23"/>
+    <row r="852" ht="15.75" customHeight="1" s="23"/>
+    <row r="853" ht="15.75" customHeight="1" s="23"/>
+    <row r="854" ht="15.75" customHeight="1" s="23"/>
+    <row r="855" ht="15.75" customHeight="1" s="23"/>
+    <row r="856" ht="15.75" customHeight="1" s="23"/>
+    <row r="857" ht="15.75" customHeight="1" s="23"/>
+    <row r="858" ht="15.75" customHeight="1" s="23"/>
+    <row r="859" ht="15.75" customHeight="1" s="23"/>
+    <row r="860" ht="15.75" customHeight="1" s="23"/>
+    <row r="861" ht="15.75" customHeight="1" s="23"/>
+    <row r="862" ht="15.75" customHeight="1" s="23"/>
+    <row r="863" ht="15.75" customHeight="1" s="23"/>
+    <row r="864" ht="15.75" customHeight="1" s="23"/>
+    <row r="865" ht="15.75" customHeight="1" s="23"/>
+    <row r="866" ht="15.75" customHeight="1" s="23"/>
+    <row r="867" ht="15.75" customHeight="1" s="23"/>
+    <row r="868" ht="15.75" customHeight="1" s="23"/>
+    <row r="869" ht="15.75" customHeight="1" s="23"/>
+    <row r="870" ht="15.75" customHeight="1" s="23"/>
+    <row r="871" ht="15.75" customHeight="1" s="23"/>
+    <row r="872" ht="15.75" customHeight="1" s="23"/>
+    <row r="873" ht="15.75" customHeight="1" s="23"/>
+    <row r="874" ht="15.75" customHeight="1" s="23"/>
+    <row r="875" ht="15.75" customHeight="1" s="23"/>
+    <row r="876" ht="15.75" customHeight="1" s="23"/>
+    <row r="877" ht="15.75" customHeight="1" s="23"/>
+    <row r="878" ht="15.75" customHeight="1" s="23"/>
+    <row r="879" ht="15.75" customHeight="1" s="23"/>
+    <row r="880" ht="15.75" customHeight="1" s="23"/>
+    <row r="881" ht="15.75" customHeight="1" s="23"/>
+    <row r="882" ht="15.75" customHeight="1" s="23"/>
+    <row r="883" ht="15.75" customHeight="1" s="23"/>
+    <row r="884" ht="15.75" customHeight="1" s="23"/>
+    <row r="885" ht="15.75" customHeight="1" s="23"/>
+    <row r="886" ht="15.75" customHeight="1" s="23"/>
+    <row r="887" ht="15.75" customHeight="1" s="23"/>
+    <row r="888" ht="15.75" customHeight="1" s="23"/>
+    <row r="889" ht="15.75" customHeight="1" s="23"/>
+    <row r="890" ht="15.75" customHeight="1" s="23"/>
+    <row r="891" ht="15.75" customHeight="1" s="23"/>
+    <row r="892" ht="15.75" customHeight="1" s="23"/>
+    <row r="893" ht="15.75" customHeight="1" s="23"/>
+    <row r="894" ht="15.75" customHeight="1" s="23"/>
+    <row r="895" ht="15.75" customHeight="1" s="23"/>
+    <row r="896" ht="15.75" customHeight="1" s="23"/>
+    <row r="897" ht="15.75" customHeight="1" s="23"/>
+    <row r="898" ht="15.75" customHeight="1" s="23"/>
+    <row r="899" ht="15.75" customHeight="1" s="23"/>
+    <row r="900" ht="15.75" customHeight="1" s="23"/>
+    <row r="901" ht="15.75" customHeight="1" s="23"/>
+    <row r="902" ht="15.75" customHeight="1" s="23"/>
+    <row r="903" ht="15.75" customHeight="1" s="23"/>
+    <row r="904" ht="15.75" customHeight="1" s="23"/>
+    <row r="905" ht="15.75" customHeight="1" s="23"/>
+    <row r="906" ht="15.75" customHeight="1" s="23"/>
+    <row r="907" ht="15.75" customHeight="1" s="23"/>
+    <row r="908" ht="15.75" customHeight="1" s="23"/>
+    <row r="909" ht="15.75" customHeight="1" s="23"/>
+    <row r="910" ht="15.75" customHeight="1" s="23"/>
+    <row r="911" ht="15.75" customHeight="1" s="23"/>
+    <row r="912" ht="15.75" customHeight="1" s="23"/>
+    <row r="913" ht="15.75" customHeight="1" s="23"/>
+    <row r="914" ht="15.75" customHeight="1" s="23"/>
+    <row r="915" ht="15.75" customHeight="1" s="23"/>
+    <row r="916" ht="15.75" customHeight="1" s="23"/>
+    <row r="917" ht="15.75" customHeight="1" s="23"/>
+    <row r="918" ht="15.75" customHeight="1" s="23"/>
+    <row r="919" ht="15.75" customHeight="1" s="23"/>
+    <row r="920" ht="15.75" customHeight="1" s="23"/>
+    <row r="921" ht="15.75" customHeight="1" s="23"/>
+    <row r="922" ht="15.75" customHeight="1" s="23"/>
+    <row r="923" ht="15.75" customHeight="1" s="23"/>
+    <row r="924" ht="15.75" customHeight="1" s="23"/>
+    <row r="925" ht="15.75" customHeight="1" s="23"/>
+    <row r="926" ht="15.75" customHeight="1" s="23"/>
+    <row r="927" ht="15.75" customHeight="1" s="23"/>
+    <row r="928" ht="15.75" customHeight="1" s="23"/>
+    <row r="929" ht="15.75" customHeight="1" s="23"/>
+    <row r="930" ht="15.75" customHeight="1" s="23"/>
+    <row r="931" ht="15.75" customHeight="1" s="23"/>
+    <row r="932" ht="15.75" customHeight="1" s="23"/>
+    <row r="933" ht="15.75" customHeight="1" s="23"/>
+    <row r="934" ht="15.75" customHeight="1" s="23"/>
+    <row r="935" ht="15.75" customHeight="1" s="23"/>
+    <row r="936" ht="15.75" customHeight="1" s="23"/>
+    <row r="937" ht="15.75" customHeight="1" s="23"/>
+    <row r="938" ht="15.75" customHeight="1" s="23"/>
+    <row r="939" ht="15.75" customHeight="1" s="23"/>
+    <row r="940" ht="15.75" customHeight="1" s="23"/>
+    <row r="941" ht="15.75" customHeight="1" s="23"/>
+    <row r="942" ht="15.75" customHeight="1" s="23"/>
+    <row r="943" ht="15.75" customHeight="1" s="23"/>
+    <row r="944" ht="15.75" customHeight="1" s="23"/>
+    <row r="945" ht="15.75" customHeight="1" s="23"/>
+    <row r="946" ht="15.75" customHeight="1" s="23"/>
+    <row r="947" ht="15.75" customHeight="1" s="23"/>
+    <row r="948" ht="15.75" customHeight="1" s="23"/>
+    <row r="949" ht="15.75" customHeight="1" s="23"/>
+    <row r="950" ht="15.75" customHeight="1" s="23"/>
+    <row r="951" ht="15.75" customHeight="1" s="23"/>
+    <row r="952" ht="15.75" customHeight="1" s="23"/>
+    <row r="953" ht="15.75" customHeight="1" s="23"/>
+    <row r="954" ht="15.75" customHeight="1" s="23"/>
+    <row r="955" ht="15.75" customHeight="1" s="23"/>
+    <row r="956" ht="15.75" customHeight="1" s="23"/>
+    <row r="957" ht="15.75" customHeight="1" s="23"/>
+    <row r="958" ht="15.75" customHeight="1" s="23"/>
+    <row r="959" ht="15.75" customHeight="1" s="23"/>
+    <row r="960" ht="15.75" customHeight="1" s="23"/>
+    <row r="961" ht="15.75" customHeight="1" s="23"/>
+    <row r="962" ht="15.75" customHeight="1" s="23"/>
+    <row r="963" ht="15.75" customHeight="1" s="23"/>
+    <row r="964" ht="15.75" customHeight="1" s="23"/>
+    <row r="965" ht="15.75" customHeight="1" s="23"/>
+    <row r="966" ht="15.75" customHeight="1" s="23"/>
+    <row r="967" ht="15.75" customHeight="1" s="23"/>
+    <row r="968" ht="15.75" customHeight="1" s="23"/>
+    <row r="969" ht="15.75" customHeight="1" s="23"/>
+    <row r="970" ht="15.75" customHeight="1" s="23"/>
+    <row r="971" ht="15.75" customHeight="1" s="23"/>
+    <row r="972" ht="15.75" customHeight="1" s="23"/>
+    <row r="973" ht="15.75" customHeight="1" s="23"/>
+    <row r="974" ht="15.75" customHeight="1" s="23"/>
+    <row r="975" ht="15.75" customHeight="1" s="23"/>
+    <row r="976" ht="15.75" customHeight="1" s="23"/>
+    <row r="977" ht="15.75" customHeight="1" s="23"/>
+    <row r="978" ht="15.75" customHeight="1" s="23"/>
+    <row r="979" ht="15.75" customHeight="1" s="23"/>
+    <row r="980" ht="15.75" customHeight="1" s="23"/>
+    <row r="981" ht="15.75" customHeight="1" s="23"/>
+    <row r="982" ht="15.75" customHeight="1" s="23"/>
+    <row r="983" ht="15.75" customHeight="1" s="23"/>
+    <row r="984" ht="15.75" customHeight="1" s="23"/>
+    <row r="985" ht="15.75" customHeight="1" s="23"/>
+    <row r="986" ht="15.75" customHeight="1" s="23"/>
+    <row r="987" ht="15.75" customHeight="1" s="23"/>
+    <row r="988" ht="15.75" customHeight="1" s="23"/>
+    <row r="989" ht="15.75" customHeight="1" s="23"/>
+    <row r="990" ht="15.75" customHeight="1" s="23"/>
+    <row r="991" ht="15.75" customHeight="1" s="23"/>
+    <row r="992" ht="15.75" customHeight="1" s="23"/>
+    <row r="993" ht="15.75" customHeight="1" s="23"/>
+    <row r="994" ht="15.75" customHeight="1" s="23"/>
+    <row r="995" ht="15.75" customHeight="1" s="23"/>
+    <row r="996" ht="15.75" customHeight="1" s="23"/>
+    <row r="997" ht="15.75" customHeight="1" s="23"/>
+    <row r="998" ht="15.75" customHeight="1" s="23"/>
+    <row r="999" ht="15.75" customHeight="1" s="23"/>
+    <row r="1000" ht="15.75" customHeight="1" s="23"/>
   </sheetData>
-  <conditionalFormatting sqref="A5:D304">
+  <conditionalFormatting sqref="A5:D1000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$B5="Einnahme"</formula>
     </cfRule>
@@ -5613,11 +7391,12 @@
     <dataValidation sqref="B5:B304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Einnahme,Ausgabe"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Datum" error="Bitte ein Datum aus 2026 eintragen." type="date" operator="between">
-      <formula1>46023</formula1>
-      <formula2>46387</formula2>
+    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Datum - Bitte ein Datum aus 2026 eintragen." type="date">
+      <formula1>46023.0</formula1>
+      <formula2>46387.0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
--- a/einnahmen/Einnahmen_Ausgaben_2025-2026.xlsx
+++ b/einnahmen/Einnahmen_Ausgaben_2025-2026.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D33"/>
+  <dimension ref="A2:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="23" min="1" max="1"/>
@@ -536,6 +536,7 @@
     <col width="16" customWidth="1" style="23" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1" s="23"/>
     <row r="2" ht="30" customHeight="1" s="23">
       <c r="A2" s="24" t="inlineStr">
         <is>
@@ -558,500 +559,459 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" s="23">
       <c r="A3" s="10">
-        <f>'2025'!F5</f>
+        <f>'2025'!F8</f>
         <v/>
       </c>
       <c r="B3" s="11">
-        <f>'2025'!G5</f>
+        <f>'2025'!G8</f>
         <v/>
       </c>
       <c r="C3" s="12">
-        <f>'2025'!H5</f>
+        <f>'2025'!H8</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>'2025'!I5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
+        <f>'2025'!I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" s="23">
       <c r="A4" s="10">
-        <f>'2025'!F6</f>
+        <f>'2025'!F9</f>
         <v/>
       </c>
       <c r="B4" s="11">
-        <f>'2025'!G6</f>
+        <f>'2025'!G9</f>
         <v/>
       </c>
       <c r="C4" s="12">
-        <f>'2025'!H6</f>
+        <f>'2025'!H9</f>
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>'2025'!I6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
+        <f>'2025'!I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" s="23">
       <c r="A5" s="10">
-        <f>'2025'!F7</f>
+        <f>'2025'!F10</f>
         <v/>
       </c>
       <c r="B5" s="11">
-        <f>'2025'!G7</f>
+        <f>'2025'!G10</f>
         <v/>
       </c>
       <c r="C5" s="12">
-        <f>'2025'!H7</f>
+        <f>'2025'!H10</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>'2025'!I7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
+        <f>'2025'!I10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" s="23">
       <c r="A6" s="10">
-        <f>'2025'!F8</f>
+        <f>'2025'!F11</f>
         <v/>
       </c>
       <c r="B6" s="11">
-        <f>'2025'!G8</f>
+        <f>'2025'!G11</f>
         <v/>
       </c>
       <c r="C6" s="12">
-        <f>'2025'!H8</f>
+        <f>'2025'!H11</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>'2025'!I8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
+        <f>'2025'!I11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" s="23">
       <c r="A7" s="10">
-        <f>'2025'!F9</f>
+        <f>'2025'!F12</f>
         <v/>
       </c>
       <c r="B7" s="11">
-        <f>'2025'!G9</f>
+        <f>'2025'!G12</f>
         <v/>
       </c>
       <c r="C7" s="12">
-        <f>'2025'!H9</f>
+        <f>'2025'!H12</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>'2025'!I9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
+        <f>'2025'!I12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" s="23">
       <c r="A8" s="10">
-        <f>'2025'!F10</f>
+        <f>'2025'!F13</f>
         <v/>
       </c>
       <c r="B8" s="11">
-        <f>'2025'!G10</f>
+        <f>'2025'!G13</f>
         <v/>
       </c>
       <c r="C8" s="12">
-        <f>'2025'!H10</f>
+        <f>'2025'!H13</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>'2025'!I10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
+        <f>'2025'!I13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" s="23">
       <c r="A9" s="10">
-        <f>'2025'!F11</f>
+        <f>'2025'!F14</f>
         <v/>
       </c>
       <c r="B9" s="11">
-        <f>'2025'!G11</f>
+        <f>'2025'!G14</f>
         <v/>
       </c>
       <c r="C9" s="12">
-        <f>'2025'!H11</f>
+        <f>'2025'!H14</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>'2025'!I11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
+        <f>'2025'!I14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" s="23">
       <c r="A10" s="10">
-        <f>'2025'!F12</f>
+        <f>'2025'!F15</f>
         <v/>
       </c>
       <c r="B10" s="11">
-        <f>'2025'!G12</f>
+        <f>'2025'!G15</f>
         <v/>
       </c>
       <c r="C10" s="12">
-        <f>'2025'!H12</f>
+        <f>'2025'!H15</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>'2025'!I12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
+        <f>'2025'!I15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" s="23">
       <c r="A11" s="10">
-        <f>'2025'!F13</f>
+        <f>'2025'!F16</f>
         <v/>
       </c>
       <c r="B11" s="11">
-        <f>'2025'!G13</f>
+        <f>'2025'!G16</f>
         <v/>
       </c>
       <c r="C11" s="12">
-        <f>'2025'!H13</f>
+        <f>'2025'!H16</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>'2025'!I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10">
-        <f>'2025'!F14</f>
-        <v/>
-      </c>
-      <c r="B12" s="11">
-        <f>'2025'!G14</f>
-        <v/>
-      </c>
-      <c r="C12" s="12">
-        <f>'2025'!H14</f>
-        <v/>
-      </c>
-      <c r="D12" s="13">
-        <f>'2025'!I14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10">
-        <f>'2025'!F15</f>
-        <v/>
-      </c>
-      <c r="B13" s="11">
-        <f>'2025'!G15</f>
-        <v/>
-      </c>
-      <c r="C13" s="12">
-        <f>'2025'!H15</f>
-        <v/>
-      </c>
-      <c r="D13" s="13">
-        <f>'2025'!I15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10">
-        <f>'2025'!F16</f>
-        <v/>
-      </c>
-      <c r="B14" s="11">
-        <f>'2025'!G16</f>
-        <v/>
-      </c>
-      <c r="C14" s="12">
-        <f>'2025'!H16</f>
-        <v/>
-      </c>
-      <c r="D14" s="13">
         <f>'2025'!I16</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Gesamt 2025</t>
-        </is>
-      </c>
-      <c r="B15" s="17">
-        <f>'2025'!G17</f>
-        <v/>
-      </c>
-      <c r="C15" s="18">
-        <f>'2025'!H17</f>
-        <v/>
-      </c>
-      <c r="D15" s="19">
-        <f>'2025'!I17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" s="23">
-      <c r="A20" s="24" t="inlineStr">
+    <row r="12" s="23">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Gesamt 2025 (ab April)</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
+        <f>SUM(B3:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="18">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="19">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" s="23"/>
+    <row r="14" s="23"/>
+    <row r="15" s="23"/>
+    <row r="16" s="23"/>
+    <row r="17" ht="30" customHeight="1" s="23">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Monat 2026</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Einnahmen (€)</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>Ausgaben (€)</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>Differenz (€)</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="18" s="23">
+      <c r="A18" s="10">
+        <f>'2026'!F5</f>
+        <v/>
+      </c>
+      <c r="B18" s="11">
+        <f>'2026'!G5</f>
+        <v/>
+      </c>
+      <c r="C18" s="12">
+        <f>'2026'!H5</f>
+        <v/>
+      </c>
+      <c r="D18" s="13">
+        <f>'2026'!I5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" s="23">
+      <c r="A19" s="10">
+        <f>'2026'!F6</f>
+        <v/>
+      </c>
+      <c r="B19" s="11">
+        <f>'2026'!G6</f>
+        <v/>
+      </c>
+      <c r="C19" s="12">
+        <f>'2026'!H6</f>
+        <v/>
+      </c>
+      <c r="D19" s="13">
+        <f>'2026'!I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" s="23">
+      <c r="A20" s="10">
+        <f>'2026'!F7</f>
+        <v/>
+      </c>
+      <c r="B20" s="11">
+        <f>'2026'!G7</f>
+        <v/>
+      </c>
+      <c r="C20" s="12">
+        <f>'2026'!H7</f>
+        <v/>
+      </c>
+      <c r="D20" s="13">
+        <f>'2026'!I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" s="23">
       <c r="A21" s="10">
-        <f>'2026'!F5</f>
+        <f>'2026'!F8</f>
         <v/>
       </c>
       <c r="B21" s="11">
-        <f>'2026'!G5</f>
+        <f>'2026'!G8</f>
         <v/>
       </c>
       <c r="C21" s="12">
-        <f>'2026'!H5</f>
+        <f>'2026'!H8</f>
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>'2026'!I5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
+        <f>'2026'!I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" s="23">
       <c r="A22" s="10">
-        <f>'2026'!F6</f>
+        <f>'2026'!F9</f>
         <v/>
       </c>
       <c r="B22" s="11">
-        <f>'2026'!G6</f>
+        <f>'2026'!G9</f>
         <v/>
       </c>
       <c r="C22" s="12">
-        <f>'2026'!H6</f>
+        <f>'2026'!H9</f>
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>'2026'!I6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
+        <f>'2026'!I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" s="23">
       <c r="A23" s="10">
-        <f>'2026'!F7</f>
+        <f>'2026'!F10</f>
         <v/>
       </c>
       <c r="B23" s="11">
-        <f>'2026'!G7</f>
+        <f>'2026'!G10</f>
         <v/>
       </c>
       <c r="C23" s="12">
-        <f>'2026'!H7</f>
+        <f>'2026'!H10</f>
         <v/>
       </c>
       <c r="D23" s="13">
-        <f>'2026'!I7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
+        <f>'2026'!I10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" s="23">
       <c r="A24" s="10">
-        <f>'2026'!F8</f>
+        <f>'2026'!F11</f>
         <v/>
       </c>
       <c r="B24" s="11">
-        <f>'2026'!G8</f>
+        <f>'2026'!G11</f>
         <v/>
       </c>
       <c r="C24" s="12">
-        <f>'2026'!H8</f>
+        <f>'2026'!H11</f>
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>'2026'!I8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
+        <f>'2026'!I11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" s="23">
       <c r="A25" s="10">
-        <f>'2026'!F9</f>
+        <f>'2026'!F12</f>
         <v/>
       </c>
       <c r="B25" s="11">
-        <f>'2026'!G9</f>
+        <f>'2026'!G12</f>
         <v/>
       </c>
       <c r="C25" s="12">
-        <f>'2026'!H9</f>
+        <f>'2026'!H12</f>
         <v/>
       </c>
       <c r="D25" s="13">
-        <f>'2026'!I9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
+        <f>'2026'!I12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" s="23">
       <c r="A26" s="10">
-        <f>'2026'!F10</f>
+        <f>'2026'!F13</f>
         <v/>
       </c>
       <c r="B26" s="11">
-        <f>'2026'!G10</f>
+        <f>'2026'!G13</f>
         <v/>
       </c>
       <c r="C26" s="12">
-        <f>'2026'!H10</f>
+        <f>'2026'!H13</f>
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>'2026'!I10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
+        <f>'2026'!I13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" s="23">
       <c r="A27" s="10">
-        <f>'2026'!F11</f>
+        <f>'2026'!F14</f>
         <v/>
       </c>
       <c r="B27" s="11">
-        <f>'2026'!G11</f>
+        <f>'2026'!G14</f>
         <v/>
       </c>
       <c r="C27" s="12">
-        <f>'2026'!H11</f>
+        <f>'2026'!H14</f>
         <v/>
       </c>
       <c r="D27" s="13">
-        <f>'2026'!I11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
+        <f>'2026'!I14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" s="23">
       <c r="A28" s="10">
-        <f>'2026'!F12</f>
+        <f>'2026'!F15</f>
         <v/>
       </c>
       <c r="B28" s="11">
-        <f>'2026'!G12</f>
+        <f>'2026'!G15</f>
         <v/>
       </c>
       <c r="C28" s="12">
-        <f>'2026'!H12</f>
+        <f>'2026'!H15</f>
         <v/>
       </c>
       <c r="D28" s="13">
-        <f>'2026'!I12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
+        <f>'2026'!I15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" s="23">
       <c r="A29" s="10">
-        <f>'2026'!F13</f>
+        <f>'2026'!F16</f>
         <v/>
       </c>
       <c r="B29" s="11">
-        <f>'2026'!G13</f>
+        <f>'2026'!G16</f>
         <v/>
       </c>
       <c r="C29" s="12">
-        <f>'2026'!H13</f>
+        <f>'2026'!H16</f>
         <v/>
       </c>
       <c r="D29" s="13">
-        <f>'2026'!I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10">
-        <f>'2026'!F14</f>
-        <v/>
-      </c>
-      <c r="B30" s="11">
-        <f>'2026'!G14</f>
-        <v/>
-      </c>
-      <c r="C30" s="12">
-        <f>'2026'!H14</f>
-        <v/>
-      </c>
-      <c r="D30" s="13">
-        <f>'2026'!I14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10">
-        <f>'2026'!F15</f>
-        <v/>
-      </c>
-      <c r="B31" s="11">
-        <f>'2026'!G15</f>
-        <v/>
-      </c>
-      <c r="C31" s="12">
-        <f>'2026'!H15</f>
-        <v/>
-      </c>
-      <c r="D31" s="13">
-        <f>'2026'!I15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10">
-        <f>'2026'!F16</f>
-        <v/>
-      </c>
-      <c r="B32" s="11">
-        <f>'2026'!G16</f>
-        <v/>
-      </c>
-      <c r="C32" s="12">
-        <f>'2026'!H16</f>
-        <v/>
-      </c>
-      <c r="D32" s="13">
         <f>'2026'!I16</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+    <row r="30" s="23">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Gesamt 2026</t>
         </is>
       </c>
-      <c r="B33" s="17">
+      <c r="B30" s="17">
         <f>'2026'!G17</f>
         <v/>
       </c>
-      <c r="C33" s="18">
+      <c r="C30" s="18">
         <f>'2026'!H17</f>
         <v/>
       </c>
-      <c r="D33" s="19">
+      <c r="D30" s="19">
         <f>'2026'!I17</f>
         <v/>
       </c>
     </row>
+    <row r="31" s="23"/>
+    <row r="32" s="23"/>
+    <row r="33" s="23"/>
+    <row r="34" s="23"/>
+    <row r="35" s="23"/>
+    <row r="36" s="23"/>
+    <row r="37" s="23"/>
+    <row r="38" s="23"/>
+    <row r="39" s="23"/>
   </sheetData>
-  <conditionalFormatting sqref="D3:D15">
+  <conditionalFormatting sqref="D3:D12">
     <cfRule type="expression" priority="1" dxfId="4">
       <formula>D3&lt;0</formula>
     </cfRule>
@@ -1059,12 +1019,12 @@
       <formula>D3&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D21:D33">
+  <conditionalFormatting sqref="D18:D30">
     <cfRule type="expression" priority="3" dxfId="4">
-      <formula>D21&lt;0</formula>
+      <formula>D18&lt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="5">
-      <formula>D21&gt;0</formula>
+      <formula>D18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1101,42 +1061,42 @@
       <c r="A2" s="2" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1" s="23">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Art</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Was war es?</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Betrag (€)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Monat 2025</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Einnahmen (€)</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="26" t="inlineStr">
         <is>
           <t>Ausgaben (€)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Differenz (€)</t>
         </is>
@@ -4399,42 +4359,42 @@
       <c r="A2" s="2" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1" s="23">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Art</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Was war es?</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Betrag (€)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Monat 2026</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Einnahmen (€)</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="26" t="inlineStr">
         <is>
           <t>Ausgaben (€)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Differenz (€)</t>
         </is>
